--- a/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
+++ b/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
@@ -29,6 +29,9 @@
     <sheet name="9 September" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="10 September" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="11 September" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="12 September" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="13 September" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="14 September" sheetId="25" state="visible" r:id="rId25"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H765"/>
+  <dimension ref="A1:H841"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -24594,6 +24597,2430 @@
         </is>
       </c>
       <c r="H765" s="2" t="inlineStr"/>
+    </row>
+    <row r="766" ht="20" customHeight="1">
+      <c r="A766" s="3" t="n">
+        <v>762</v>
+      </c>
+      <c r="B766" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C766" s="3" t="n">
+        <v>968</v>
+      </c>
+      <c r="D766" s="3" t="inlineStr">
+        <is>
+          <t>280139</t>
+        </is>
+      </c>
+      <c r="E766" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F766" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G766" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H766" s="3" t="inlineStr"/>
+    </row>
+    <row r="767" ht="20" customHeight="1">
+      <c r="A767" s="2" t="n">
+        <v>763</v>
+      </c>
+      <c r="B767" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C767" s="2" t="n">
+        <v>969</v>
+      </c>
+      <c r="D767" s="2" t="inlineStr">
+        <is>
+          <t>280140</t>
+        </is>
+      </c>
+      <c r="E767" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F767" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G767" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H767" s="2" t="inlineStr"/>
+    </row>
+    <row r="768" ht="20" customHeight="1">
+      <c r="A768" s="3" t="n">
+        <v>764</v>
+      </c>
+      <c r="B768" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C768" s="3" t="n">
+        <v>970</v>
+      </c>
+      <c r="D768" s="3" t="inlineStr">
+        <is>
+          <t>280141</t>
+        </is>
+      </c>
+      <c r="E768" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F768" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G768" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H768" s="3" t="inlineStr"/>
+    </row>
+    <row r="769" ht="20" customHeight="1">
+      <c r="A769" s="2" t="n">
+        <v>765</v>
+      </c>
+      <c r="B769" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C769" s="2" t="n">
+        <v>971</v>
+      </c>
+      <c r="D769" s="2" t="inlineStr">
+        <is>
+          <t>125987</t>
+        </is>
+      </c>
+      <c r="E769" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F769" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G769" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H769" s="2" t="inlineStr"/>
+    </row>
+    <row r="770" ht="20" customHeight="1">
+      <c r="A770" s="3" t="n">
+        <v>766</v>
+      </c>
+      <c r="B770" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C770" s="3" t="n">
+        <v>972</v>
+      </c>
+      <c r="D770" s="3" t="inlineStr">
+        <is>
+          <t>39841</t>
+        </is>
+      </c>
+      <c r="E770" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F770" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G770" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H770" s="3" t="inlineStr"/>
+    </row>
+    <row r="771" ht="20" customHeight="1">
+      <c r="A771" s="2" t="n">
+        <v>767</v>
+      </c>
+      <c r="B771" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C771" s="2" t="n">
+        <v>973</v>
+      </c>
+      <c r="D771" s="2" t="inlineStr">
+        <is>
+          <t>39842</t>
+        </is>
+      </c>
+      <c r="E771" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F771" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G771" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H771" s="2" t="inlineStr"/>
+    </row>
+    <row r="772" ht="20" customHeight="1">
+      <c r="A772" s="3" t="n">
+        <v>768</v>
+      </c>
+      <c r="B772" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C772" s="3" t="n">
+        <v>974</v>
+      </c>
+      <c r="D772" s="3" t="inlineStr"/>
+      <c r="E772" s="3" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="F772" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G772" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H772" s="3" t="inlineStr"/>
+    </row>
+    <row r="773" ht="20" customHeight="1">
+      <c r="A773" s="2" t="n">
+        <v>769</v>
+      </c>
+      <c r="B773" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C773" s="2" t="n">
+        <v>975</v>
+      </c>
+      <c r="D773" s="2" t="inlineStr">
+        <is>
+          <t>280145</t>
+        </is>
+      </c>
+      <c r="E773" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F773" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G773" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H773" s="2" t="inlineStr"/>
+    </row>
+    <row r="774" ht="20" customHeight="1">
+      <c r="A774" s="3" t="n">
+        <v>770</v>
+      </c>
+      <c r="B774" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C774" s="3" t="n">
+        <v>976</v>
+      </c>
+      <c r="D774" s="3" t="inlineStr">
+        <is>
+          <t>280146</t>
+        </is>
+      </c>
+      <c r="E774" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F774" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G774" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H774" s="3" t="inlineStr"/>
+    </row>
+    <row r="775" ht="20" customHeight="1">
+      <c r="A775" s="2" t="n">
+        <v>771</v>
+      </c>
+      <c r="B775" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C775" s="2" t="n">
+        <v>977</v>
+      </c>
+      <c r="D775" s="2" t="inlineStr">
+        <is>
+          <t>280144</t>
+        </is>
+      </c>
+      <c r="E775" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F775" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G775" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H775" s="2" t="inlineStr"/>
+    </row>
+    <row r="776" ht="20" customHeight="1">
+      <c r="A776" s="3" t="n">
+        <v>772</v>
+      </c>
+      <c r="B776" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C776" s="3" t="n">
+        <v>978</v>
+      </c>
+      <c r="D776" s="3" t="inlineStr">
+        <is>
+          <t>125822</t>
+        </is>
+      </c>
+      <c r="E776" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F776" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G776" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H776" s="3" t="inlineStr"/>
+    </row>
+    <row r="777" ht="20" customHeight="1">
+      <c r="A777" s="2" t="n">
+        <v>773</v>
+      </c>
+      <c r="B777" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C777" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="D777" s="2" t="inlineStr">
+        <is>
+          <t>125821</t>
+        </is>
+      </c>
+      <c r="E777" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F777" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G777" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H777" s="2" t="inlineStr"/>
+    </row>
+    <row r="778" ht="20" customHeight="1">
+      <c r="A778" s="3" t="n">
+        <v>774</v>
+      </c>
+      <c r="B778" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C778" s="3" t="n">
+        <v>980</v>
+      </c>
+      <c r="D778" s="3" t="inlineStr">
+        <is>
+          <t>280302</t>
+        </is>
+      </c>
+      <c r="E778" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F778" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G778" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H778" s="3" t="inlineStr"/>
+    </row>
+    <row r="779" ht="20" customHeight="1">
+      <c r="A779" s="2" t="n">
+        <v>775</v>
+      </c>
+      <c r="B779" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C779" s="2" t="n">
+        <v>981</v>
+      </c>
+      <c r="D779" s="2" t="inlineStr">
+        <is>
+          <t>125991</t>
+        </is>
+      </c>
+      <c r="E779" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F779" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G779" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H779" s="2" t="inlineStr"/>
+    </row>
+    <row r="780" ht="20" customHeight="1">
+      <c r="A780" s="3" t="n">
+        <v>776</v>
+      </c>
+      <c r="B780" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C780" s="3" t="n">
+        <v>982</v>
+      </c>
+      <c r="D780" s="3" t="inlineStr">
+        <is>
+          <t>125990</t>
+        </is>
+      </c>
+      <c r="E780" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F780" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G780" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H780" s="3" t="inlineStr"/>
+    </row>
+    <row r="781" ht="20" customHeight="1">
+      <c r="A781" s="2" t="n">
+        <v>777</v>
+      </c>
+      <c r="B781" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C781" s="2" t="n">
+        <v>983</v>
+      </c>
+      <c r="D781" s="2" t="inlineStr">
+        <is>
+          <t>125992</t>
+        </is>
+      </c>
+      <c r="E781" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F781" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G781" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H781" s="2" t="inlineStr"/>
+    </row>
+    <row r="782" ht="20" customHeight="1">
+      <c r="A782" s="3" t="n">
+        <v>778</v>
+      </c>
+      <c r="B782" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C782" s="3" t="n">
+        <v>984</v>
+      </c>
+      <c r="D782" s="3" t="inlineStr">
+        <is>
+          <t>125988</t>
+        </is>
+      </c>
+      <c r="E782" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F782" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G782" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H782" s="3" t="inlineStr"/>
+    </row>
+    <row r="783" ht="20" customHeight="1">
+      <c r="A783" s="2" t="n">
+        <v>779</v>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C783" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="D783" s="2" t="inlineStr">
+        <is>
+          <t>280143</t>
+        </is>
+      </c>
+      <c r="E783" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F783" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G783" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H783" s="2" t="inlineStr"/>
+    </row>
+    <row r="784" ht="20" customHeight="1">
+      <c r="A784" s="3" t="n">
+        <v>780</v>
+      </c>
+      <c r="B784" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C784" s="3" t="n">
+        <v>986</v>
+      </c>
+      <c r="D784" s="3" t="inlineStr">
+        <is>
+          <t>125989</t>
+        </is>
+      </c>
+      <c r="E784" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F784" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G784" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H784" s="3" t="inlineStr"/>
+    </row>
+    <row r="785" ht="20" customHeight="1">
+      <c r="A785" s="2" t="n">
+        <v>781</v>
+      </c>
+      <c r="B785" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="C785" s="2" t="n">
+        <v>987</v>
+      </c>
+      <c r="D785" s="2" t="inlineStr">
+        <is>
+          <t>280142</t>
+        </is>
+      </c>
+      <c r="E785" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F785" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G785" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H785" s="2" t="inlineStr"/>
+    </row>
+    <row r="786" ht="20" customHeight="1">
+      <c r="A786" s="3" t="n">
+        <v>782</v>
+      </c>
+      <c r="B786" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C786" s="3" t="n">
+        <v>991</v>
+      </c>
+      <c r="D786" s="3" t="inlineStr">
+        <is>
+          <t>280619</t>
+        </is>
+      </c>
+      <c r="E786" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F786" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G786" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H786" s="3" t="inlineStr"/>
+    </row>
+    <row r="787" ht="20" customHeight="1">
+      <c r="A787" s="2" t="n">
+        <v>783</v>
+      </c>
+      <c r="B787" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C787" s="2" t="n">
+        <v>992</v>
+      </c>
+      <c r="D787" s="2" t="inlineStr">
+        <is>
+          <t>280763</t>
+        </is>
+      </c>
+      <c r="E787" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F787" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G787" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H787" s="2" t="inlineStr"/>
+    </row>
+    <row r="788" ht="20" customHeight="1">
+      <c r="A788" s="3" t="n">
+        <v>784</v>
+      </c>
+      <c r="B788" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C788" s="3" t="n">
+        <v>993</v>
+      </c>
+      <c r="D788" s="3" t="inlineStr">
+        <is>
+          <t>280618</t>
+        </is>
+      </c>
+      <c r="E788" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F788" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G788" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H788" s="3" t="inlineStr"/>
+    </row>
+    <row r="789" ht="20" customHeight="1">
+      <c r="A789" s="2" t="n">
+        <v>785</v>
+      </c>
+      <c r="B789" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C789" s="2" t="n">
+        <v>994</v>
+      </c>
+      <c r="D789" s="2" t="inlineStr">
+        <is>
+          <t>280762</t>
+        </is>
+      </c>
+      <c r="E789" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F789" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G789" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H789" s="2" t="inlineStr"/>
+    </row>
+    <row r="790" ht="20" customHeight="1">
+      <c r="A790" s="3" t="n">
+        <v>786</v>
+      </c>
+      <c r="B790" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C790" s="3" t="n">
+        <v>995</v>
+      </c>
+      <c r="D790" s="3" t="inlineStr">
+        <is>
+          <t>39844</t>
+        </is>
+      </c>
+      <c r="E790" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F790" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G790" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H790" s="3" t="inlineStr"/>
+    </row>
+    <row r="791" ht="20" customHeight="1">
+      <c r="A791" s="2" t="n">
+        <v>787</v>
+      </c>
+      <c r="B791" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C791" s="2" t="n">
+        <v>996</v>
+      </c>
+      <c r="D791" s="2" t="inlineStr">
+        <is>
+          <t>39843</t>
+        </is>
+      </c>
+      <c r="E791" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F791" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G791" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H791" s="2" t="inlineStr"/>
+    </row>
+    <row r="792" ht="20" customHeight="1">
+      <c r="A792" s="3" t="n">
+        <v>788</v>
+      </c>
+      <c r="B792" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C792" s="3" t="n">
+        <v>997</v>
+      </c>
+      <c r="D792" s="3" t="inlineStr">
+        <is>
+          <t>280617</t>
+        </is>
+      </c>
+      <c r="E792" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F792" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G792" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H792" s="3" t="inlineStr"/>
+    </row>
+    <row r="793" ht="20" customHeight="1">
+      <c r="A793" s="2" t="n">
+        <v>789</v>
+      </c>
+      <c r="B793" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C793" s="2" t="n">
+        <v>998</v>
+      </c>
+      <c r="D793" s="2" t="inlineStr">
+        <is>
+          <t>280761</t>
+        </is>
+      </c>
+      <c r="E793" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F793" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G793" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H793" s="2" t="inlineStr"/>
+    </row>
+    <row r="794" ht="20" customHeight="1">
+      <c r="A794" s="3" t="n">
+        <v>790</v>
+      </c>
+      <c r="B794" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C794" s="3" t="n">
+        <v>999</v>
+      </c>
+      <c r="D794" s="3" t="inlineStr">
+        <is>
+          <t>280616</t>
+        </is>
+      </c>
+      <c r="E794" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F794" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G794" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H794" s="3" t="inlineStr"/>
+    </row>
+    <row r="795" ht="20" customHeight="1">
+      <c r="A795" s="2" t="n">
+        <v>791</v>
+      </c>
+      <c r="B795" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C795" s="2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="D795" s="2" t="inlineStr">
+        <is>
+          <t>125833</t>
+        </is>
+      </c>
+      <c r="E795" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F795" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G795" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H795" s="2" t="inlineStr"/>
+    </row>
+    <row r="796" ht="20" customHeight="1">
+      <c r="A796" s="3" t="n">
+        <v>792</v>
+      </c>
+      <c r="B796" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C796" s="3" t="n">
+        <v>1001</v>
+      </c>
+      <c r="D796" s="3" t="inlineStr">
+        <is>
+          <t>280613</t>
+        </is>
+      </c>
+      <c r="E796" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F796" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G796" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H796" s="3" t="inlineStr"/>
+    </row>
+    <row r="797" ht="20" customHeight="1">
+      <c r="A797" s="2" t="n">
+        <v>793</v>
+      </c>
+      <c r="B797" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C797" s="2" t="n">
+        <v>1002</v>
+      </c>
+      <c r="D797" s="2" t="inlineStr"/>
+      <c r="E797" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F797" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G797" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H797" s="2" t="inlineStr"/>
+    </row>
+    <row r="798" ht="20" customHeight="1">
+      <c r="A798" s="3" t="n">
+        <v>794</v>
+      </c>
+      <c r="B798" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C798" s="3" t="n">
+        <v>1003</v>
+      </c>
+      <c r="D798" s="3" t="inlineStr">
+        <is>
+          <t>125832</t>
+        </is>
+      </c>
+      <c r="E798" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F798" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G798" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H798" s="3" t="inlineStr"/>
+    </row>
+    <row r="799" ht="20" customHeight="1">
+      <c r="A799" s="2" t="n">
+        <v>795</v>
+      </c>
+      <c r="B799" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C799" s="2" t="n">
+        <v>1004</v>
+      </c>
+      <c r="D799" s="2" t="inlineStr">
+        <is>
+          <t>125862</t>
+        </is>
+      </c>
+      <c r="E799" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F799" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G799" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H799" s="2" t="inlineStr"/>
+    </row>
+    <row r="800" ht="20" customHeight="1">
+      <c r="A800" s="3" t="n">
+        <v>796</v>
+      </c>
+      <c r="B800" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C800" s="3" t="n">
+        <v>1005</v>
+      </c>
+      <c r="D800" s="3" t="inlineStr">
+        <is>
+          <t>125866</t>
+        </is>
+      </c>
+      <c r="E800" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F800" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G800" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H800" s="3" t="inlineStr"/>
+    </row>
+    <row r="801" ht="20" customHeight="1">
+      <c r="A801" s="2" t="n">
+        <v>797</v>
+      </c>
+      <c r="B801" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C801" s="2" t="n">
+        <v>1006</v>
+      </c>
+      <c r="D801" s="2" t="inlineStr">
+        <is>
+          <t>125863</t>
+        </is>
+      </c>
+      <c r="E801" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F801" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G801" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H801" s="2" t="inlineStr"/>
+    </row>
+    <row r="802" ht="20" customHeight="1">
+      <c r="A802" s="3" t="n">
+        <v>798</v>
+      </c>
+      <c r="B802" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C802" s="3" t="n">
+        <v>1007</v>
+      </c>
+      <c r="D802" s="3" t="inlineStr">
+        <is>
+          <t>125864</t>
+        </is>
+      </c>
+      <c r="E802" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F802" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G802" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H802" s="3" t="inlineStr"/>
+    </row>
+    <row r="803" ht="20" customHeight="1">
+      <c r="A803" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="B803" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C803" s="2" t="n">
+        <v>1008</v>
+      </c>
+      <c r="D803" s="2" t="inlineStr">
+        <is>
+          <t>125865</t>
+        </is>
+      </c>
+      <c r="E803" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F803" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G803" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H803" s="2" t="inlineStr"/>
+    </row>
+    <row r="804" ht="20" customHeight="1">
+      <c r="A804" s="3" t="n">
+        <v>800</v>
+      </c>
+      <c r="B804" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C804" s="3" t="n">
+        <v>1009</v>
+      </c>
+      <c r="D804" s="3" t="inlineStr">
+        <is>
+          <t>125831</t>
+        </is>
+      </c>
+      <c r="E804" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="F804" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G804" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H804" s="3" t="inlineStr"/>
+    </row>
+    <row r="805" ht="20" customHeight="1">
+      <c r="A805" s="2" t="n">
+        <v>801</v>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C805" s="2" t="n">
+        <v>1010</v>
+      </c>
+      <c r="D805" s="2" t="inlineStr">
+        <is>
+          <t>280760</t>
+        </is>
+      </c>
+      <c r="E805" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F805" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G805" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H805" s="2" t="inlineStr"/>
+    </row>
+    <row r="806" ht="20" customHeight="1">
+      <c r="A806" s="3" t="n">
+        <v>802</v>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C806" s="3" t="n">
+        <v>1011</v>
+      </c>
+      <c r="D806" s="3" t="inlineStr">
+        <is>
+          <t>280614</t>
+        </is>
+      </c>
+      <c r="E806" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F806" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G806" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H806" s="3" t="inlineStr"/>
+    </row>
+    <row r="807" ht="20" customHeight="1">
+      <c r="A807" s="2" t="n">
+        <v>803</v>
+      </c>
+      <c r="B807" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C807" s="2" t="n">
+        <v>1012</v>
+      </c>
+      <c r="D807" s="2" t="inlineStr">
+        <is>
+          <t>280612</t>
+        </is>
+      </c>
+      <c r="E807" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F807" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G807" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H807" s="2" t="inlineStr"/>
+    </row>
+    <row r="808" ht="20" customHeight="1">
+      <c r="A808" s="3" t="n">
+        <v>804</v>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C808" s="3" t="n">
+        <v>1013</v>
+      </c>
+      <c r="D808" s="3" t="inlineStr">
+        <is>
+          <t>280759</t>
+        </is>
+      </c>
+      <c r="E808" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F808" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G808" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H808" s="3" t="inlineStr"/>
+    </row>
+    <row r="809" ht="20" customHeight="1">
+      <c r="A809" s="2" t="n">
+        <v>805</v>
+      </c>
+      <c r="B809" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C809" s="2" t="n">
+        <v>1014</v>
+      </c>
+      <c r="D809" s="2" t="inlineStr">
+        <is>
+          <t>280615</t>
+        </is>
+      </c>
+      <c r="E809" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F809" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G809" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H809" s="2" t="inlineStr"/>
+    </row>
+    <row r="810" ht="20" customHeight="1">
+      <c r="A810" s="3" t="n">
+        <v>806</v>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C810" s="3" t="n">
+        <v>1015</v>
+      </c>
+      <c r="D810" s="3" t="inlineStr">
+        <is>
+          <t>280620</t>
+        </is>
+      </c>
+      <c r="E810" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F810" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G810" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H810" s="3" t="inlineStr"/>
+    </row>
+    <row r="811" ht="20" customHeight="1">
+      <c r="A811" s="2" t="n">
+        <v>807</v>
+      </c>
+      <c r="B811" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C811" s="2" t="n">
+        <v>1016</v>
+      </c>
+      <c r="D811" s="2" t="inlineStr">
+        <is>
+          <t>280611</t>
+        </is>
+      </c>
+      <c r="E811" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F811" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G811" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H811" s="2" t="inlineStr"/>
+    </row>
+    <row r="812" ht="20" customHeight="1">
+      <c r="A812" s="3" t="n">
+        <v>808</v>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C812" s="3" t="n">
+        <v>1017</v>
+      </c>
+      <c r="D812" s="3" t="inlineStr">
+        <is>
+          <t>280412</t>
+        </is>
+      </c>
+      <c r="E812" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F812" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G812" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H812" s="3" t="inlineStr"/>
+    </row>
+    <row r="813" ht="20" customHeight="1">
+      <c r="A813" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="B813" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C813" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="D813" s="2" t="inlineStr">
+        <is>
+          <t>280299</t>
+        </is>
+      </c>
+      <c r="E813" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F813" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G813" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H813" s="2" t="inlineStr"/>
+    </row>
+    <row r="814" ht="20" customHeight="1">
+      <c r="A814" s="3" t="n">
+        <v>810</v>
+      </c>
+      <c r="B814" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="C814" s="3" t="n">
+        <v>1019</v>
+      </c>
+      <c r="D814" s="3" t="inlineStr">
+        <is>
+          <t>280300</t>
+        </is>
+      </c>
+      <c r="E814" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F814" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G814" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H814" s="3" t="inlineStr"/>
+    </row>
+    <row r="815" ht="20" customHeight="1">
+      <c r="A815" s="2" t="n">
+        <v>811</v>
+      </c>
+      <c r="B815" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C815" s="2" t="n">
+        <v>1020</v>
+      </c>
+      <c r="D815" s="2" t="inlineStr">
+        <is>
+          <t>282168</t>
+        </is>
+      </c>
+      <c r="E815" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F815" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G815" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H815" s="2" t="inlineStr"/>
+    </row>
+    <row r="816" ht="20" customHeight="1">
+      <c r="A816" s="3" t="n">
+        <v>812</v>
+      </c>
+      <c r="B816" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C816" s="3" t="n">
+        <v>1021</v>
+      </c>
+      <c r="D816" s="3" t="inlineStr">
+        <is>
+          <t>282096</t>
+        </is>
+      </c>
+      <c r="E816" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F816" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G816" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H816" s="3" t="inlineStr"/>
+    </row>
+    <row r="817" ht="20" customHeight="1">
+      <c r="A817" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="B817" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C817" s="2" t="n">
+        <v>1022</v>
+      </c>
+      <c r="D817" s="2" t="inlineStr">
+        <is>
+          <t>282097</t>
+        </is>
+      </c>
+      <c r="E817" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F817" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G817" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H817" s="2" t="inlineStr"/>
+    </row>
+    <row r="818" ht="20" customHeight="1">
+      <c r="A818" s="3" t="n">
+        <v>814</v>
+      </c>
+      <c r="B818" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C818" s="3" t="n">
+        <v>1023</v>
+      </c>
+      <c r="D818" s="3" t="inlineStr">
+        <is>
+          <t>282098</t>
+        </is>
+      </c>
+      <c r="E818" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F818" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G818" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H818" s="3" t="inlineStr"/>
+    </row>
+    <row r="819" ht="20" customHeight="1">
+      <c r="A819" s="2" t="n">
+        <v>815</v>
+      </c>
+      <c r="B819" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C819" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="D819" s="2" t="inlineStr">
+        <is>
+          <t>282171</t>
+        </is>
+      </c>
+      <c r="E819" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F819" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G819" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H819" s="2" t="inlineStr"/>
+    </row>
+    <row r="820" ht="20" customHeight="1">
+      <c r="A820" s="3" t="n">
+        <v>816</v>
+      </c>
+      <c r="B820" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C820" s="3" t="n">
+        <v>1025</v>
+      </c>
+      <c r="D820" s="3" t="inlineStr">
+        <is>
+          <t>282174</t>
+        </is>
+      </c>
+      <c r="E820" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F820" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G820" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H820" s="3" t="inlineStr"/>
+    </row>
+    <row r="821" ht="20" customHeight="1">
+      <c r="A821" s="2" t="n">
+        <v>817</v>
+      </c>
+      <c r="B821" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C821" s="2" t="n">
+        <v>1026</v>
+      </c>
+      <c r="D821" s="2" t="inlineStr">
+        <is>
+          <t>282173</t>
+        </is>
+      </c>
+      <c r="E821" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F821" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G821" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H821" s="2" t="inlineStr"/>
+    </row>
+    <row r="822" ht="20" customHeight="1">
+      <c r="A822" s="3" t="n">
+        <v>818</v>
+      </c>
+      <c r="B822" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C822" s="3" t="n">
+        <v>1027</v>
+      </c>
+      <c r="D822" s="3" t="inlineStr">
+        <is>
+          <t>282176</t>
+        </is>
+      </c>
+      <c r="E822" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F822" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G822" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H822" s="3" t="inlineStr"/>
+    </row>
+    <row r="823" ht="20" customHeight="1">
+      <c r="A823" s="2" t="n">
+        <v>819</v>
+      </c>
+      <c r="B823" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C823" s="2" t="n">
+        <v>1028</v>
+      </c>
+      <c r="D823" s="2" t="inlineStr">
+        <is>
+          <t>282169</t>
+        </is>
+      </c>
+      <c r="E823" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F823" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G823" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H823" s="2" t="inlineStr"/>
+    </row>
+    <row r="824" ht="20" customHeight="1">
+      <c r="A824" s="3" t="n">
+        <v>820</v>
+      </c>
+      <c r="B824" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C824" s="3" t="n">
+        <v>1029</v>
+      </c>
+      <c r="D824" s="3" t="inlineStr">
+        <is>
+          <t>282170</t>
+        </is>
+      </c>
+      <c r="E824" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F824" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G824" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H824" s="3" t="inlineStr"/>
+    </row>
+    <row r="825" ht="20" customHeight="1">
+      <c r="A825" s="2" t="n">
+        <v>821</v>
+      </c>
+      <c r="B825" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C825" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="D825" s="2" t="inlineStr">
+        <is>
+          <t>282175</t>
+        </is>
+      </c>
+      <c r="E825" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F825" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G825" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H825" s="2" t="inlineStr"/>
+    </row>
+    <row r="826" ht="20" customHeight="1">
+      <c r="A826" s="3" t="n">
+        <v>822</v>
+      </c>
+      <c r="B826" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C826" s="3" t="n">
+        <v>1031</v>
+      </c>
+      <c r="D826" s="3" t="inlineStr">
+        <is>
+          <t>282252</t>
+        </is>
+      </c>
+      <c r="E826" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F826" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G826" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H826" s="3" t="inlineStr"/>
+    </row>
+    <row r="827" ht="20" customHeight="1">
+      <c r="A827" s="2" t="n">
+        <v>823</v>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C827" s="2" t="n">
+        <v>1032</v>
+      </c>
+      <c r="D827" s="2" t="inlineStr">
+        <is>
+          <t>282228</t>
+        </is>
+      </c>
+      <c r="E827" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F827" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G827" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H827" s="2" t="inlineStr"/>
+    </row>
+    <row r="828" ht="20" customHeight="1">
+      <c r="A828" s="3" t="n">
+        <v>824</v>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C828" s="3" t="n">
+        <v>1033</v>
+      </c>
+      <c r="D828" s="3" t="inlineStr">
+        <is>
+          <t>282099</t>
+        </is>
+      </c>
+      <c r="E828" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F828" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G828" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H828" s="3" t="inlineStr"/>
+    </row>
+    <row r="829" ht="20" customHeight="1">
+      <c r="A829" s="2" t="n">
+        <v>825</v>
+      </c>
+      <c r="B829" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C829" s="2" t="n">
+        <v>1034</v>
+      </c>
+      <c r="D829" s="2" t="inlineStr">
+        <is>
+          <t>282251</t>
+        </is>
+      </c>
+      <c r="E829" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F829" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G829" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H829" s="2" t="inlineStr"/>
+    </row>
+    <row r="830" ht="20" customHeight="1">
+      <c r="A830" s="3" t="n">
+        <v>826</v>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C830" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="D830" s="3" t="inlineStr">
+        <is>
+          <t>282100</t>
+        </is>
+      </c>
+      <c r="E830" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F830" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G830" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H830" s="3" t="inlineStr"/>
+    </row>
+    <row r="831" ht="20" customHeight="1">
+      <c r="A831" s="2" t="n">
+        <v>827</v>
+      </c>
+      <c r="B831" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C831" s="2" t="n">
+        <v>1036</v>
+      </c>
+      <c r="D831" s="2" t="inlineStr">
+        <is>
+          <t>280315</t>
+        </is>
+      </c>
+      <c r="E831" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F831" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G831" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H831" s="2" t="inlineStr"/>
+    </row>
+    <row r="832" ht="20" customHeight="1">
+      <c r="A832" s="3" t="n">
+        <v>828</v>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C832" s="3" t="n">
+        <v>1037</v>
+      </c>
+      <c r="D832" s="3" t="inlineStr">
+        <is>
+          <t>280314</t>
+        </is>
+      </c>
+      <c r="E832" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F832" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G832" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H832" s="3" t="inlineStr"/>
+    </row>
+    <row r="833" ht="20" customHeight="1">
+      <c r="A833" s="2" t="n">
+        <v>829</v>
+      </c>
+      <c r="B833" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C833" s="2" t="n">
+        <v>1038</v>
+      </c>
+      <c r="D833" s="2" t="inlineStr">
+        <is>
+          <t>282172</t>
+        </is>
+      </c>
+      <c r="E833" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F833" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G833" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H833" s="2" t="inlineStr"/>
+    </row>
+    <row r="834" ht="20" customHeight="1">
+      <c r="A834" s="3" t="n">
+        <v>830</v>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C834" s="3" t="n">
+        <v>1039</v>
+      </c>
+      <c r="D834" s="3" t="inlineStr">
+        <is>
+          <t>282229</t>
+        </is>
+      </c>
+      <c r="E834" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F834" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G834" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H834" s="3" t="inlineStr"/>
+    </row>
+    <row r="835" ht="20" customHeight="1">
+      <c r="A835" s="2" t="n">
+        <v>831</v>
+      </c>
+      <c r="B835" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C835" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="D835" s="2" t="inlineStr">
+        <is>
+          <t>282253</t>
+        </is>
+      </c>
+      <c r="E835" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F835" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G835" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H835" s="2" t="inlineStr"/>
+    </row>
+    <row r="836" ht="20" customHeight="1">
+      <c r="A836" s="3" t="n">
+        <v>832</v>
+      </c>
+      <c r="B836" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C836" s="3" t="n">
+        <v>1041</v>
+      </c>
+      <c r="D836" s="3" t="inlineStr">
+        <is>
+          <t>282230</t>
+        </is>
+      </c>
+      <c r="E836" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F836" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G836" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H836" s="3" t="inlineStr"/>
+    </row>
+    <row r="837" ht="20" customHeight="1">
+      <c r="A837" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="B837" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C837" s="2" t="n">
+        <v>1042</v>
+      </c>
+      <c r="D837" s="2" t="inlineStr">
+        <is>
+          <t>282231</t>
+        </is>
+      </c>
+      <c r="E837" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F837" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G837" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H837" s="2" t="inlineStr"/>
+    </row>
+    <row r="838" ht="20" customHeight="1">
+      <c r="A838" s="3" t="n">
+        <v>834</v>
+      </c>
+      <c r="B838" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C838" s="3" t="n">
+        <v>1043</v>
+      </c>
+      <c r="D838" s="3" t="inlineStr">
+        <is>
+          <t>282167</t>
+        </is>
+      </c>
+      <c r="E838" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F838" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G838" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H838" s="3" t="inlineStr"/>
+    </row>
+    <row r="839" ht="20" customHeight="1">
+      <c r="A839" s="2" t="n">
+        <v>835</v>
+      </c>
+      <c r="B839" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C839" s="2" t="n">
+        <v>1044</v>
+      </c>
+      <c r="D839" s="2" t="inlineStr">
+        <is>
+          <t>282166</t>
+        </is>
+      </c>
+      <c r="E839" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F839" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G839" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H839" s="2" t="inlineStr"/>
+    </row>
+    <row r="840" ht="20" customHeight="1">
+      <c r="A840" s="3" t="n">
+        <v>836</v>
+      </c>
+      <c r="B840" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C840" s="3" t="n">
+        <v>1045</v>
+      </c>
+      <c r="D840" s="3" t="inlineStr">
+        <is>
+          <t>282416</t>
+        </is>
+      </c>
+      <c r="E840" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F840" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G840" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H840" s="3" t="inlineStr"/>
+    </row>
+    <row r="841" ht="20" customHeight="1">
+      <c r="A841" s="2" t="n">
+        <v>837</v>
+      </c>
+      <c r="B841" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C841" s="2" t="n">
+        <v>1046</v>
+      </c>
+      <c r="D841" s="2" t="inlineStr">
+        <is>
+          <t>282095</t>
+        </is>
+      </c>
+      <c r="E841" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F841" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G841" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H841" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -37002,6 +39429,2239 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>968</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>280139</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>969</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>280140</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>970</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>280141</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>971</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>125987</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>972</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>39841</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>973</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>39842</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>974</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr"/>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>975</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>280145</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>280146</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>977</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>280144</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>978</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>125822</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>979</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>125821</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>980</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>280302</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>981</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>125991</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>982</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>125990</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>983</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>125992</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>984</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>125988</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>985</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>280143</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>986</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>125989</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>987</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>280142</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>991</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>280619</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>992</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>280763</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>993</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>280618</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>994</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>280762</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>995</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>39844</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>996</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>39843</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>997</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>280617</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>998</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>280761</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>280616</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>125833</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>280613</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr"/>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1003</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>125832</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1004</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>125862</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1005</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>125866</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1006</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>125863</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>125864</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1008</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>125865</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>125831</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>280760</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>280614</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1012</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>280612</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1013</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>280759</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1014</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>280615</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>280620</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1016</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>280611</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>280412</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1018</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>280299</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>280300</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1020</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>282168</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1021</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>282096</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1022</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>282097</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1023</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>282098</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>282171</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1025</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>282174</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1026</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>282173</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1027</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>282176</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1028</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>282169</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1029</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>282170</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1030</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>282175</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1031</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>282252</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1032</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>282228</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1033</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>282099</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1034</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>282251</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1035</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>282100</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1036</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>280315</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1037</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>280314</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1038</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>282172</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1039</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>282229</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1040</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>282253</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1041</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>282230</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1042</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>282231</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1043</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>282167</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1044</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>282166</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1045</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>282416</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1046</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>282095</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
+++ b/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
@@ -32,6 +32,9 @@
     <sheet name="12 September" sheetId="23" state="visible" r:id="rId23"/>
     <sheet name="13 September" sheetId="24" state="visible" r:id="rId24"/>
     <sheet name="14 September" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="17 September" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="18 September" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="19 September" sheetId="28" state="visible" r:id="rId28"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H841"/>
+  <dimension ref="A1:H959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27021,6 +27024,3782 @@
         </is>
       </c>
       <c r="H841" s="2" t="inlineStr"/>
+    </row>
+    <row r="842" ht="20" customHeight="1">
+      <c r="A842" s="3" t="n">
+        <v>838</v>
+      </c>
+      <c r="B842" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C842" s="3" t="n">
+        <v>1047</v>
+      </c>
+      <c r="D842" s="3" t="inlineStr">
+        <is>
+          <t>284912</t>
+        </is>
+      </c>
+      <c r="E842" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F842" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G842" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H842" s="3" t="inlineStr"/>
+    </row>
+    <row r="843" ht="20" customHeight="1">
+      <c r="A843" s="2" t="n">
+        <v>839</v>
+      </c>
+      <c r="B843" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C843" s="2" t="n">
+        <v>1048</v>
+      </c>
+      <c r="D843" s="2" t="inlineStr">
+        <is>
+          <t>284626</t>
+        </is>
+      </c>
+      <c r="E843" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F843" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G843" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H843" s="2" t="inlineStr"/>
+    </row>
+    <row r="844" ht="20" customHeight="1">
+      <c r="A844" s="3" t="n">
+        <v>840</v>
+      </c>
+      <c r="B844" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C844" s="3" t="n">
+        <v>1049</v>
+      </c>
+      <c r="D844" s="3" t="inlineStr">
+        <is>
+          <t>284906</t>
+        </is>
+      </c>
+      <c r="E844" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F844" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G844" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H844" s="3" t="inlineStr"/>
+    </row>
+    <row r="845" ht="20" customHeight="1">
+      <c r="A845" s="2" t="n">
+        <v>841</v>
+      </c>
+      <c r="B845" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C845" s="2" t="n">
+        <v>1050</v>
+      </c>
+      <c r="D845" s="2" t="inlineStr">
+        <is>
+          <t>284908</t>
+        </is>
+      </c>
+      <c r="E845" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F845" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G845" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H845" s="2" t="inlineStr"/>
+    </row>
+    <row r="846" ht="20" customHeight="1">
+      <c r="A846" s="3" t="n">
+        <v>842</v>
+      </c>
+      <c r="B846" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C846" s="3" t="n">
+        <v>1051</v>
+      </c>
+      <c r="D846" s="3" t="inlineStr">
+        <is>
+          <t>284721</t>
+        </is>
+      </c>
+      <c r="E846" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F846" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G846" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H846" s="3" t="inlineStr"/>
+    </row>
+    <row r="847" ht="20" customHeight="1">
+      <c r="A847" s="2" t="n">
+        <v>843</v>
+      </c>
+      <c r="B847" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C847" s="2" t="n">
+        <v>1052</v>
+      </c>
+      <c r="D847" s="2" t="inlineStr">
+        <is>
+          <t>284627</t>
+        </is>
+      </c>
+      <c r="E847" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F847" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G847" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H847" s="2" t="inlineStr"/>
+    </row>
+    <row r="848" ht="20" customHeight="1">
+      <c r="A848" s="3" t="n">
+        <v>844</v>
+      </c>
+      <c r="B848" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C848" s="3" t="n">
+        <v>1053</v>
+      </c>
+      <c r="D848" s="3" t="inlineStr">
+        <is>
+          <t>284628</t>
+        </is>
+      </c>
+      <c r="E848" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F848" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G848" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H848" s="3" t="inlineStr"/>
+    </row>
+    <row r="849" ht="20" customHeight="1">
+      <c r="A849" s="2" t="n">
+        <v>845</v>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C849" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="D849" s="2" t="inlineStr">
+        <is>
+          <t>284911</t>
+        </is>
+      </c>
+      <c r="E849" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F849" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G849" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H849" s="2" t="inlineStr"/>
+    </row>
+    <row r="850" ht="20" customHeight="1">
+      <c r="A850" s="3" t="n">
+        <v>846</v>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C850" s="3" t="n">
+        <v>1055</v>
+      </c>
+      <c r="D850" s="3" t="inlineStr">
+        <is>
+          <t>284909</t>
+        </is>
+      </c>
+      <c r="E850" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F850" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G850" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H850" s="3" t="inlineStr"/>
+    </row>
+    <row r="851" ht="20" customHeight="1">
+      <c r="A851" s="2" t="n">
+        <v>847</v>
+      </c>
+      <c r="B851" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C851" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="D851" s="2" t="inlineStr">
+        <is>
+          <t>284910</t>
+        </is>
+      </c>
+      <c r="E851" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F851" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G851" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H851" s="2" t="inlineStr"/>
+    </row>
+    <row r="852" ht="20" customHeight="1">
+      <c r="A852" s="3" t="n">
+        <v>848</v>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C852" s="3" t="n">
+        <v>1057</v>
+      </c>
+      <c r="D852" s="3" t="inlineStr">
+        <is>
+          <t>284914</t>
+        </is>
+      </c>
+      <c r="E852" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F852" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G852" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H852" s="3" t="inlineStr"/>
+    </row>
+    <row r="853" ht="20" customHeight="1">
+      <c r="A853" s="2" t="n">
+        <v>849</v>
+      </c>
+      <c r="B853" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C853" s="2" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D853" s="2" t="inlineStr">
+        <is>
+          <t>284913</t>
+        </is>
+      </c>
+      <c r="E853" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F853" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G853" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H853" s="2" t="inlineStr"/>
+    </row>
+    <row r="854" ht="20" customHeight="1">
+      <c r="A854" s="3" t="n">
+        <v>850</v>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C854" s="3" t="n">
+        <v>1059</v>
+      </c>
+      <c r="D854" s="3" t="inlineStr">
+        <is>
+          <t>284717</t>
+        </is>
+      </c>
+      <c r="E854" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F854" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G854" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H854" s="3" t="inlineStr"/>
+    </row>
+    <row r="855" ht="20" customHeight="1">
+      <c r="A855" s="2" t="n">
+        <v>851</v>
+      </c>
+      <c r="B855" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C855" s="2" t="n">
+        <v>1060</v>
+      </c>
+      <c r="D855" s="2" t="inlineStr">
+        <is>
+          <t>284718</t>
+        </is>
+      </c>
+      <c r="E855" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F855" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G855" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H855" s="2" t="inlineStr"/>
+    </row>
+    <row r="856" ht="20" customHeight="1">
+      <c r="A856" s="3" t="n">
+        <v>852</v>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C856" s="3" t="n">
+        <v>1072</v>
+      </c>
+      <c r="D856" s="3" t="inlineStr">
+        <is>
+          <t>374138</t>
+        </is>
+      </c>
+      <c r="E856" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F856" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G856" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H856" s="3" t="inlineStr"/>
+    </row>
+    <row r="857" ht="20" customHeight="1">
+      <c r="A857" s="2" t="n">
+        <v>853</v>
+      </c>
+      <c r="B857" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C857" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="D857" s="2" t="inlineStr">
+        <is>
+          <t>374137</t>
+        </is>
+      </c>
+      <c r="E857" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F857" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G857" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H857" s="2" t="inlineStr"/>
+    </row>
+    <row r="858" ht="20" customHeight="1">
+      <c r="A858" s="3" t="n">
+        <v>854</v>
+      </c>
+      <c r="B858" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C858" s="3" t="n">
+        <v>1093</v>
+      </c>
+      <c r="D858" s="3" t="inlineStr">
+        <is>
+          <t>284907</t>
+        </is>
+      </c>
+      <c r="E858" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F858" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G858" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H858" s="3" t="inlineStr"/>
+    </row>
+    <row r="859" ht="20" customHeight="1">
+      <c r="A859" s="2" t="n">
+        <v>855</v>
+      </c>
+      <c r="B859" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C859" s="2" t="n">
+        <v>1094</v>
+      </c>
+      <c r="D859" s="2" t="inlineStr">
+        <is>
+          <t>284637</t>
+        </is>
+      </c>
+      <c r="E859" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F859" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G859" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H859" s="2" t="inlineStr"/>
+    </row>
+    <row r="860" ht="20" customHeight="1">
+      <c r="A860" s="3" t="n">
+        <v>856</v>
+      </c>
+      <c r="B860" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C860" s="3" t="n">
+        <v>1095</v>
+      </c>
+      <c r="D860" s="3" t="inlineStr">
+        <is>
+          <t>284282</t>
+        </is>
+      </c>
+      <c r="E860" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F860" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G860" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H860" s="3" t="inlineStr"/>
+    </row>
+    <row r="861" ht="20" customHeight="1">
+      <c r="A861" s="2" t="n">
+        <v>857</v>
+      </c>
+      <c r="B861" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C861" s="2" t="n">
+        <v>1096</v>
+      </c>
+      <c r="D861" s="2" t="inlineStr">
+        <is>
+          <t>284715</t>
+        </is>
+      </c>
+      <c r="E861" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F861" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G861" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H861" s="2" t="inlineStr"/>
+    </row>
+    <row r="862" ht="20" customHeight="1">
+      <c r="A862" s="3" t="n">
+        <v>858</v>
+      </c>
+      <c r="B862" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C862" s="3" t="n">
+        <v>1097</v>
+      </c>
+      <c r="D862" s="3" t="inlineStr">
+        <is>
+          <t>284716</t>
+        </is>
+      </c>
+      <c r="E862" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F862" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G862" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H862" s="3" t="inlineStr"/>
+    </row>
+    <row r="863" ht="20" customHeight="1">
+      <c r="A863" s="2" t="n">
+        <v>859</v>
+      </c>
+      <c r="B863" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C863" s="2" t="n">
+        <v>1098</v>
+      </c>
+      <c r="D863" s="2" t="inlineStr">
+        <is>
+          <t>284283</t>
+        </is>
+      </c>
+      <c r="E863" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F863" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G863" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H863" s="2" t="inlineStr"/>
+    </row>
+    <row r="864" ht="20" customHeight="1">
+      <c r="A864" s="3" t="n">
+        <v>860</v>
+      </c>
+      <c r="B864" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C864" s="3" t="n">
+        <v>1099</v>
+      </c>
+      <c r="D864" s="3" t="inlineStr">
+        <is>
+          <t>284904</t>
+        </is>
+      </c>
+      <c r="E864" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F864" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G864" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H864" s="3" t="inlineStr"/>
+    </row>
+    <row r="865" ht="20" customHeight="1">
+      <c r="A865" s="2" t="n">
+        <v>861</v>
+      </c>
+      <c r="B865" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C865" s="2" t="n">
+        <v>1100</v>
+      </c>
+      <c r="D865" s="2" t="inlineStr">
+        <is>
+          <t>284905</t>
+        </is>
+      </c>
+      <c r="E865" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F865" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G865" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H865" s="2" t="inlineStr"/>
+    </row>
+    <row r="866" ht="20" customHeight="1">
+      <c r="A866" s="3" t="n">
+        <v>862</v>
+      </c>
+      <c r="B866" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C866" s="3" t="n">
+        <v>1101</v>
+      </c>
+      <c r="D866" s="3" t="inlineStr">
+        <is>
+          <t>284901</t>
+        </is>
+      </c>
+      <c r="E866" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F866" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G866" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H866" s="3" t="inlineStr"/>
+    </row>
+    <row r="867" ht="20" customHeight="1">
+      <c r="A867" s="2" t="n">
+        <v>863</v>
+      </c>
+      <c r="B867" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C867" s="2" t="n">
+        <v>1102</v>
+      </c>
+      <c r="D867" s="2" t="inlineStr">
+        <is>
+          <t>284902</t>
+        </is>
+      </c>
+      <c r="E867" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F867" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G867" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H867" s="2" t="inlineStr"/>
+    </row>
+    <row r="868" ht="20" customHeight="1">
+      <c r="A868" s="3" t="n">
+        <v>864</v>
+      </c>
+      <c r="B868" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C868" s="3" t="n">
+        <v>1103</v>
+      </c>
+      <c r="D868" s="3" t="inlineStr">
+        <is>
+          <t>284903</t>
+        </is>
+      </c>
+      <c r="E868" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F868" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G868" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H868" s="3" t="inlineStr"/>
+    </row>
+    <row r="869" ht="20" customHeight="1">
+      <c r="A869" s="2" t="n">
+        <v>865</v>
+      </c>
+      <c r="B869" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C869" s="2" t="n">
+        <v>1104</v>
+      </c>
+      <c r="D869" s="2" t="inlineStr">
+        <is>
+          <t>284636</t>
+        </is>
+      </c>
+      <c r="E869" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F869" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G869" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H869" s="2" t="inlineStr"/>
+    </row>
+    <row r="870" ht="20" customHeight="1">
+      <c r="A870" s="3" t="n">
+        <v>866</v>
+      </c>
+      <c r="B870" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C870" s="3" t="n">
+        <v>1105</v>
+      </c>
+      <c r="D870" s="3" t="inlineStr">
+        <is>
+          <t>284919</t>
+        </is>
+      </c>
+      <c r="E870" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F870" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G870" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H870" s="3" t="inlineStr"/>
+    </row>
+    <row r="871" ht="20" customHeight="1">
+      <c r="A871" s="2" t="n">
+        <v>867</v>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C871" s="2" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D871" s="2" t="inlineStr">
+        <is>
+          <t>284635</t>
+        </is>
+      </c>
+      <c r="E871" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F871" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G871" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H871" s="2" t="inlineStr"/>
+    </row>
+    <row r="872" ht="20" customHeight="1">
+      <c r="A872" s="3" t="n">
+        <v>868</v>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C872" s="3" t="n">
+        <v>1107</v>
+      </c>
+      <c r="D872" s="3" t="inlineStr">
+        <is>
+          <t>284634</t>
+        </is>
+      </c>
+      <c r="E872" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F872" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G872" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H872" s="3" t="inlineStr"/>
+    </row>
+    <row r="873" ht="20" customHeight="1">
+      <c r="A873" s="2" t="n">
+        <v>869</v>
+      </c>
+      <c r="B873" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C873" s="2" t="n">
+        <v>1108</v>
+      </c>
+      <c r="D873" s="2" t="inlineStr">
+        <is>
+          <t>284920</t>
+        </is>
+      </c>
+      <c r="E873" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F873" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G873" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H873" s="2" t="inlineStr"/>
+    </row>
+    <row r="874" ht="20" customHeight="1">
+      <c r="A874" s="3" t="n">
+        <v>870</v>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C874" s="3" t="n">
+        <v>1109</v>
+      </c>
+      <c r="D874" s="3" t="inlineStr">
+        <is>
+          <t>284629</t>
+        </is>
+      </c>
+      <c r="E874" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F874" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G874" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H874" s="3" t="inlineStr"/>
+    </row>
+    <row r="875" ht="20" customHeight="1">
+      <c r="A875" s="2" t="n">
+        <v>871</v>
+      </c>
+      <c r="B875" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C875" s="2" t="n">
+        <v>1110</v>
+      </c>
+      <c r="D875" s="2" t="inlineStr">
+        <is>
+          <t>284633</t>
+        </is>
+      </c>
+      <c r="E875" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F875" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G875" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H875" s="2" t="inlineStr"/>
+    </row>
+    <row r="876" ht="20" customHeight="1">
+      <c r="A876" s="3" t="n">
+        <v>872</v>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C876" s="3" t="n">
+        <v>1111</v>
+      </c>
+      <c r="D876" s="3" t="inlineStr">
+        <is>
+          <t>284632</t>
+        </is>
+      </c>
+      <c r="E876" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F876" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G876" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H876" s="3" t="inlineStr"/>
+    </row>
+    <row r="877" ht="20" customHeight="1">
+      <c r="A877" s="2" t="n">
+        <v>873</v>
+      </c>
+      <c r="B877" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C877" s="2" t="n">
+        <v>1112</v>
+      </c>
+      <c r="D877" s="2" t="inlineStr">
+        <is>
+          <t>284630</t>
+        </is>
+      </c>
+      <c r="E877" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F877" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G877" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H877" s="2" t="inlineStr"/>
+    </row>
+    <row r="878" ht="20" customHeight="1">
+      <c r="A878" s="3" t="n">
+        <v>874</v>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C878" s="3" t="n">
+        <v>1113</v>
+      </c>
+      <c r="D878" s="3" t="inlineStr">
+        <is>
+          <t>284631</t>
+        </is>
+      </c>
+      <c r="E878" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F878" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G878" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H878" s="3" t="inlineStr"/>
+    </row>
+    <row r="879" ht="20" customHeight="1">
+      <c r="A879" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="B879" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C879" s="2" t="n">
+        <v>1114</v>
+      </c>
+      <c r="D879" s="2" t="inlineStr">
+        <is>
+          <t>284918</t>
+        </is>
+      </c>
+      <c r="E879" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F879" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G879" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H879" s="2" t="inlineStr"/>
+    </row>
+    <row r="880" ht="20" customHeight="1">
+      <c r="A880" s="3" t="n">
+        <v>876</v>
+      </c>
+      <c r="B880" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C880" s="3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="D880" s="3" t="inlineStr">
+        <is>
+          <t>284916</t>
+        </is>
+      </c>
+      <c r="E880" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F880" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G880" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H880" s="3" t="inlineStr"/>
+    </row>
+    <row r="881" ht="20" customHeight="1">
+      <c r="A881" s="2" t="n">
+        <v>877</v>
+      </c>
+      <c r="B881" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C881" s="2" t="n">
+        <v>1116</v>
+      </c>
+      <c r="D881" s="2" t="inlineStr">
+        <is>
+          <t>284915</t>
+        </is>
+      </c>
+      <c r="E881" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F881" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G881" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H881" s="2" t="inlineStr"/>
+    </row>
+    <row r="882" ht="20" customHeight="1">
+      <c r="A882" s="3" t="n">
+        <v>878</v>
+      </c>
+      <c r="B882" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C882" s="3" t="n">
+        <v>1117</v>
+      </c>
+      <c r="D882" s="3" t="inlineStr">
+        <is>
+          <t>284917</t>
+        </is>
+      </c>
+      <c r="E882" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F882" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G882" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H882" s="3" t="inlineStr"/>
+    </row>
+    <row r="883" ht="20" customHeight="1">
+      <c r="A883" s="2" t="n">
+        <v>879</v>
+      </c>
+      <c r="B883" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C883" s="2" t="n">
+        <v>1118</v>
+      </c>
+      <c r="D883" s="2" t="inlineStr">
+        <is>
+          <t>284720</t>
+        </is>
+      </c>
+      <c r="E883" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F883" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G883" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H883" s="2" t="inlineStr"/>
+    </row>
+    <row r="884" ht="20" customHeight="1">
+      <c r="A884" s="3" t="n">
+        <v>880</v>
+      </c>
+      <c r="B884" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C884" s="3" t="n">
+        <v>1119</v>
+      </c>
+      <c r="D884" s="3" t="inlineStr">
+        <is>
+          <t>284719</t>
+        </is>
+      </c>
+      <c r="E884" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F884" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G884" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H884" s="3" t="inlineStr"/>
+    </row>
+    <row r="885" ht="20" customHeight="1">
+      <c r="A885" s="2" t="n">
+        <v>881</v>
+      </c>
+      <c r="B885" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C885" s="2" t="n">
+        <v>1120</v>
+      </c>
+      <c r="D885" s="2" t="inlineStr">
+        <is>
+          <t>284922</t>
+        </is>
+      </c>
+      <c r="E885" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F885" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G885" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H885" s="2" t="inlineStr"/>
+    </row>
+    <row r="886" ht="20" customHeight="1">
+      <c r="A886" s="3" t="n">
+        <v>882</v>
+      </c>
+      <c r="B886" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C886" s="3" t="n">
+        <v>1121</v>
+      </c>
+      <c r="D886" s="3" t="inlineStr">
+        <is>
+          <t>284823</t>
+        </is>
+      </c>
+      <c r="E886" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F886" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G886" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H886" s="3" t="inlineStr"/>
+    </row>
+    <row r="887" ht="20" customHeight="1">
+      <c r="A887" s="2" t="n">
+        <v>883</v>
+      </c>
+      <c r="B887" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C887" s="2" t="n">
+        <v>1122</v>
+      </c>
+      <c r="D887" s="2" t="inlineStr">
+        <is>
+          <t>280336</t>
+        </is>
+      </c>
+      <c r="E887" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F887" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G887" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H887" s="2" t="inlineStr"/>
+    </row>
+    <row r="888" ht="20" customHeight="1">
+      <c r="A888" s="3" t="n">
+        <v>884</v>
+      </c>
+      <c r="B888" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C888" s="3" t="n">
+        <v>1123</v>
+      </c>
+      <c r="D888" s="3" t="inlineStr">
+        <is>
+          <t>284822</t>
+        </is>
+      </c>
+      <c r="E888" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F888" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G888" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H888" s="3" t="inlineStr"/>
+    </row>
+    <row r="889" ht="20" customHeight="1">
+      <c r="A889" s="2" t="n">
+        <v>885</v>
+      </c>
+      <c r="B889" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C889" s="2" t="n">
+        <v>1124</v>
+      </c>
+      <c r="D889" s="2" t="inlineStr">
+        <is>
+          <t>284820</t>
+        </is>
+      </c>
+      <c r="E889" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F889" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G889" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H889" s="2" t="inlineStr"/>
+    </row>
+    <row r="890" ht="20" customHeight="1">
+      <c r="A890" s="3" t="n">
+        <v>886</v>
+      </c>
+      <c r="B890" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C890" s="3" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D890" s="3" t="inlineStr">
+        <is>
+          <t>284819</t>
+        </is>
+      </c>
+      <c r="E890" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F890" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G890" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H890" s="3" t="inlineStr"/>
+    </row>
+    <row r="891" ht="20" customHeight="1">
+      <c r="A891" s="2" t="n">
+        <v>887</v>
+      </c>
+      <c r="B891" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C891" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="D891" s="2" t="inlineStr">
+        <is>
+          <t>286479</t>
+        </is>
+      </c>
+      <c r="E891" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F891" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G891" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H891" s="2" t="inlineStr"/>
+    </row>
+    <row r="892" ht="20" customHeight="1">
+      <c r="A892" s="3" t="n">
+        <v>888</v>
+      </c>
+      <c r="B892" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C892" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="D892" s="3" t="inlineStr">
+        <is>
+          <t>284821</t>
+        </is>
+      </c>
+      <c r="E892" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F892" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G892" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H892" s="3" t="inlineStr"/>
+    </row>
+    <row r="893" ht="20" customHeight="1">
+      <c r="A893" s="2" t="n">
+        <v>889</v>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C893" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D893" s="2" t="inlineStr">
+        <is>
+          <t>284422</t>
+        </is>
+      </c>
+      <c r="E893" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F893" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G893" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H893" s="2" t="inlineStr"/>
+    </row>
+    <row r="894" ht="20" customHeight="1">
+      <c r="A894" s="3" t="n">
+        <v>890</v>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C894" s="3" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D894" s="3" t="inlineStr">
+        <is>
+          <t>286058</t>
+        </is>
+      </c>
+      <c r="E894" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F894" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G894" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H894" s="3" t="inlineStr"/>
+    </row>
+    <row r="895" ht="20" customHeight="1">
+      <c r="A895" s="2" t="n">
+        <v>891</v>
+      </c>
+      <c r="B895" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C895" s="2" t="n">
+        <v>1131</v>
+      </c>
+      <c r="D895" s="2" t="inlineStr">
+        <is>
+          <t>284833</t>
+        </is>
+      </c>
+      <c r="E895" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F895" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G895" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H895" s="2" t="inlineStr"/>
+    </row>
+    <row r="896" ht="20" customHeight="1">
+      <c r="A896" s="3" t="n">
+        <v>892</v>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C896" s="3" t="n">
+        <v>1132</v>
+      </c>
+      <c r="D896" s="3" t="inlineStr">
+        <is>
+          <t>284922</t>
+        </is>
+      </c>
+      <c r="E896" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F896" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G896" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H896" s="3" t="inlineStr"/>
+    </row>
+    <row r="897" ht="20" customHeight="1">
+      <c r="A897" s="2" t="n">
+        <v>893</v>
+      </c>
+      <c r="B897" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C897" s="2" t="n">
+        <v>1133</v>
+      </c>
+      <c r="D897" s="2" t="inlineStr">
+        <is>
+          <t>284921</t>
+        </is>
+      </c>
+      <c r="E897" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F897" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G897" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H897" s="2" t="inlineStr"/>
+    </row>
+    <row r="898" ht="20" customHeight="1">
+      <c r="A898" s="3" t="n">
+        <v>894</v>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C898" s="3" t="n">
+        <v>1134</v>
+      </c>
+      <c r="D898" s="3" t="inlineStr">
+        <is>
+          <t>284830</t>
+        </is>
+      </c>
+      <c r="E898" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F898" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G898" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H898" s="3" t="inlineStr"/>
+    </row>
+    <row r="899" ht="20" customHeight="1">
+      <c r="A899" s="2" t="n">
+        <v>895</v>
+      </c>
+      <c r="B899" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C899" s="2" t="n">
+        <v>1135</v>
+      </c>
+      <c r="D899" s="2" t="inlineStr">
+        <is>
+          <t>280338</t>
+        </is>
+      </c>
+      <c r="E899" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F899" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G899" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H899" s="2" t="inlineStr"/>
+    </row>
+    <row r="900" ht="20" customHeight="1">
+      <c r="A900" s="3" t="n">
+        <v>896</v>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C900" s="3" t="n">
+        <v>1136</v>
+      </c>
+      <c r="D900" s="3" t="inlineStr">
+        <is>
+          <t>282923</t>
+        </is>
+      </c>
+      <c r="E900" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F900" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G900" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H900" s="3" t="inlineStr"/>
+    </row>
+    <row r="901" ht="20" customHeight="1">
+      <c r="A901" s="2" t="n">
+        <v>897</v>
+      </c>
+      <c r="B901" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C901" s="2" t="n">
+        <v>1137</v>
+      </c>
+      <c r="D901" s="2" t="inlineStr">
+        <is>
+          <t>284831</t>
+        </is>
+      </c>
+      <c r="E901" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F901" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G901" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H901" s="2" t="inlineStr"/>
+    </row>
+    <row r="902" ht="20" customHeight="1">
+      <c r="A902" s="3" t="n">
+        <v>898</v>
+      </c>
+      <c r="B902" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C902" s="3" t="n">
+        <v>1138</v>
+      </c>
+      <c r="D902" s="3" t="inlineStr">
+        <is>
+          <t>284832</t>
+        </is>
+      </c>
+      <c r="E902" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F902" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G902" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H902" s="3" t="inlineStr"/>
+    </row>
+    <row r="903" ht="20" customHeight="1">
+      <c r="A903" s="2" t="n">
+        <v>899</v>
+      </c>
+      <c r="B903" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C903" s="2" t="n">
+        <v>1139</v>
+      </c>
+      <c r="D903" s="2" t="inlineStr">
+        <is>
+          <t>284427</t>
+        </is>
+      </c>
+      <c r="E903" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F903" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G903" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H903" s="2" t="inlineStr"/>
+    </row>
+    <row r="904" ht="20" customHeight="1">
+      <c r="A904" s="3" t="n">
+        <v>900</v>
+      </c>
+      <c r="B904" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C904" s="3" t="n">
+        <v>1140</v>
+      </c>
+      <c r="D904" s="3" t="inlineStr">
+        <is>
+          <t>280337</t>
+        </is>
+      </c>
+      <c r="E904" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F904" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G904" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H904" s="3" t="inlineStr"/>
+    </row>
+    <row r="905" ht="20" customHeight="1">
+      <c r="A905" s="2" t="n">
+        <v>901</v>
+      </c>
+      <c r="B905" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C905" s="2" t="n">
+        <v>1141</v>
+      </c>
+      <c r="D905" s="2" t="inlineStr">
+        <is>
+          <t>284426</t>
+        </is>
+      </c>
+      <c r="E905" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F905" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G905" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H905" s="2" t="inlineStr"/>
+    </row>
+    <row r="906" ht="20" customHeight="1">
+      <c r="A906" s="3" t="n">
+        <v>902</v>
+      </c>
+      <c r="B906" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C906" s="3" t="n">
+        <v>1142</v>
+      </c>
+      <c r="D906" s="3" t="inlineStr">
+        <is>
+          <t>284425</t>
+        </is>
+      </c>
+      <c r="E906" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F906" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G906" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H906" s="3" t="inlineStr"/>
+    </row>
+    <row r="907" ht="20" customHeight="1">
+      <c r="A907" s="2" t="n">
+        <v>903</v>
+      </c>
+      <c r="B907" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C907" s="2" t="n">
+        <v>1143</v>
+      </c>
+      <c r="D907" s="2" t="inlineStr">
+        <is>
+          <t>284829</t>
+        </is>
+      </c>
+      <c r="E907" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F907" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G907" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H907" s="2" t="inlineStr"/>
+    </row>
+    <row r="908" ht="20" customHeight="1">
+      <c r="A908" s="3" t="n">
+        <v>904</v>
+      </c>
+      <c r="B908" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C908" s="3" t="n">
+        <v>1144</v>
+      </c>
+      <c r="D908" s="3" t="inlineStr">
+        <is>
+          <t>284824</t>
+        </is>
+      </c>
+      <c r="E908" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F908" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G908" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H908" s="3" t="inlineStr"/>
+    </row>
+    <row r="909" ht="20" customHeight="1">
+      <c r="A909" s="2" t="n">
+        <v>905</v>
+      </c>
+      <c r="B909" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C909" s="2" t="n">
+        <v>1145</v>
+      </c>
+      <c r="D909" s="2" t="inlineStr">
+        <is>
+          <t>284825</t>
+        </is>
+      </c>
+      <c r="E909" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F909" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G909" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H909" s="2" t="inlineStr"/>
+    </row>
+    <row r="910" ht="20" customHeight="1">
+      <c r="A910" s="3" t="n">
+        <v>906</v>
+      </c>
+      <c r="B910" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C910" s="3" t="n">
+        <v>1146</v>
+      </c>
+      <c r="D910" s="3" t="inlineStr">
+        <is>
+          <t>284828</t>
+        </is>
+      </c>
+      <c r="E910" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F910" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G910" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H910" s="3" t="inlineStr"/>
+    </row>
+    <row r="911" ht="20" customHeight="1">
+      <c r="A911" s="2" t="n">
+        <v>907</v>
+      </c>
+      <c r="B911" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C911" s="2" t="n">
+        <v>1147</v>
+      </c>
+      <c r="D911" s="2" t="inlineStr">
+        <is>
+          <t>284826</t>
+        </is>
+      </c>
+      <c r="E911" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F911" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G911" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H911" s="2" t="inlineStr"/>
+    </row>
+    <row r="912" ht="20" customHeight="1">
+      <c r="A912" s="3" t="n">
+        <v>908</v>
+      </c>
+      <c r="B912" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C912" s="3" t="n">
+        <v>1148</v>
+      </c>
+      <c r="D912" s="3" t="inlineStr">
+        <is>
+          <t>284827</t>
+        </is>
+      </c>
+      <c r="E912" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F912" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G912" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H912" s="3" t="inlineStr"/>
+    </row>
+    <row r="913" ht="20" customHeight="1">
+      <c r="A913" s="2" t="n">
+        <v>909</v>
+      </c>
+      <c r="B913" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C913" s="2" t="n">
+        <v>1149</v>
+      </c>
+      <c r="D913" s="2" t="inlineStr">
+        <is>
+          <t>284446</t>
+        </is>
+      </c>
+      <c r="E913" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F913" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G913" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H913" s="2" t="inlineStr"/>
+    </row>
+    <row r="914" ht="20" customHeight="1">
+      <c r="A914" s="3" t="n">
+        <v>910</v>
+      </c>
+      <c r="B914" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C914" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="D914" s="3" t="inlineStr">
+        <is>
+          <t>284424</t>
+        </is>
+      </c>
+      <c r="E914" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F914" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G914" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H914" s="3" t="inlineStr"/>
+    </row>
+    <row r="915" ht="20" customHeight="1">
+      <c r="A915" s="2" t="n">
+        <v>911</v>
+      </c>
+      <c r="B915" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C915" s="2" t="n">
+        <v>1151</v>
+      </c>
+      <c r="D915" s="2" t="inlineStr">
+        <is>
+          <t>284423</t>
+        </is>
+      </c>
+      <c r="E915" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F915" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G915" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H915" s="2" t="inlineStr"/>
+    </row>
+    <row r="916" ht="20" customHeight="1">
+      <c r="A916" s="3" t="n">
+        <v>912</v>
+      </c>
+      <c r="B916" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C916" s="3" t="n">
+        <v>1153</v>
+      </c>
+      <c r="D916" s="3" t="inlineStr">
+        <is>
+          <t>284722</t>
+        </is>
+      </c>
+      <c r="E916" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F916" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G916" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H916" s="3" t="inlineStr"/>
+    </row>
+    <row r="917" ht="20" customHeight="1">
+      <c r="A917" s="2" t="n">
+        <v>913</v>
+      </c>
+      <c r="B917" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="C917" s="2" t="n">
+        <v>1154</v>
+      </c>
+      <c r="D917" s="2" t="inlineStr">
+        <is>
+          <t>284284</t>
+        </is>
+      </c>
+      <c r="E917" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F917" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G917" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H917" s="2" t="inlineStr"/>
+    </row>
+    <row r="918" ht="20" customHeight="1">
+      <c r="A918" s="3" t="n">
+        <v>914</v>
+      </c>
+      <c r="B918" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C918" s="3" t="n">
+        <v>1155</v>
+      </c>
+      <c r="D918" s="3" t="inlineStr">
+        <is>
+          <t>286190</t>
+        </is>
+      </c>
+      <c r="E918" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F918" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G918" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H918" s="3" t="inlineStr"/>
+    </row>
+    <row r="919" ht="20" customHeight="1">
+      <c r="A919" s="2" t="n">
+        <v>915</v>
+      </c>
+      <c r="B919" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C919" s="2" t="n">
+        <v>1156</v>
+      </c>
+      <c r="D919" s="2" t="inlineStr">
+        <is>
+          <t>374040</t>
+        </is>
+      </c>
+      <c r="E919" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F919" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G919" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H919" s="2" t="inlineStr"/>
+    </row>
+    <row r="920" ht="20" customHeight="1">
+      <c r="A920" s="3" t="n">
+        <v>916</v>
+      </c>
+      <c r="B920" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C920" s="3" t="n">
+        <v>1157</v>
+      </c>
+      <c r="D920" s="3" t="inlineStr">
+        <is>
+          <t>286368</t>
+        </is>
+      </c>
+      <c r="E920" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F920" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G920" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H920" s="3" t="inlineStr"/>
+    </row>
+    <row r="921" ht="20" customHeight="1">
+      <c r="A921" s="2" t="n">
+        <v>917</v>
+      </c>
+      <c r="B921" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C921" s="2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="D921" s="2" t="inlineStr">
+        <is>
+          <t>286193</t>
+        </is>
+      </c>
+      <c r="E921" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F921" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G921" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H921" s="2" t="inlineStr"/>
+    </row>
+    <row r="922" ht="20" customHeight="1">
+      <c r="A922" s="3" t="n">
+        <v>918</v>
+      </c>
+      <c r="B922" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C922" s="3" t="n">
+        <v>1159</v>
+      </c>
+      <c r="D922" s="3" t="inlineStr">
+        <is>
+          <t>286192</t>
+        </is>
+      </c>
+      <c r="E922" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F922" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="G922" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H922" s="3" t="inlineStr"/>
+    </row>
+    <row r="923" ht="20" customHeight="1">
+      <c r="A923" s="2" t="n">
+        <v>919</v>
+      </c>
+      <c r="B923" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C923" s="2" t="n">
+        <v>1160</v>
+      </c>
+      <c r="D923" s="2" t="inlineStr">
+        <is>
+          <t>286194</t>
+        </is>
+      </c>
+      <c r="E923" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F923" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G923" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H923" s="2" t="inlineStr"/>
+    </row>
+    <row r="924" ht="20" customHeight="1">
+      <c r="A924" s="3" t="n">
+        <v>920</v>
+      </c>
+      <c r="B924" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C924" s="3" t="n">
+        <v>1161</v>
+      </c>
+      <c r="D924" s="3" t="inlineStr">
+        <is>
+          <t>286195</t>
+        </is>
+      </c>
+      <c r="E924" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F924" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G924" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H924" s="3" t="inlineStr"/>
+    </row>
+    <row r="925" ht="20" customHeight="1">
+      <c r="A925" s="2" t="n">
+        <v>921</v>
+      </c>
+      <c r="B925" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C925" s="2" t="n">
+        <v>1162</v>
+      </c>
+      <c r="D925" s="2" t="inlineStr">
+        <is>
+          <t>286367</t>
+        </is>
+      </c>
+      <c r="E925" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F925" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G925" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H925" s="2" t="inlineStr"/>
+    </row>
+    <row r="926" ht="20" customHeight="1">
+      <c r="A926" s="3" t="n">
+        <v>922</v>
+      </c>
+      <c r="B926" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C926" s="3" t="n">
+        <v>1163</v>
+      </c>
+      <c r="D926" s="3" t="inlineStr">
+        <is>
+          <t>286369</t>
+        </is>
+      </c>
+      <c r="E926" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F926" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G926" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H926" s="3" t="inlineStr"/>
+    </row>
+    <row r="927" ht="20" customHeight="1">
+      <c r="A927" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="B927" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C927" s="2" t="n">
+        <v>1164</v>
+      </c>
+      <c r="D927" s="2" t="inlineStr">
+        <is>
+          <t>286477</t>
+        </is>
+      </c>
+      <c r="E927" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F927" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G927" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H927" s="2" t="inlineStr"/>
+    </row>
+    <row r="928" ht="20" customHeight="1">
+      <c r="A928" s="3" t="n">
+        <v>924</v>
+      </c>
+      <c r="B928" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C928" s="3" t="n">
+        <v>1165</v>
+      </c>
+      <c r="D928" s="3" t="inlineStr">
+        <is>
+          <t>286191</t>
+        </is>
+      </c>
+      <c r="E928" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F928" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G928" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H928" s="3" t="inlineStr"/>
+    </row>
+    <row r="929" ht="20" customHeight="1">
+      <c r="A929" s="2" t="n">
+        <v>925</v>
+      </c>
+      <c r="B929" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C929" s="2" t="n">
+        <v>1166</v>
+      </c>
+      <c r="D929" s="2" t="inlineStr">
+        <is>
+          <t>284798</t>
+        </is>
+      </c>
+      <c r="E929" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F929" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G929" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H929" s="2" t="inlineStr"/>
+    </row>
+    <row r="930" ht="20" customHeight="1">
+      <c r="A930" s="3" t="n">
+        <v>926</v>
+      </c>
+      <c r="B930" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C930" s="3" t="n">
+        <v>1167</v>
+      </c>
+      <c r="D930" s="3" t="inlineStr">
+        <is>
+          <t>284799</t>
+        </is>
+      </c>
+      <c r="E930" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F930" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G930" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H930" s="3" t="inlineStr"/>
+    </row>
+    <row r="931" ht="20" customHeight="1">
+      <c r="A931" s="2" t="n">
+        <v>927</v>
+      </c>
+      <c r="B931" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C931" s="2" t="n">
+        <v>1168</v>
+      </c>
+      <c r="D931" s="2" t="inlineStr">
+        <is>
+          <t>286371</t>
+        </is>
+      </c>
+      <c r="E931" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F931" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G931" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H931" s="2" t="inlineStr"/>
+    </row>
+    <row r="932" ht="20" customHeight="1">
+      <c r="A932" s="3" t="n">
+        <v>928</v>
+      </c>
+      <c r="B932" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C932" s="3" t="n">
+        <v>1169</v>
+      </c>
+      <c r="D932" s="3" t="inlineStr">
+        <is>
+          <t>286402</t>
+        </is>
+      </c>
+      <c r="E932" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F932" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G932" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H932" s="3" t="inlineStr"/>
+    </row>
+    <row r="933" ht="20" customHeight="1">
+      <c r="A933" s="2" t="n">
+        <v>929</v>
+      </c>
+      <c r="B933" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C933" s="2" t="n">
+        <v>1170</v>
+      </c>
+      <c r="D933" s="2" t="inlineStr">
+        <is>
+          <t>286476</t>
+        </is>
+      </c>
+      <c r="E933" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F933" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G933" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H933" s="2" t="inlineStr"/>
+    </row>
+    <row r="934" ht="20" customHeight="1">
+      <c r="A934" s="3" t="n">
+        <v>930</v>
+      </c>
+      <c r="B934" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C934" s="3" t="n">
+        <v>1172</v>
+      </c>
+      <c r="D934" s="3" t="inlineStr">
+        <is>
+          <t>374250</t>
+        </is>
+      </c>
+      <c r="E934" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F934" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G934" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H934" s="3" t="inlineStr"/>
+    </row>
+    <row r="935" ht="20" customHeight="1">
+      <c r="A935" s="2" t="n">
+        <v>931</v>
+      </c>
+      <c r="B935" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C935" s="2" t="n">
+        <v>1173</v>
+      </c>
+      <c r="D935" s="2" t="inlineStr">
+        <is>
+          <t>374038</t>
+        </is>
+      </c>
+      <c r="E935" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F935" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G935" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H935" s="2" t="inlineStr"/>
+    </row>
+    <row r="936" ht="20" customHeight="1">
+      <c r="A936" s="3" t="n">
+        <v>932</v>
+      </c>
+      <c r="B936" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C936" s="3" t="n">
+        <v>1174</v>
+      </c>
+      <c r="D936" s="3" t="inlineStr">
+        <is>
+          <t>286199</t>
+        </is>
+      </c>
+      <c r="E936" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F936" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G936" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H936" s="3" t="inlineStr"/>
+    </row>
+    <row r="937" ht="20" customHeight="1">
+      <c r="A937" s="2" t="n">
+        <v>933</v>
+      </c>
+      <c r="B937" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C937" s="2" t="n">
+        <v>1176</v>
+      </c>
+      <c r="D937" s="2" t="inlineStr">
+        <is>
+          <t>286374</t>
+        </is>
+      </c>
+      <c r="E937" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F937" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G937" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H937" s="2" t="inlineStr"/>
+    </row>
+    <row r="938" ht="20" customHeight="1">
+      <c r="A938" s="3" t="n">
+        <v>934</v>
+      </c>
+      <c r="B938" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C938" s="3" t="n">
+        <v>1177</v>
+      </c>
+      <c r="D938" s="3" t="inlineStr">
+        <is>
+          <t>286376</t>
+        </is>
+      </c>
+      <c r="E938" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F938" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G938" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H938" s="3" t="inlineStr"/>
+    </row>
+    <row r="939" ht="20" customHeight="1">
+      <c r="A939" s="2" t="n">
+        <v>935</v>
+      </c>
+      <c r="B939" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C939" s="2" t="n">
+        <v>1179</v>
+      </c>
+      <c r="D939" s="2" t="inlineStr">
+        <is>
+          <t>286196</t>
+        </is>
+      </c>
+      <c r="E939" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F939" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G939" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H939" s="2" t="inlineStr"/>
+    </row>
+    <row r="940" ht="20" customHeight="1">
+      <c r="A940" s="3" t="n">
+        <v>936</v>
+      </c>
+      <c r="B940" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C940" s="3" t="n">
+        <v>1180</v>
+      </c>
+      <c r="D940" s="3" t="inlineStr">
+        <is>
+          <t>284795</t>
+        </is>
+      </c>
+      <c r="E940" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F940" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G940" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H940" s="3" t="inlineStr"/>
+    </row>
+    <row r="941" ht="20" customHeight="1">
+      <c r="A941" s="2" t="n">
+        <v>937</v>
+      </c>
+      <c r="B941" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C941" s="2" t="n">
+        <v>1181</v>
+      </c>
+      <c r="D941" s="2" t="inlineStr">
+        <is>
+          <t>374039</t>
+        </is>
+      </c>
+      <c r="E941" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F941" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G941" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H941" s="2" t="inlineStr"/>
+    </row>
+    <row r="942" ht="20" customHeight="1">
+      <c r="A942" s="3" t="n">
+        <v>938</v>
+      </c>
+      <c r="B942" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C942" s="3" t="n">
+        <v>1182</v>
+      </c>
+      <c r="D942" s="3" t="inlineStr">
+        <is>
+          <t>286189</t>
+        </is>
+      </c>
+      <c r="E942" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F942" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G942" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H942" s="3" t="inlineStr"/>
+    </row>
+    <row r="943" ht="20" customHeight="1">
+      <c r="A943" s="2" t="n">
+        <v>939</v>
+      </c>
+      <c r="B943" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C943" s="2" t="n">
+        <v>1183</v>
+      </c>
+      <c r="D943" s="2" t="inlineStr">
+        <is>
+          <t>374041</t>
+        </is>
+      </c>
+      <c r="E943" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F943" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G943" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H943" s="2" t="inlineStr"/>
+    </row>
+    <row r="944" ht="20" customHeight="1">
+      <c r="A944" s="3" t="n">
+        <v>940</v>
+      </c>
+      <c r="B944" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C944" s="3" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D944" s="3" t="inlineStr">
+        <is>
+          <t>286375</t>
+        </is>
+      </c>
+      <c r="E944" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F944" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G944" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H944" s="3" t="inlineStr"/>
+    </row>
+    <row r="945" ht="20" customHeight="1">
+      <c r="A945" s="2" t="n">
+        <v>941</v>
+      </c>
+      <c r="B945" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C945" s="2" t="n">
+        <v>1186</v>
+      </c>
+      <c r="D945" s="2" t="inlineStr">
+        <is>
+          <t>286373</t>
+        </is>
+      </c>
+      <c r="E945" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F945" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G945" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H945" s="2" t="inlineStr"/>
+    </row>
+    <row r="946" ht="20" customHeight="1">
+      <c r="A946" s="3" t="n">
+        <v>942</v>
+      </c>
+      <c r="B946" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C946" s="3" t="n">
+        <v>1190</v>
+      </c>
+      <c r="D946" s="3" t="inlineStr">
+        <is>
+          <t>286057</t>
+        </is>
+      </c>
+      <c r="E946" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F946" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G946" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H946" s="3" t="inlineStr"/>
+    </row>
+    <row r="947" ht="20" customHeight="1">
+      <c r="A947" s="2" t="n">
+        <v>943</v>
+      </c>
+      <c r="B947" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C947" s="2" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D947" s="2" t="inlineStr">
+        <is>
+          <t>282939</t>
+        </is>
+      </c>
+      <c r="E947" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F947" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G947" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H947" s="2" t="inlineStr"/>
+    </row>
+    <row r="948" ht="20" customHeight="1">
+      <c r="A948" s="3" t="n">
+        <v>944</v>
+      </c>
+      <c r="B948" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C948" s="3" t="n">
+        <v>1194</v>
+      </c>
+      <c r="D948" s="3" t="inlineStr">
+        <is>
+          <t>284796</t>
+        </is>
+      </c>
+      <c r="E948" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F948" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G948" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H948" s="3" t="inlineStr"/>
+    </row>
+    <row r="949" ht="20" customHeight="1">
+      <c r="A949" s="2" t="n">
+        <v>945</v>
+      </c>
+      <c r="B949" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C949" s="2" t="n">
+        <v>1196</v>
+      </c>
+      <c r="D949" s="2" t="inlineStr">
+        <is>
+          <t>286370</t>
+        </is>
+      </c>
+      <c r="E949" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F949" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G949" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H949" s="2" t="inlineStr"/>
+    </row>
+    <row r="950" ht="20" customHeight="1">
+      <c r="A950" s="3" t="n">
+        <v>946</v>
+      </c>
+      <c r="B950" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C950" s="3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="D950" s="3" t="inlineStr">
+        <is>
+          <t>286372</t>
+        </is>
+      </c>
+      <c r="E950" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F950" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G950" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H950" s="3" t="inlineStr"/>
+    </row>
+    <row r="951" ht="20" customHeight="1">
+      <c r="A951" s="2" t="n">
+        <v>947</v>
+      </c>
+      <c r="B951" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C951" s="2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D951" s="2" t="inlineStr">
+        <is>
+          <t>284797</t>
+        </is>
+      </c>
+      <c r="E951" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F951" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G951" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H951" s="2" t="inlineStr"/>
+    </row>
+    <row r="952" ht="20" customHeight="1">
+      <c r="A952" s="3" t="n">
+        <v>948</v>
+      </c>
+      <c r="B952" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C952" s="3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D952" s="3" t="inlineStr">
+        <is>
+          <t>284800</t>
+        </is>
+      </c>
+      <c r="E952" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F952" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G952" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H952" s="3" t="inlineStr"/>
+    </row>
+    <row r="953" ht="20" customHeight="1">
+      <c r="A953" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="B953" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C953" s="2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D953" s="2" t="inlineStr">
+        <is>
+          <t>284445</t>
+        </is>
+      </c>
+      <c r="E953" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F953" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G953" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H953" s="2" t="inlineStr"/>
+    </row>
+    <row r="954" ht="20" customHeight="1">
+      <c r="A954" s="3" t="n">
+        <v>950</v>
+      </c>
+      <c r="B954" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C954" s="3" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D954" s="3" t="inlineStr">
+        <is>
+          <t>286197</t>
+        </is>
+      </c>
+      <c r="E954" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F954" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G954" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H954" s="3" t="inlineStr"/>
+    </row>
+    <row r="955" ht="20" customHeight="1">
+      <c r="A955" s="2" t="n">
+        <v>951</v>
+      </c>
+      <c r="B955" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C955" s="2" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D955" s="2" t="inlineStr">
+        <is>
+          <t>286401</t>
+        </is>
+      </c>
+      <c r="E955" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F955" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G955" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H955" s="2" t="inlineStr"/>
+    </row>
+    <row r="956" ht="20" customHeight="1">
+      <c r="A956" s="3" t="n">
+        <v>952</v>
+      </c>
+      <c r="B956" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C956" s="3" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D956" s="3" t="inlineStr">
+        <is>
+          <t>284448</t>
+        </is>
+      </c>
+      <c r="E956" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F956" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G956" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H956" s="3" t="inlineStr"/>
+    </row>
+    <row r="957" ht="20" customHeight="1">
+      <c r="A957" s="2" t="n">
+        <v>953</v>
+      </c>
+      <c r="B957" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C957" s="2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D957" s="2" t="inlineStr">
+        <is>
+          <t>286198</t>
+        </is>
+      </c>
+      <c r="E957" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F957" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G957" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H957" s="2" t="inlineStr"/>
+    </row>
+    <row r="958" ht="20" customHeight="1">
+      <c r="A958" s="3" t="n">
+        <v>954</v>
+      </c>
+      <c r="B958" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C958" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="D958" s="3" t="inlineStr">
+        <is>
+          <t>284447</t>
+        </is>
+      </c>
+      <c r="E958" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F958" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G958" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H958" s="3" t="inlineStr"/>
+    </row>
+    <row r="959" ht="20" customHeight="1">
+      <c r="A959" s="2" t="n">
+        <v>955</v>
+      </c>
+      <c r="B959" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C959" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="D959" s="2" t="inlineStr">
+        <is>
+          <t>286059</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F959" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G959" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H959" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -41662,6 +45441,3381 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G75"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>284912</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1048</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>284626</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1049</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>284906</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>284908</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1051</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>284721</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>284627</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1053</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>284628</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1054</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>284911</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1055</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>284909</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1056</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>284910</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1057</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>284914</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1058</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>284913</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>284717</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1060</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>284718</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1093</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>284907</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1094</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>284637</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1095</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>284282</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1096</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>284715</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1097</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>284716</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1098</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>284283</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1099</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>284904</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1100</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>284905</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1101</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>284901</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1102</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>284902</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1103</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>284903</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1104</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>284636</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1105</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>284919</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1106</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>284635</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1107</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>284634</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1108</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>284920</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1109</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>284629</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1110</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>284633</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1111</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>284632</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1112</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>284630</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>284631</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1114</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>284918</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1115</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>284916</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1116</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>284915</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1117</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>284917</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1118</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>284720</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1119</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>284719</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1120</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>284922</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1121</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>284823</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1122</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>280336</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1123</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>284822</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1124</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>284820</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1125</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>284819</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1127</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>284821</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1128</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>284422</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1131</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>284833</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1132</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>284922</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1133</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>284921</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1134</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>284830</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1135</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>280338</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1136</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>282923</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1137</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>284831</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1138</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>284832</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1139</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>284427</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1140</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>280337</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1141</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>284426</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1142</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>284425</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1143</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>284829</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1144</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>284824</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1145</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>284825</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>1146</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>284828</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1147</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>284826</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1148</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>284827</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1150</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>284424</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>1151</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>284423</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>1153</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>284722</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>1154</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>284284</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G41"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1130</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>286058</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1149</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>284446</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1155</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>286190</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1157</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>286368</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1158</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>286193</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1159</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>286192</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1160</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>286194</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1161</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>286195</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1162</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>286367</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1163</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>286369</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1165</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>286191</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1166</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>284798</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1167</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>284799</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1168</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>286371</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1169</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>286402</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1174</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>286199</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1176</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>286374</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1177</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>286376</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1179</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>286196</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1180</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>284795</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1182</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>286189</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1185</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>286375</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1186</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>286373</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1190</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>286057</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1191</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>282939</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1194</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>284796</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1196</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>286370</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1198</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>286372</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1201</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>284797</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1202</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>284800</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1203</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>284445</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1205</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>286197</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1206</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>286401</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1209</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>284448</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1211</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>286198</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1212</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>284447</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1215</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>286059</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1072</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>374138</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1075</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>374137</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1126</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>286479</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1156</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>374040</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1164</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>286477</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1170</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>286476</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1172</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>374250</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1173</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>374038</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1181</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>374039</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1183</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>374041</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
+++ b/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
@@ -35,6 +35,7 @@
     <sheet name="17 September" sheetId="26" state="visible" r:id="rId26"/>
     <sheet name="18 September" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="19 September" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="20 September" sheetId="29" state="visible" r:id="rId29"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +484,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H959"/>
+  <dimension ref="A1:H975"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -30295,24 +30296,24 @@
       </c>
       <c r="B944" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C944" s="3" t="n">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D944" s="3" t="inlineStr">
         <is>
-          <t>286375</t>
+          <t>374136</t>
         </is>
       </c>
       <c r="E944" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F944" s="3" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G944" s="3" t="inlineStr">
         <is>
@@ -30331,20 +30332,20 @@
         </is>
       </c>
       <c r="C945" s="2" t="n">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="D945" s="2" t="inlineStr">
         <is>
-          <t>286373</t>
+          <t>286375</t>
         </is>
       </c>
       <c r="E945" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F945" s="2" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G945" s="2" t="inlineStr">
         <is>
@@ -30363,20 +30364,20 @@
         </is>
       </c>
       <c r="C946" s="3" t="n">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D946" s="3" t="inlineStr">
         <is>
-          <t>286057</t>
+          <t>286373</t>
         </is>
       </c>
       <c r="E946" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F946" s="3" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G946" s="3" t="inlineStr">
         <is>
@@ -30391,15 +30392,15 @@
       </c>
       <c r="B947" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C947" s="2" t="n">
-        <v>1191</v>
+        <v>1189</v>
       </c>
       <c r="D947" s="2" t="inlineStr">
         <is>
-          <t>282939</t>
+          <t>374140</t>
         </is>
       </c>
       <c r="E947" s="2" t="inlineStr">
@@ -30408,7 +30409,7 @@
         </is>
       </c>
       <c r="F947" s="2" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G947" s="2" t="inlineStr">
         <is>
@@ -30427,20 +30428,20 @@
         </is>
       </c>
       <c r="C948" s="3" t="n">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="D948" s="3" t="inlineStr">
         <is>
-          <t>284796</t>
+          <t>286057</t>
         </is>
       </c>
       <c r="E948" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F948" s="3" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G948" s="3" t="inlineStr">
         <is>
@@ -30459,20 +30460,20 @@
         </is>
       </c>
       <c r="C949" s="2" t="n">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>286370</t>
+          <t>282939</t>
         </is>
       </c>
       <c r="E949" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F949" s="2" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G949" s="2" t="inlineStr">
         <is>
@@ -30487,24 +30488,24 @@
       </c>
       <c r="B950" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C950" s="3" t="n">
-        <v>1198</v>
+        <v>1192</v>
       </c>
       <c r="D950" s="3" t="inlineStr">
         <is>
-          <t>286372</t>
+          <t>374141</t>
         </is>
       </c>
       <c r="E950" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F950" s="3" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G950" s="3" t="inlineStr">
         <is>
@@ -30519,24 +30520,24 @@
       </c>
       <c r="B951" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C951" s="2" t="n">
-        <v>1201</v>
+        <v>1193</v>
       </c>
       <c r="D951" s="2" t="inlineStr">
         <is>
-          <t>284797</t>
+          <t>374310</t>
         </is>
       </c>
       <c r="E951" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F951" s="2" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="G951" s="2" t="inlineStr">
         <is>
@@ -30555,20 +30556,20 @@
         </is>
       </c>
       <c r="C952" s="3" t="n">
-        <v>1202</v>
+        <v>1194</v>
       </c>
       <c r="D952" s="3" t="inlineStr">
         <is>
-          <t>284800</t>
+          <t>284796</t>
         </is>
       </c>
       <c r="E952" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F952" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G952" s="3" t="inlineStr">
         <is>
@@ -30583,15 +30584,15 @@
       </c>
       <c r="B953" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C953" s="2" t="n">
-        <v>1203</v>
+        <v>1195</v>
       </c>
       <c r="D953" s="2" t="inlineStr">
         <is>
-          <t>284445</t>
+          <t>286478</t>
         </is>
       </c>
       <c r="E953" s="2" t="inlineStr">
@@ -30600,7 +30601,7 @@
         </is>
       </c>
       <c r="F953" s="2" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G953" s="2" t="inlineStr">
         <is>
@@ -30619,11 +30620,11 @@
         </is>
       </c>
       <c r="C954" s="3" t="n">
-        <v>1205</v>
+        <v>1196</v>
       </c>
       <c r="D954" s="3" t="inlineStr">
         <is>
-          <t>286197</t>
+          <t>286370</t>
         </is>
       </c>
       <c r="E954" s="3" t="inlineStr">
@@ -30632,7 +30633,7 @@
         </is>
       </c>
       <c r="F954" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G954" s="3" t="inlineStr">
         <is>
@@ -30647,20 +30648,20 @@
       </c>
       <c r="B955" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C955" s="2" t="n">
-        <v>1206</v>
+        <v>1197</v>
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>286401</t>
+          <t>125880</t>
         </is>
       </c>
       <c r="E955" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F955" s="2" t="n">
@@ -30683,20 +30684,20 @@
         </is>
       </c>
       <c r="C956" s="3" t="n">
-        <v>1209</v>
+        <v>1198</v>
       </c>
       <c r="D956" s="3" t="inlineStr">
         <is>
-          <t>284448</t>
+          <t>286372</t>
         </is>
       </c>
       <c r="E956" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F956" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G956" s="3" t="inlineStr">
         <is>
@@ -30711,24 +30712,24 @@
       </c>
       <c r="B957" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C957" s="2" t="n">
-        <v>1211</v>
+        <v>1199</v>
       </c>
       <c r="D957" s="2" t="inlineStr">
         <is>
-          <t>286198</t>
+          <t>374249</t>
         </is>
       </c>
       <c r="E957" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F957" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G957" s="2" t="inlineStr">
         <is>
@@ -30747,20 +30748,20 @@
         </is>
       </c>
       <c r="C958" s="3" t="n">
-        <v>1212</v>
+        <v>1201</v>
       </c>
       <c r="D958" s="3" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>284797</t>
         </is>
       </c>
       <c r="E958" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F958" s="3" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="G958" s="3" t="inlineStr">
         <is>
@@ -30779,27 +30780,539 @@
         </is>
       </c>
       <c r="C959" s="2" t="n">
+        <v>1202</v>
+      </c>
+      <c r="D959" s="2" t="inlineStr">
+        <is>
+          <t>284800</t>
+        </is>
+      </c>
+      <c r="E959" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F959" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G959" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H959" s="2" t="inlineStr"/>
+    </row>
+    <row r="960" ht="20" customHeight="1">
+      <c r="A960" s="3" t="n">
+        <v>956</v>
+      </c>
+      <c r="B960" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C960" s="3" t="n">
+        <v>1203</v>
+      </c>
+      <c r="D960" s="3" t="inlineStr">
+        <is>
+          <t>284445</t>
+        </is>
+      </c>
+      <c r="E960" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F960" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G960" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H960" s="3" t="inlineStr"/>
+    </row>
+    <row r="961" ht="20" customHeight="1">
+      <c r="A961" s="2" t="n">
+        <v>957</v>
+      </c>
+      <c r="B961" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C961" s="2" t="n">
+        <v>1205</v>
+      </c>
+      <c r="D961" s="2" t="inlineStr">
+        <is>
+          <t>286197</t>
+        </is>
+      </c>
+      <c r="E961" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F961" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G961" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H961" s="2" t="inlineStr"/>
+    </row>
+    <row r="962" ht="20" customHeight="1">
+      <c r="A962" s="3" t="n">
+        <v>958</v>
+      </c>
+      <c r="B962" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C962" s="3" t="n">
+        <v>1206</v>
+      </c>
+      <c r="D962" s="3" t="inlineStr">
+        <is>
+          <t>286401</t>
+        </is>
+      </c>
+      <c r="E962" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F962" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G962" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H962" s="3" t="inlineStr"/>
+    </row>
+    <row r="963" ht="20" customHeight="1">
+      <c r="A963" s="2" t="n">
+        <v>959</v>
+      </c>
+      <c r="B963" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C963" s="2" t="n">
+        <v>1207</v>
+      </c>
+      <c r="D963" s="2" t="inlineStr">
+        <is>
+          <t>125879</t>
+        </is>
+      </c>
+      <c r="E963" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F963" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G963" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H963" s="2" t="inlineStr"/>
+    </row>
+    <row r="964" ht="20" customHeight="1">
+      <c r="A964" s="3" t="n">
+        <v>960</v>
+      </c>
+      <c r="B964" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C964" s="3" t="n">
+        <v>1208</v>
+      </c>
+      <c r="D964" s="3" t="inlineStr">
+        <is>
+          <t>374179</t>
+        </is>
+      </c>
+      <c r="E964" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F964" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G964" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H964" s="3" t="inlineStr"/>
+    </row>
+    <row r="965" ht="20" customHeight="1">
+      <c r="A965" s="2" t="n">
+        <v>961</v>
+      </c>
+      <c r="B965" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C965" s="2" t="n">
+        <v>1209</v>
+      </c>
+      <c r="D965" s="2" t="inlineStr">
+        <is>
+          <t>284448</t>
+        </is>
+      </c>
+      <c r="E965" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F965" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G965" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H965" s="2" t="inlineStr"/>
+    </row>
+    <row r="966" ht="20" customHeight="1">
+      <c r="A966" s="3" t="n">
+        <v>962</v>
+      </c>
+      <c r="B966" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C966" s="3" t="n">
+        <v>1211</v>
+      </c>
+      <c r="D966" s="3" t="inlineStr">
+        <is>
+          <t>286198</t>
+        </is>
+      </c>
+      <c r="E966" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F966" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G966" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H966" s="3" t="inlineStr"/>
+    </row>
+    <row r="967" ht="20" customHeight="1">
+      <c r="A967" s="2" t="n">
+        <v>963</v>
+      </c>
+      <c r="B967" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C967" s="2" t="n">
+        <v>1212</v>
+      </c>
+      <c r="D967" s="2" t="inlineStr">
+        <is>
+          <t>284447</t>
+        </is>
+      </c>
+      <c r="E967" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F967" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G967" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H967" s="2" t="inlineStr"/>
+    </row>
+    <row r="968" ht="20" customHeight="1">
+      <c r="A968" s="3" t="n">
+        <v>964</v>
+      </c>
+      <c r="B968" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C968" s="3" t="n">
+        <v>1213</v>
+      </c>
+      <c r="D968" s="3" t="inlineStr">
+        <is>
+          <t>374143</t>
+        </is>
+      </c>
+      <c r="E968" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F968" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G968" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H968" s="3" t="inlineStr"/>
+    </row>
+    <row r="969" ht="20" customHeight="1">
+      <c r="A969" s="2" t="n">
+        <v>965</v>
+      </c>
+      <c r="B969" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C969" s="2" t="n">
         <v>1215</v>
       </c>
-      <c r="D959" s="2" t="inlineStr">
+      <c r="D969" s="2" t="inlineStr">
         <is>
           <t>286059</t>
         </is>
       </c>
-      <c r="E959" s="2" t="inlineStr">
+      <c r="E969" s="2" t="inlineStr">
         <is>
           <t>68</t>
         </is>
       </c>
-      <c r="F959" s="2" t="n">
+      <c r="F969" s="2" t="n">
         <v>45</v>
       </c>
-      <c r="G959" s="2" t="inlineStr">
-        <is>
-          <t>SELESAI</t>
-        </is>
-      </c>
-      <c r="H959" s="2" t="inlineStr"/>
+      <c r="G969" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H969" s="2" t="inlineStr"/>
+    </row>
+    <row r="970" ht="20" customHeight="1">
+      <c r="A970" s="3" t="n">
+        <v>966</v>
+      </c>
+      <c r="B970" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C970" s="3" t="n">
+        <v>1216</v>
+      </c>
+      <c r="D970" s="3" t="inlineStr">
+        <is>
+          <t>374142</t>
+        </is>
+      </c>
+      <c r="E970" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F970" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G970" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H970" s="3" t="inlineStr"/>
+    </row>
+    <row r="971" ht="20" customHeight="1">
+      <c r="A971" s="2" t="n">
+        <v>967</v>
+      </c>
+      <c r="B971" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C971" s="2" t="n">
+        <v>1217</v>
+      </c>
+      <c r="D971" s="2" t="inlineStr">
+        <is>
+          <t>286475</t>
+        </is>
+      </c>
+      <c r="E971" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F971" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G971" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H971" s="2" t="inlineStr"/>
+    </row>
+    <row r="972" ht="20" customHeight="1">
+      <c r="A972" s="3" t="n">
+        <v>968</v>
+      </c>
+      <c r="B972" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C972" s="3" t="n">
+        <v>1223</v>
+      </c>
+      <c r="D972" s="3" t="inlineStr">
+        <is>
+          <t>374253</t>
+        </is>
+      </c>
+      <c r="E972" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F972" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G972" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H972" s="3" t="inlineStr"/>
+    </row>
+    <row r="973" ht="20" customHeight="1">
+      <c r="A973" s="2" t="n">
+        <v>969</v>
+      </c>
+      <c r="B973" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C973" s="2" t="n">
+        <v>1224</v>
+      </c>
+      <c r="D973" s="2" t="inlineStr">
+        <is>
+          <t>374251</t>
+        </is>
+      </c>
+      <c r="E973" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F973" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G973" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H973" s="2" t="inlineStr"/>
+    </row>
+    <row r="974" ht="20" customHeight="1">
+      <c r="A974" s="3" t="n">
+        <v>970</v>
+      </c>
+      <c r="B974" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C974" s="3" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D974" s="3" t="inlineStr">
+        <is>
+          <t>374252</t>
+        </is>
+      </c>
+      <c r="E974" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F974" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G974" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H974" s="3" t="inlineStr"/>
+    </row>
+    <row r="975" ht="20" customHeight="1">
+      <c r="A975" s="2" t="n">
+        <v>971</v>
+      </c>
+      <c r="B975" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C975" s="2" t="n">
+        <v>1261</v>
+      </c>
+      <c r="D975" s="2" t="inlineStr">
+        <is>
+          <t>374666</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F975" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G975" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H975" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -48489,7 +49002,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -48810,6 +49323,501 @@
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1184</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>374136</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1189</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>374140</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1192</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>374141</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1193</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>374310</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1195</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>286478</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1197</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>125880</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1199</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>374249</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1207</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>125879</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1208</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>374179</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1213</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>374143</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1216</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>374142</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1217</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>286475</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1223</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>374253</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1224</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>374251</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1256</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>374252</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1261</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>374666</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
+++ b/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
@@ -36,6 +36,7 @@
     <sheet name="18 September" sheetId="27" state="visible" r:id="rId27"/>
     <sheet name="19 September" sheetId="28" state="visible" r:id="rId28"/>
     <sheet name="20 September" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="21 September" sheetId="30" state="visible" r:id="rId30"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H975"/>
+  <dimension ref="A1:H1068"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -27544,24 +27545,24 @@
       </c>
       <c r="B858" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C858" s="3" t="n">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="D858" s="3" t="inlineStr">
         <is>
-          <t>284907</t>
+          <t>286842</t>
         </is>
       </c>
       <c r="E858" s="3" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F858" s="3" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="G858" s="3" t="inlineStr">
         <is>
@@ -27580,11 +27581,11 @@
         </is>
       </c>
       <c r="C859" s="2" t="n">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D859" s="2" t="inlineStr">
         <is>
-          <t>284637</t>
+          <t>284907</t>
         </is>
       </c>
       <c r="E859" s="2" t="inlineStr">
@@ -27593,7 +27594,7 @@
         </is>
       </c>
       <c r="F859" s="2" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G859" s="2" t="inlineStr">
         <is>
@@ -27612,11 +27613,11 @@
         </is>
       </c>
       <c r="C860" s="3" t="n">
-        <v>1095</v>
+        <v>1094</v>
       </c>
       <c r="D860" s="3" t="inlineStr">
         <is>
-          <t>284282</t>
+          <t>284637</t>
         </is>
       </c>
       <c r="E860" s="3" t="inlineStr">
@@ -27625,7 +27626,7 @@
         </is>
       </c>
       <c r="F860" s="3" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G860" s="3" t="inlineStr">
         <is>
@@ -27644,11 +27645,11 @@
         </is>
       </c>
       <c r="C861" s="2" t="n">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="D861" s="2" t="inlineStr">
         <is>
-          <t>284715</t>
+          <t>284282</t>
         </is>
       </c>
       <c r="E861" s="2" t="inlineStr">
@@ -27657,7 +27658,7 @@
         </is>
       </c>
       <c r="F861" s="2" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G861" s="2" t="inlineStr">
         <is>
@@ -27676,11 +27677,11 @@
         </is>
       </c>
       <c r="C862" s="3" t="n">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="D862" s="3" t="inlineStr">
         <is>
-          <t>284716</t>
+          <t>284715</t>
         </is>
       </c>
       <c r="E862" s="3" t="inlineStr">
@@ -27689,7 +27690,7 @@
         </is>
       </c>
       <c r="F862" s="3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G862" s="3" t="inlineStr">
         <is>
@@ -27708,11 +27709,11 @@
         </is>
       </c>
       <c r="C863" s="2" t="n">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D863" s="2" t="inlineStr">
         <is>
-          <t>284283</t>
+          <t>284716</t>
         </is>
       </c>
       <c r="E863" s="2" t="inlineStr">
@@ -27721,7 +27722,7 @@
         </is>
       </c>
       <c r="F863" s="2" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="G863" s="2" t="inlineStr">
         <is>
@@ -27740,20 +27741,20 @@
         </is>
       </c>
       <c r="C864" s="3" t="n">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="D864" s="3" t="inlineStr">
         <is>
-          <t>284904</t>
+          <t>284283</t>
         </is>
       </c>
       <c r="E864" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>69</t>
         </is>
       </c>
       <c r="F864" s="3" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G864" s="3" t="inlineStr">
         <is>
@@ -27772,11 +27773,11 @@
         </is>
       </c>
       <c r="C865" s="2" t="n">
-        <v>1100</v>
+        <v>1099</v>
       </c>
       <c r="D865" s="2" t="inlineStr">
         <is>
-          <t>284905</t>
+          <t>284904</t>
         </is>
       </c>
       <c r="E865" s="2" t="inlineStr">
@@ -27785,7 +27786,7 @@
         </is>
       </c>
       <c r="F865" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G865" s="2" t="inlineStr">
         <is>
@@ -27804,20 +27805,20 @@
         </is>
       </c>
       <c r="C866" s="3" t="n">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D866" s="3" t="inlineStr">
         <is>
-          <t>284901</t>
+          <t>284905</t>
         </is>
       </c>
       <c r="E866" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F866" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G866" s="3" t="inlineStr">
         <is>
@@ -27836,11 +27837,11 @@
         </is>
       </c>
       <c r="C867" s="2" t="n">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="D867" s="2" t="inlineStr">
         <is>
-          <t>284902</t>
+          <t>284901</t>
         </is>
       </c>
       <c r="E867" s="2" t="inlineStr">
@@ -27849,7 +27850,7 @@
         </is>
       </c>
       <c r="F867" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G867" s="2" t="inlineStr">
         <is>
@@ -27868,11 +27869,11 @@
         </is>
       </c>
       <c r="C868" s="3" t="n">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="D868" s="3" t="inlineStr">
         <is>
-          <t>284903</t>
+          <t>284902</t>
         </is>
       </c>
       <c r="E868" s="3" t="inlineStr">
@@ -27881,7 +27882,7 @@
         </is>
       </c>
       <c r="F868" s="3" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G868" s="3" t="inlineStr">
         <is>
@@ -27900,11 +27901,11 @@
         </is>
       </c>
       <c r="C869" s="2" t="n">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D869" s="2" t="inlineStr">
         <is>
-          <t>284636</t>
+          <t>284903</t>
         </is>
       </c>
       <c r="E869" s="2" t="inlineStr">
@@ -27913,7 +27914,7 @@
         </is>
       </c>
       <c r="F869" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G869" s="2" t="inlineStr">
         <is>
@@ -27932,11 +27933,11 @@
         </is>
       </c>
       <c r="C870" s="3" t="n">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D870" s="3" t="inlineStr">
         <is>
-          <t>284919</t>
+          <t>284636</t>
         </is>
       </c>
       <c r="E870" s="3" t="inlineStr">
@@ -27945,7 +27946,7 @@
         </is>
       </c>
       <c r="F870" s="3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G870" s="3" t="inlineStr">
         <is>
@@ -27964,20 +27965,20 @@
         </is>
       </c>
       <c r="C871" s="2" t="n">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D871" s="2" t="inlineStr">
         <is>
-          <t>284635</t>
+          <t>284919</t>
         </is>
       </c>
       <c r="E871" s="2" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F871" s="2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G871" s="2" t="inlineStr">
         <is>
@@ -27996,20 +27997,20 @@
         </is>
       </c>
       <c r="C872" s="3" t="n">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D872" s="3" t="inlineStr">
         <is>
-          <t>284634</t>
+          <t>284635</t>
         </is>
       </c>
       <c r="E872" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>73</t>
         </is>
       </c>
       <c r="F872" s="3" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G872" s="3" t="inlineStr">
         <is>
@@ -28028,11 +28029,11 @@
         </is>
       </c>
       <c r="C873" s="2" t="n">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="D873" s="2" t="inlineStr">
         <is>
-          <t>284920</t>
+          <t>284634</t>
         </is>
       </c>
       <c r="E873" s="2" t="inlineStr">
@@ -28041,7 +28042,7 @@
         </is>
       </c>
       <c r="F873" s="2" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="G873" s="2" t="inlineStr">
         <is>
@@ -28060,20 +28061,20 @@
         </is>
       </c>
       <c r="C874" s="3" t="n">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="D874" s="3" t="inlineStr">
         <is>
-          <t>284629</t>
+          <t>284920</t>
         </is>
       </c>
       <c r="E874" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F874" s="3" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="G874" s="3" t="inlineStr">
         <is>
@@ -28092,11 +28093,11 @@
         </is>
       </c>
       <c r="C875" s="2" t="n">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="D875" s="2" t="inlineStr">
         <is>
-          <t>284633</t>
+          <t>284629</t>
         </is>
       </c>
       <c r="E875" s="2" t="inlineStr">
@@ -28105,7 +28106,7 @@
         </is>
       </c>
       <c r="F875" s="2" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G875" s="2" t="inlineStr">
         <is>
@@ -28124,11 +28125,11 @@
         </is>
       </c>
       <c r="C876" s="3" t="n">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="D876" s="3" t="inlineStr">
         <is>
-          <t>284632</t>
+          <t>284633</t>
         </is>
       </c>
       <c r="E876" s="3" t="inlineStr">
@@ -28137,7 +28138,7 @@
         </is>
       </c>
       <c r="F876" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G876" s="3" t="inlineStr">
         <is>
@@ -28156,20 +28157,20 @@
         </is>
       </c>
       <c r="C877" s="2" t="n">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="D877" s="2" t="inlineStr">
         <is>
-          <t>284630</t>
+          <t>284632</t>
         </is>
       </c>
       <c r="E877" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F877" s="2" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G877" s="2" t="inlineStr">
         <is>
@@ -28188,11 +28189,11 @@
         </is>
       </c>
       <c r="C878" s="3" t="n">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D878" s="3" t="inlineStr">
         <is>
-          <t>284631</t>
+          <t>284630</t>
         </is>
       </c>
       <c r="E878" s="3" t="inlineStr">
@@ -28201,7 +28202,7 @@
         </is>
       </c>
       <c r="F878" s="3" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G878" s="3" t="inlineStr">
         <is>
@@ -28220,20 +28221,20 @@
         </is>
       </c>
       <c r="C879" s="2" t="n">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="D879" s="2" t="inlineStr">
         <is>
-          <t>284918</t>
+          <t>284631</t>
         </is>
       </c>
       <c r="E879" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F879" s="2" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="G879" s="2" t="inlineStr">
         <is>
@@ -28252,11 +28253,11 @@
         </is>
       </c>
       <c r="C880" s="3" t="n">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="D880" s="3" t="inlineStr">
         <is>
-          <t>284916</t>
+          <t>284918</t>
         </is>
       </c>
       <c r="E880" s="3" t="inlineStr">
@@ -28265,7 +28266,7 @@
         </is>
       </c>
       <c r="F880" s="3" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="G880" s="3" t="inlineStr">
         <is>
@@ -28284,20 +28285,20 @@
         </is>
       </c>
       <c r="C881" s="2" t="n">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D881" s="2" t="inlineStr">
         <is>
-          <t>284915</t>
+          <t>284916</t>
         </is>
       </c>
       <c r="E881" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F881" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G881" s="2" t="inlineStr">
         <is>
@@ -28316,11 +28317,11 @@
         </is>
       </c>
       <c r="C882" s="3" t="n">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="D882" s="3" t="inlineStr">
         <is>
-          <t>284917</t>
+          <t>284915</t>
         </is>
       </c>
       <c r="E882" s="3" t="inlineStr">
@@ -28329,7 +28330,7 @@
         </is>
       </c>
       <c r="F882" s="3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G882" s="3" t="inlineStr">
         <is>
@@ -28348,20 +28349,20 @@
         </is>
       </c>
       <c r="C883" s="2" t="n">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="D883" s="2" t="inlineStr">
         <is>
-          <t>284720</t>
+          <t>284917</t>
         </is>
       </c>
       <c r="E883" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F883" s="2" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G883" s="2" t="inlineStr">
         <is>
@@ -28380,11 +28381,11 @@
         </is>
       </c>
       <c r="C884" s="3" t="n">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="D884" s="3" t="inlineStr">
         <is>
-          <t>284719</t>
+          <t>284720</t>
         </is>
       </c>
       <c r="E884" s="3" t="inlineStr">
@@ -28393,7 +28394,7 @@
         </is>
       </c>
       <c r="F884" s="3" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G884" s="3" t="inlineStr">
         <is>
@@ -28412,20 +28413,20 @@
         </is>
       </c>
       <c r="C885" s="2" t="n">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D885" s="2" t="inlineStr">
         <is>
-          <t>284922</t>
+          <t>284719</t>
         </is>
       </c>
       <c r="E885" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F885" s="2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="G885" s="2" t="inlineStr">
         <is>
@@ -28444,20 +28445,20 @@
         </is>
       </c>
       <c r="C886" s="3" t="n">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="D886" s="3" t="inlineStr">
         <is>
-          <t>284823</t>
+          <t>284922</t>
         </is>
       </c>
       <c r="E886" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F886" s="3" t="n">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="G886" s="3" t="inlineStr">
         <is>
@@ -28476,20 +28477,20 @@
         </is>
       </c>
       <c r="C887" s="2" t="n">
-        <v>1122</v>
+        <v>1121</v>
       </c>
       <c r="D887" s="2" t="inlineStr">
         <is>
-          <t>280336</t>
+          <t>284823</t>
         </is>
       </c>
       <c r="E887" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F887" s="2" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G887" s="2" t="inlineStr">
         <is>
@@ -28508,20 +28509,20 @@
         </is>
       </c>
       <c r="C888" s="3" t="n">
-        <v>1123</v>
+        <v>1122</v>
       </c>
       <c r="D888" s="3" t="inlineStr">
         <is>
-          <t>284822</t>
+          <t>280336</t>
         </is>
       </c>
       <c r="E888" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F888" s="3" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="G888" s="3" t="inlineStr">
         <is>
@@ -28540,20 +28541,20 @@
         </is>
       </c>
       <c r="C889" s="2" t="n">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D889" s="2" t="inlineStr">
         <is>
-          <t>284820</t>
+          <t>284822</t>
         </is>
       </c>
       <c r="E889" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F889" s="2" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G889" s="2" t="inlineStr">
         <is>
@@ -28572,11 +28573,11 @@
         </is>
       </c>
       <c r="C890" s="3" t="n">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D890" s="3" t="inlineStr">
         <is>
-          <t>284819</t>
+          <t>284820</t>
         </is>
       </c>
       <c r="E890" s="3" t="inlineStr">
@@ -28585,7 +28586,7 @@
         </is>
       </c>
       <c r="F890" s="3" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G890" s="3" t="inlineStr">
         <is>
@@ -28600,20 +28601,20 @@
       </c>
       <c r="B891" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C891" s="2" t="n">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="D891" s="2" t="inlineStr">
         <is>
-          <t>286479</t>
+          <t>284819</t>
         </is>
       </c>
       <c r="E891" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F891" s="2" t="n">
@@ -28632,15 +28633,15 @@
       </c>
       <c r="B892" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C892" s="3" t="n">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D892" s="3" t="inlineStr">
         <is>
-          <t>284821</t>
+          <t>286479</t>
         </is>
       </c>
       <c r="E892" s="3" t="inlineStr">
@@ -28649,7 +28650,7 @@
         </is>
       </c>
       <c r="F892" s="3" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="G892" s="3" t="inlineStr">
         <is>
@@ -28668,20 +28669,20 @@
         </is>
       </c>
       <c r="C893" s="2" t="n">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D893" s="2" t="inlineStr">
         <is>
-          <t>284422</t>
+          <t>284821</t>
         </is>
       </c>
       <c r="E893" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F893" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G893" s="2" t="inlineStr">
         <is>
@@ -28696,15 +28697,15 @@
       </c>
       <c r="B894" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C894" s="3" t="n">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="D894" s="3" t="inlineStr">
         <is>
-          <t>286058</t>
+          <t>284422</t>
         </is>
       </c>
       <c r="E894" s="3" t="inlineStr">
@@ -28713,7 +28714,7 @@
         </is>
       </c>
       <c r="F894" s="3" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G894" s="3" t="inlineStr">
         <is>
@@ -28728,24 +28729,24 @@
       </c>
       <c r="B895" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C895" s="2" t="n">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D895" s="2" t="inlineStr">
         <is>
-          <t>284833</t>
+          <t>286058</t>
         </is>
       </c>
       <c r="E895" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F895" s="2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G895" s="2" t="inlineStr">
         <is>
@@ -28764,20 +28765,20 @@
         </is>
       </c>
       <c r="C896" s="3" t="n">
-        <v>1132</v>
+        <v>1131</v>
       </c>
       <c r="D896" s="3" t="inlineStr">
         <is>
-          <t>284922</t>
+          <t>284833</t>
         </is>
       </c>
       <c r="E896" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F896" s="3" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G896" s="3" t="inlineStr">
         <is>
@@ -28796,11 +28797,11 @@
         </is>
       </c>
       <c r="C897" s="2" t="n">
-        <v>1133</v>
+        <v>1132</v>
       </c>
       <c r="D897" s="2" t="inlineStr">
         <is>
-          <t>284921</t>
+          <t>284922</t>
         </is>
       </c>
       <c r="E897" s="2" t="inlineStr">
@@ -28809,7 +28810,7 @@
         </is>
       </c>
       <c r="F897" s="2" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="G897" s="2" t="inlineStr">
         <is>
@@ -28828,20 +28829,20 @@
         </is>
       </c>
       <c r="C898" s="3" t="n">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D898" s="3" t="inlineStr">
         <is>
-          <t>284830</t>
+          <t>284921</t>
         </is>
       </c>
       <c r="E898" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F898" s="3" t="n">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G898" s="3" t="inlineStr">
         <is>
@@ -28860,20 +28861,20 @@
         </is>
       </c>
       <c r="C899" s="2" t="n">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="D899" s="2" t="inlineStr">
         <is>
-          <t>280338</t>
+          <t>284830</t>
         </is>
       </c>
       <c r="E899" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F899" s="2" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="G899" s="2" t="inlineStr">
         <is>
@@ -28892,20 +28893,20 @@
         </is>
       </c>
       <c r="C900" s="3" t="n">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="D900" s="3" t="inlineStr">
         <is>
-          <t>282923</t>
+          <t>280338</t>
         </is>
       </c>
       <c r="E900" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F900" s="3" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G900" s="3" t="inlineStr">
         <is>
@@ -28924,11 +28925,11 @@
         </is>
       </c>
       <c r="C901" s="2" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D901" s="2" t="inlineStr">
         <is>
-          <t>284831</t>
+          <t>282923</t>
         </is>
       </c>
       <c r="E901" s="2" t="inlineStr">
@@ -28937,7 +28938,7 @@
         </is>
       </c>
       <c r="F901" s="2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G901" s="2" t="inlineStr">
         <is>
@@ -28956,11 +28957,11 @@
         </is>
       </c>
       <c r="C902" s="3" t="n">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="D902" s="3" t="inlineStr">
         <is>
-          <t>284832</t>
+          <t>284831</t>
         </is>
       </c>
       <c r="E902" s="3" t="inlineStr">
@@ -28969,7 +28970,7 @@
         </is>
       </c>
       <c r="F902" s="3" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="G902" s="3" t="inlineStr">
         <is>
@@ -28988,16 +28989,16 @@
         </is>
       </c>
       <c r="C903" s="2" t="n">
-        <v>1139</v>
+        <v>1138</v>
       </c>
       <c r="D903" s="2" t="inlineStr">
         <is>
-          <t>284427</t>
+          <t>284832</t>
         </is>
       </c>
       <c r="E903" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F903" s="2" t="n">
@@ -29020,20 +29021,20 @@
         </is>
       </c>
       <c r="C904" s="3" t="n">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D904" s="3" t="inlineStr">
         <is>
-          <t>280337</t>
+          <t>284427</t>
         </is>
       </c>
       <c r="E904" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F904" s="3" t="n">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="G904" s="3" t="inlineStr">
         <is>
@@ -29052,11 +29053,11 @@
         </is>
       </c>
       <c r="C905" s="2" t="n">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="D905" s="2" t="inlineStr">
         <is>
-          <t>284426</t>
+          <t>280337</t>
         </is>
       </c>
       <c r="E905" s="2" t="inlineStr">
@@ -29065,7 +29066,7 @@
         </is>
       </c>
       <c r="F905" s="2" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G905" s="2" t="inlineStr">
         <is>
@@ -29084,16 +29085,16 @@
         </is>
       </c>
       <c r="C906" s="3" t="n">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D906" s="3" t="inlineStr">
         <is>
-          <t>284425</t>
+          <t>284426</t>
         </is>
       </c>
       <c r="E906" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F906" s="3" t="n">
@@ -29116,11 +29117,11 @@
         </is>
       </c>
       <c r="C907" s="2" t="n">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D907" s="2" t="inlineStr">
         <is>
-          <t>284829</t>
+          <t>284425</t>
         </is>
       </c>
       <c r="E907" s="2" t="inlineStr">
@@ -29129,7 +29130,7 @@
         </is>
       </c>
       <c r="F907" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G907" s="2" t="inlineStr">
         <is>
@@ -29148,20 +29149,20 @@
         </is>
       </c>
       <c r="C908" s="3" t="n">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="D908" s="3" t="inlineStr">
         <is>
-          <t>284824</t>
+          <t>284829</t>
         </is>
       </c>
       <c r="E908" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F908" s="3" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G908" s="3" t="inlineStr">
         <is>
@@ -29180,20 +29181,20 @@
         </is>
       </c>
       <c r="C909" s="2" t="n">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="D909" s="2" t="inlineStr">
         <is>
-          <t>284825</t>
+          <t>284824</t>
         </is>
       </c>
       <c r="E909" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F909" s="2" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G909" s="2" t="inlineStr">
         <is>
@@ -29212,16 +29213,16 @@
         </is>
       </c>
       <c r="C910" s="3" t="n">
-        <v>1146</v>
+        <v>1145</v>
       </c>
       <c r="D910" s="3" t="inlineStr">
         <is>
-          <t>284828</t>
+          <t>284825</t>
         </is>
       </c>
       <c r="E910" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F910" s="3" t="n">
@@ -29244,11 +29245,11 @@
         </is>
       </c>
       <c r="C911" s="2" t="n">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D911" s="2" t="inlineStr">
         <is>
-          <t>284826</t>
+          <t>284828</t>
         </is>
       </c>
       <c r="E911" s="2" t="inlineStr">
@@ -29257,7 +29258,7 @@
         </is>
       </c>
       <c r="F911" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G911" s="2" t="inlineStr">
         <is>
@@ -29276,11 +29277,11 @@
         </is>
       </c>
       <c r="C912" s="3" t="n">
-        <v>1148</v>
+        <v>1147</v>
       </c>
       <c r="D912" s="3" t="inlineStr">
         <is>
-          <t>284827</t>
+          <t>284826</t>
         </is>
       </c>
       <c r="E912" s="3" t="inlineStr">
@@ -29289,7 +29290,7 @@
         </is>
       </c>
       <c r="F912" s="3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G912" s="3" t="inlineStr">
         <is>
@@ -29304,20 +29305,20 @@
       </c>
       <c r="B913" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C913" s="2" t="n">
-        <v>1149</v>
+        <v>1148</v>
       </c>
       <c r="D913" s="2" t="inlineStr">
         <is>
-          <t>284446</t>
+          <t>284827</t>
         </is>
       </c>
       <c r="E913" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F913" s="2" t="n">
@@ -29336,20 +29337,20 @@
       </c>
       <c r="B914" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C914" s="3" t="n">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D914" s="3" t="inlineStr">
         <is>
-          <t>284424</t>
+          <t>284446</t>
         </is>
       </c>
       <c r="E914" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F914" s="3" t="n">
@@ -29372,20 +29373,20 @@
         </is>
       </c>
       <c r="C915" s="2" t="n">
-        <v>1151</v>
+        <v>1150</v>
       </c>
       <c r="D915" s="2" t="inlineStr">
         <is>
-          <t>284423</t>
+          <t>284424</t>
         </is>
       </c>
       <c r="E915" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F915" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G915" s="2" t="inlineStr">
         <is>
@@ -29404,11 +29405,11 @@
         </is>
       </c>
       <c r="C916" s="3" t="n">
-        <v>1153</v>
+        <v>1151</v>
       </c>
       <c r="D916" s="3" t="inlineStr">
         <is>
-          <t>284722</t>
+          <t>284423</t>
         </is>
       </c>
       <c r="E916" s="3" t="inlineStr">
@@ -29417,7 +29418,7 @@
         </is>
       </c>
       <c r="F916" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G916" s="3" t="inlineStr">
         <is>
@@ -29432,24 +29433,24 @@
       </c>
       <c r="B917" s="2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C917" s="2" t="n">
-        <v>1154</v>
+        <v>1152</v>
       </c>
       <c r="D917" s="2" t="inlineStr">
         <is>
-          <t>284284</t>
+          <t>374575</t>
         </is>
       </c>
       <c r="E917" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F917" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G917" s="2" t="inlineStr">
         <is>
@@ -29464,24 +29465,24 @@
       </c>
       <c r="B918" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C918" s="3" t="n">
-        <v>1155</v>
+        <v>1153</v>
       </c>
       <c r="D918" s="3" t="inlineStr">
         <is>
-          <t>286190</t>
+          <t>284722</t>
         </is>
       </c>
       <c r="E918" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F918" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G918" s="3" t="inlineStr">
         <is>
@@ -29496,24 +29497,24 @@
       </c>
       <c r="B919" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="C919" s="2" t="n">
-        <v>1156</v>
+        <v>1154</v>
       </c>
       <c r="D919" s="2" t="inlineStr">
         <is>
-          <t>374040</t>
+          <t>284284</t>
         </is>
       </c>
       <c r="E919" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F919" s="2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G919" s="2" t="inlineStr">
         <is>
@@ -29532,11 +29533,11 @@
         </is>
       </c>
       <c r="C920" s="3" t="n">
-        <v>1157</v>
+        <v>1155</v>
       </c>
       <c r="D920" s="3" t="inlineStr">
         <is>
-          <t>286368</t>
+          <t>286190</t>
         </is>
       </c>
       <c r="E920" s="3" t="inlineStr">
@@ -29545,7 +29546,7 @@
         </is>
       </c>
       <c r="F920" s="3" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G920" s="3" t="inlineStr">
         <is>
@@ -29560,15 +29561,15 @@
       </c>
       <c r="B921" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C921" s="2" t="n">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="D921" s="2" t="inlineStr">
         <is>
-          <t>286193</t>
+          <t>374040</t>
         </is>
       </c>
       <c r="E921" s="2" t="inlineStr">
@@ -29596,11 +29597,11 @@
         </is>
       </c>
       <c r="C922" s="3" t="n">
-        <v>1159</v>
+        <v>1157</v>
       </c>
       <c r="D922" s="3" t="inlineStr">
         <is>
-          <t>286192</t>
+          <t>286368</t>
         </is>
       </c>
       <c r="E922" s="3" t="inlineStr">
@@ -29609,7 +29610,7 @@
         </is>
       </c>
       <c r="F922" s="3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G922" s="3" t="inlineStr">
         <is>
@@ -29628,11 +29629,11 @@
         </is>
       </c>
       <c r="C923" s="2" t="n">
-        <v>1160</v>
+        <v>1158</v>
       </c>
       <c r="D923" s="2" t="inlineStr">
         <is>
-          <t>286194</t>
+          <t>286193</t>
         </is>
       </c>
       <c r="E923" s="2" t="inlineStr">
@@ -29641,7 +29642,7 @@
         </is>
       </c>
       <c r="F923" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G923" s="2" t="inlineStr">
         <is>
@@ -29660,11 +29661,11 @@
         </is>
       </c>
       <c r="C924" s="3" t="n">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="D924" s="3" t="inlineStr">
         <is>
-          <t>286195</t>
+          <t>286192</t>
         </is>
       </c>
       <c r="E924" s="3" t="inlineStr">
@@ -29673,7 +29674,7 @@
         </is>
       </c>
       <c r="F924" s="3" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G924" s="3" t="inlineStr">
         <is>
@@ -29692,11 +29693,11 @@
         </is>
       </c>
       <c r="C925" s="2" t="n">
-        <v>1162</v>
+        <v>1160</v>
       </c>
       <c r="D925" s="2" t="inlineStr">
         <is>
-          <t>286367</t>
+          <t>286194</t>
         </is>
       </c>
       <c r="E925" s="2" t="inlineStr">
@@ -29705,7 +29706,7 @@
         </is>
       </c>
       <c r="F925" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G925" s="2" t="inlineStr">
         <is>
@@ -29724,11 +29725,11 @@
         </is>
       </c>
       <c r="C926" s="3" t="n">
-        <v>1163</v>
+        <v>1161</v>
       </c>
       <c r="D926" s="3" t="inlineStr">
         <is>
-          <t>286369</t>
+          <t>286195</t>
         </is>
       </c>
       <c r="E926" s="3" t="inlineStr">
@@ -29752,24 +29753,24 @@
       </c>
       <c r="B927" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C927" s="2" t="n">
-        <v>1164</v>
+        <v>1162</v>
       </c>
       <c r="D927" s="2" t="inlineStr">
         <is>
-          <t>286477</t>
+          <t>286367</t>
         </is>
       </c>
       <c r="E927" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F927" s="2" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="G927" s="2" t="inlineStr">
         <is>
@@ -29788,11 +29789,11 @@
         </is>
       </c>
       <c r="C928" s="3" t="n">
-        <v>1165</v>
+        <v>1163</v>
       </c>
       <c r="D928" s="3" t="inlineStr">
         <is>
-          <t>286191</t>
+          <t>286369</t>
         </is>
       </c>
       <c r="E928" s="3" t="inlineStr">
@@ -29801,7 +29802,7 @@
         </is>
       </c>
       <c r="F928" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G928" s="3" t="inlineStr">
         <is>
@@ -29816,15 +29817,15 @@
       </c>
       <c r="B929" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C929" s="2" t="n">
-        <v>1166</v>
+        <v>1164</v>
       </c>
       <c r="D929" s="2" t="inlineStr">
         <is>
-          <t>284798</t>
+          <t>286477</t>
         </is>
       </c>
       <c r="E929" s="2" t="inlineStr">
@@ -29833,7 +29834,7 @@
         </is>
       </c>
       <c r="F929" s="2" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G929" s="2" t="inlineStr">
         <is>
@@ -29852,20 +29853,20 @@
         </is>
       </c>
       <c r="C930" s="3" t="n">
-        <v>1167</v>
+        <v>1165</v>
       </c>
       <c r="D930" s="3" t="inlineStr">
         <is>
-          <t>284799</t>
+          <t>286191</t>
         </is>
       </c>
       <c r="E930" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F930" s="3" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G930" s="3" t="inlineStr">
         <is>
@@ -29884,20 +29885,20 @@
         </is>
       </c>
       <c r="C931" s="2" t="n">
-        <v>1168</v>
+        <v>1166</v>
       </c>
       <c r="D931" s="2" t="inlineStr">
         <is>
-          <t>286371</t>
+          <t>284798</t>
         </is>
       </c>
       <c r="E931" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F931" s="2" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="G931" s="2" t="inlineStr">
         <is>
@@ -29916,20 +29917,20 @@
         </is>
       </c>
       <c r="C932" s="3" t="n">
-        <v>1169</v>
+        <v>1167</v>
       </c>
       <c r="D932" s="3" t="inlineStr">
         <is>
-          <t>286402</t>
+          <t>284799</t>
         </is>
       </c>
       <c r="E932" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F932" s="3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G932" s="3" t="inlineStr">
         <is>
@@ -29944,24 +29945,24 @@
       </c>
       <c r="B933" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C933" s="2" t="n">
-        <v>1170</v>
+        <v>1168</v>
       </c>
       <c r="D933" s="2" t="inlineStr">
         <is>
-          <t>286476</t>
+          <t>374895</t>
         </is>
       </c>
       <c r="E933" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F933" s="2" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="G933" s="2" t="inlineStr">
         <is>
@@ -29976,15 +29977,15 @@
       </c>
       <c r="B934" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C934" s="3" t="n">
-        <v>1172</v>
+        <v>1169</v>
       </c>
       <c r="D934" s="3" t="inlineStr">
         <is>
-          <t>374250</t>
+          <t>286402</t>
         </is>
       </c>
       <c r="E934" s="3" t="inlineStr">
@@ -29993,7 +29994,7 @@
         </is>
       </c>
       <c r="F934" s="3" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G934" s="3" t="inlineStr">
         <is>
@@ -30012,20 +30013,20 @@
         </is>
       </c>
       <c r="C935" s="2" t="n">
-        <v>1173</v>
+        <v>1170</v>
       </c>
       <c r="D935" s="2" t="inlineStr">
         <is>
-          <t>374038</t>
+          <t>286476</t>
         </is>
       </c>
       <c r="E935" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F935" s="2" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G935" s="2" t="inlineStr">
         <is>
@@ -30040,24 +30041,24 @@
       </c>
       <c r="B936" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="C936" s="3" t="n">
-        <v>1174</v>
+        <v>1171</v>
       </c>
       <c r="D936" s="3" t="inlineStr">
         <is>
-          <t>286199</t>
+          <t>374443</t>
         </is>
       </c>
       <c r="E936" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F936" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G936" s="3" t="inlineStr">
         <is>
@@ -30072,24 +30073,24 @@
       </c>
       <c r="B937" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C937" s="2" t="n">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D937" s="2" t="inlineStr">
         <is>
-          <t>286374</t>
+          <t>374250</t>
         </is>
       </c>
       <c r="E937" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F937" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G937" s="2" t="inlineStr">
         <is>
@@ -30104,24 +30105,24 @@
       </c>
       <c r="B938" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C938" s="3" t="n">
-        <v>1177</v>
+        <v>1173</v>
       </c>
       <c r="D938" s="3" t="inlineStr">
         <is>
-          <t>286376</t>
+          <t>374038</t>
         </is>
       </c>
       <c r="E938" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F938" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G938" s="3" t="inlineStr">
         <is>
@@ -30140,11 +30141,11 @@
         </is>
       </c>
       <c r="C939" s="2" t="n">
-        <v>1179</v>
+        <v>1174</v>
       </c>
       <c r="D939" s="2" t="inlineStr">
         <is>
-          <t>286196</t>
+          <t>286199</t>
         </is>
       </c>
       <c r="E939" s="2" t="inlineStr">
@@ -30153,7 +30154,7 @@
         </is>
       </c>
       <c r="F939" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G939" s="2" t="inlineStr">
         <is>
@@ -30172,20 +30173,20 @@
         </is>
       </c>
       <c r="C940" s="3" t="n">
-        <v>1180</v>
+        <v>1176</v>
       </c>
       <c r="D940" s="3" t="inlineStr">
         <is>
-          <t>284795</t>
+          <t>286374</t>
         </is>
       </c>
       <c r="E940" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F940" s="3" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="G940" s="3" t="inlineStr">
         <is>
@@ -30200,15 +30201,15 @@
       </c>
       <c r="B941" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C941" s="2" t="n">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="D941" s="2" t="inlineStr">
         <is>
-          <t>374039</t>
+          <t>286376</t>
         </is>
       </c>
       <c r="E941" s="2" t="inlineStr">
@@ -30217,7 +30218,7 @@
         </is>
       </c>
       <c r="F941" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G941" s="2" t="inlineStr">
         <is>
@@ -30236,20 +30237,20 @@
         </is>
       </c>
       <c r="C942" s="3" t="n">
-        <v>1182</v>
+        <v>1179</v>
       </c>
       <c r="D942" s="3" t="inlineStr">
         <is>
-          <t>286189</t>
+          <t>286196</t>
         </is>
       </c>
       <c r="E942" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F942" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G942" s="3" t="inlineStr">
         <is>
@@ -30264,24 +30265,24 @@
       </c>
       <c r="B943" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C943" s="2" t="n">
-        <v>1183</v>
+        <v>1180</v>
       </c>
       <c r="D943" s="2" t="inlineStr">
         <is>
-          <t>374041</t>
+          <t>284795</t>
         </is>
       </c>
       <c r="E943" s="2" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F943" s="2" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G943" s="2" t="inlineStr">
         <is>
@@ -30300,20 +30301,20 @@
         </is>
       </c>
       <c r="C944" s="3" t="n">
-        <v>1184</v>
+        <v>1181</v>
       </c>
       <c r="D944" s="3" t="inlineStr">
         <is>
-          <t>374136</t>
+          <t>374039</t>
         </is>
       </c>
       <c r="E944" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F944" s="3" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G944" s="3" t="inlineStr">
         <is>
@@ -30332,20 +30333,20 @@
         </is>
       </c>
       <c r="C945" s="2" t="n">
-        <v>1185</v>
+        <v>1182</v>
       </c>
       <c r="D945" s="2" t="inlineStr">
         <is>
-          <t>286375</t>
+          <t>286189</t>
         </is>
       </c>
       <c r="E945" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F945" s="2" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G945" s="2" t="inlineStr">
         <is>
@@ -30360,15 +30361,15 @@
       </c>
       <c r="B946" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C946" s="3" t="n">
-        <v>1186</v>
+        <v>1183</v>
       </c>
       <c r="D946" s="3" t="inlineStr">
         <is>
-          <t>286373</t>
+          <t>374041</t>
         </is>
       </c>
       <c r="E946" s="3" t="inlineStr">
@@ -30377,7 +30378,7 @@
         </is>
       </c>
       <c r="F946" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G946" s="3" t="inlineStr">
         <is>
@@ -30396,11 +30397,11 @@
         </is>
       </c>
       <c r="C947" s="2" t="n">
-        <v>1189</v>
+        <v>1184</v>
       </c>
       <c r="D947" s="2" t="inlineStr">
         <is>
-          <t>374140</t>
+          <t>374136</t>
         </is>
       </c>
       <c r="E947" s="2" t="inlineStr">
@@ -30428,20 +30429,20 @@
         </is>
       </c>
       <c r="C948" s="3" t="n">
-        <v>1190</v>
+        <v>1185</v>
       </c>
       <c r="D948" s="3" t="inlineStr">
         <is>
-          <t>286057</t>
+          <t>286375</t>
         </is>
       </c>
       <c r="E948" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F948" s="3" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G948" s="3" t="inlineStr">
         <is>
@@ -30460,20 +30461,20 @@
         </is>
       </c>
       <c r="C949" s="2" t="n">
-        <v>1191</v>
+        <v>1186</v>
       </c>
       <c r="D949" s="2" t="inlineStr">
         <is>
-          <t>282939</t>
+          <t>286373</t>
         </is>
       </c>
       <c r="E949" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F949" s="2" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="G949" s="2" t="inlineStr">
         <is>
@@ -30492,20 +30493,20 @@
         </is>
       </c>
       <c r="C950" s="3" t="n">
-        <v>1192</v>
+        <v>1189</v>
       </c>
       <c r="D950" s="3" t="inlineStr">
         <is>
-          <t>374141</t>
+          <t>374140</t>
         </is>
       </c>
       <c r="E950" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F950" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G950" s="3" t="inlineStr">
         <is>
@@ -30520,24 +30521,24 @@
       </c>
       <c r="B951" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C951" s="2" t="n">
-        <v>1193</v>
+        <v>1190</v>
       </c>
       <c r="D951" s="2" t="inlineStr">
         <is>
-          <t>374310</t>
+          <t>286057</t>
         </is>
       </c>
       <c r="E951" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F951" s="2" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G951" s="2" t="inlineStr">
         <is>
@@ -30556,20 +30557,20 @@
         </is>
       </c>
       <c r="C952" s="3" t="n">
-        <v>1194</v>
+        <v>1191</v>
       </c>
       <c r="D952" s="3" t="inlineStr">
         <is>
-          <t>284796</t>
+          <t>282939</t>
         </is>
       </c>
       <c r="E952" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F952" s="3" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G952" s="3" t="inlineStr">
         <is>
@@ -30588,20 +30589,20 @@
         </is>
       </c>
       <c r="C953" s="2" t="n">
-        <v>1195</v>
+        <v>1192</v>
       </c>
       <c r="D953" s="2" t="inlineStr">
         <is>
-          <t>286478</t>
+          <t>374141</t>
         </is>
       </c>
       <c r="E953" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F953" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G953" s="2" t="inlineStr">
         <is>
@@ -30616,24 +30617,24 @@
       </c>
       <c r="B954" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C954" s="3" t="n">
-        <v>1196</v>
+        <v>1193</v>
       </c>
       <c r="D954" s="3" t="inlineStr">
         <is>
-          <t>286370</t>
+          <t>374310</t>
         </is>
       </c>
       <c r="E954" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F954" s="3" t="n">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="G954" s="3" t="inlineStr">
         <is>
@@ -30648,24 +30649,24 @@
       </c>
       <c r="B955" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C955" s="2" t="n">
-        <v>1197</v>
+        <v>1194</v>
       </c>
       <c r="D955" s="2" t="inlineStr">
         <is>
-          <t>125880</t>
+          <t>284796</t>
         </is>
       </c>
       <c r="E955" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F955" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G955" s="2" t="inlineStr">
         <is>
@@ -30680,24 +30681,24 @@
       </c>
       <c r="B956" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C956" s="3" t="n">
-        <v>1198</v>
+        <v>1195</v>
       </c>
       <c r="D956" s="3" t="inlineStr">
         <is>
-          <t>286372</t>
+          <t>286478</t>
         </is>
       </c>
       <c r="E956" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F956" s="3" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="G956" s="3" t="inlineStr">
         <is>
@@ -30712,15 +30713,15 @@
       </c>
       <c r="B957" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C957" s="2" t="n">
-        <v>1199</v>
+        <v>1196</v>
       </c>
       <c r="D957" s="2" t="inlineStr">
         <is>
-          <t>374249</t>
+          <t>286370</t>
         </is>
       </c>
       <c r="E957" s="2" t="inlineStr">
@@ -30729,7 +30730,7 @@
         </is>
       </c>
       <c r="F957" s="2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G957" s="2" t="inlineStr">
         <is>
@@ -30744,24 +30745,24 @@
       </c>
       <c r="B958" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C958" s="3" t="n">
-        <v>1201</v>
+        <v>1197</v>
       </c>
       <c r="D958" s="3" t="inlineStr">
         <is>
-          <t>284797</t>
+          <t>125880</t>
         </is>
       </c>
       <c r="E958" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F958" s="3" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G958" s="3" t="inlineStr">
         <is>
@@ -30780,20 +30781,20 @@
         </is>
       </c>
       <c r="C959" s="2" t="n">
-        <v>1202</v>
+        <v>1198</v>
       </c>
       <c r="D959" s="2" t="inlineStr">
         <is>
-          <t>284800</t>
+          <t>286372</t>
         </is>
       </c>
       <c r="E959" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F959" s="2" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G959" s="2" t="inlineStr">
         <is>
@@ -30808,24 +30809,24 @@
       </c>
       <c r="B960" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C960" s="3" t="n">
-        <v>1203</v>
+        <v>1199</v>
       </c>
       <c r="D960" s="3" t="inlineStr">
         <is>
-          <t>284445</t>
+          <t>374249</t>
         </is>
       </c>
       <c r="E960" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F960" s="3" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="G960" s="3" t="inlineStr">
         <is>
@@ -30844,20 +30845,20 @@
         </is>
       </c>
       <c r="C961" s="2" t="n">
-        <v>1205</v>
+        <v>1201</v>
       </c>
       <c r="D961" s="2" t="inlineStr">
         <is>
-          <t>286197</t>
+          <t>284797</t>
         </is>
       </c>
       <c r="E961" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F961" s="2" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G961" s="2" t="inlineStr">
         <is>
@@ -30876,20 +30877,20 @@
         </is>
       </c>
       <c r="C962" s="3" t="n">
-        <v>1206</v>
+        <v>1202</v>
       </c>
       <c r="D962" s="3" t="inlineStr">
         <is>
-          <t>286401</t>
+          <t>284800</t>
         </is>
       </c>
       <c r="E962" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F962" s="3" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G962" s="3" t="inlineStr">
         <is>
@@ -30904,24 +30905,24 @@
       </c>
       <c r="B963" s="2" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C963" s="2" t="n">
-        <v>1207</v>
+        <v>1203</v>
       </c>
       <c r="D963" s="2" t="inlineStr">
         <is>
-          <t>125879</t>
+          <t>284445</t>
         </is>
       </c>
       <c r="E963" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F963" s="2" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="G963" s="2" t="inlineStr">
         <is>
@@ -30936,24 +30937,24 @@
       </c>
       <c r="B964" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C964" s="3" t="n">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="D964" s="3" t="inlineStr">
         <is>
-          <t>374179</t>
+          <t>286197</t>
         </is>
       </c>
       <c r="E964" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F964" s="3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G964" s="3" t="inlineStr">
         <is>
@@ -30972,20 +30973,20 @@
         </is>
       </c>
       <c r="C965" s="2" t="n">
-        <v>1209</v>
+        <v>1206</v>
       </c>
       <c r="D965" s="2" t="inlineStr">
         <is>
-          <t>284448</t>
+          <t>286401</t>
         </is>
       </c>
       <c r="E965" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F965" s="2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G965" s="2" t="inlineStr">
         <is>
@@ -31000,24 +31001,24 @@
       </c>
       <c r="B966" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C966" s="3" t="n">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="D966" s="3" t="inlineStr">
         <is>
-          <t>286198</t>
+          <t>125879</t>
         </is>
       </c>
       <c r="E966" s="3" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F966" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G966" s="3" t="inlineStr">
         <is>
@@ -31032,24 +31033,24 @@
       </c>
       <c r="B967" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="C967" s="2" t="n">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="D967" s="2" t="inlineStr">
         <is>
-          <t>284447</t>
+          <t>374179</t>
         </is>
       </c>
       <c r="E967" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F967" s="2" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G967" s="2" t="inlineStr">
         <is>
@@ -31064,24 +31065,24 @@
       </c>
       <c r="B968" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C968" s="3" t="n">
-        <v>1213</v>
+        <v>1209</v>
       </c>
       <c r="D968" s="3" t="inlineStr">
         <is>
-          <t>374143</t>
+          <t>284448</t>
         </is>
       </c>
       <c r="E968" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F968" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G968" s="3" t="inlineStr">
         <is>
@@ -31100,20 +31101,20 @@
         </is>
       </c>
       <c r="C969" s="2" t="n">
-        <v>1215</v>
+        <v>1211</v>
       </c>
       <c r="D969" s="2" t="inlineStr">
         <is>
-          <t>286059</t>
+          <t>286198</t>
         </is>
       </c>
       <c r="E969" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>74</t>
         </is>
       </c>
       <c r="F969" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G969" s="2" t="inlineStr">
         <is>
@@ -31128,24 +31129,24 @@
       </c>
       <c r="B970" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C970" s="3" t="n">
-        <v>1216</v>
+        <v>1212</v>
       </c>
       <c r="D970" s="3" t="inlineStr">
         <is>
-          <t>374142</t>
+          <t>284447</t>
         </is>
       </c>
       <c r="E970" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F970" s="3" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G970" s="3" t="inlineStr">
         <is>
@@ -31164,20 +31165,20 @@
         </is>
       </c>
       <c r="C971" s="2" t="n">
-        <v>1217</v>
+        <v>1213</v>
       </c>
       <c r="D971" s="2" t="inlineStr">
         <is>
-          <t>286475</t>
+          <t>374143</t>
         </is>
       </c>
       <c r="E971" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F971" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G971" s="2" t="inlineStr">
         <is>
@@ -31192,20 +31193,20 @@
       </c>
       <c r="B972" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C972" s="3" t="n">
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="D972" s="3" t="inlineStr">
         <is>
-          <t>374253</t>
+          <t>286059</t>
         </is>
       </c>
       <c r="E972" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F972" s="3" t="n">
@@ -31228,20 +31229,20 @@
         </is>
       </c>
       <c r="C973" s="2" t="n">
-        <v>1224</v>
+        <v>1216</v>
       </c>
       <c r="D973" s="2" t="inlineStr">
         <is>
-          <t>374251</t>
+          <t>374142</t>
         </is>
       </c>
       <c r="E973" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F973" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G973" s="2" t="inlineStr">
         <is>
@@ -31260,20 +31261,20 @@
         </is>
       </c>
       <c r="C974" s="3" t="n">
-        <v>1256</v>
+        <v>1217</v>
       </c>
       <c r="D974" s="3" t="inlineStr">
         <is>
-          <t>374252</t>
+          <t>286475</t>
         </is>
       </c>
       <c r="E974" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F974" s="3" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G974" s="3" t="inlineStr">
         <is>
@@ -31288,31 +31289,2971 @@
       </c>
       <c r="B975" s="2" t="inlineStr">
         <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C975" s="2" t="n">
+        <v>1223</v>
+      </c>
+      <c r="D975" s="2" t="inlineStr">
+        <is>
+          <t>374253</t>
+        </is>
+      </c>
+      <c r="E975" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F975" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G975" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H975" s="2" t="inlineStr"/>
+    </row>
+    <row r="976" ht="20" customHeight="1">
+      <c r="A976" s="3" t="n">
+        <v>972</v>
+      </c>
+      <c r="B976" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C976" s="3" t="n">
+        <v>1224</v>
+      </c>
+      <c r="D976" s="3" t="inlineStr">
+        <is>
+          <t>374251</t>
+        </is>
+      </c>
+      <c r="E976" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F976" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G976" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H976" s="3" t="inlineStr"/>
+    </row>
+    <row r="977" ht="20" customHeight="1">
+      <c r="A977" s="2" t="n">
+        <v>973</v>
+      </c>
+      <c r="B977" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="C977" s="2" t="n">
+        <v>1256</v>
+      </c>
+      <c r="D977" s="2" t="inlineStr">
+        <is>
+          <t>374252</t>
+        </is>
+      </c>
+      <c r="E977" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F977" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G977" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H977" s="2" t="inlineStr"/>
+    </row>
+    <row r="978" ht="20" customHeight="1">
+      <c r="A978" s="3" t="n">
+        <v>974</v>
+      </c>
+      <c r="B978" s="3" t="inlineStr">
+        <is>
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="C975" s="2" t="n">
+      <c r="C978" s="3" t="n">
+        <v>1258</v>
+      </c>
+      <c r="D978" s="3" t="inlineStr">
+        <is>
+          <t>374897</t>
+        </is>
+      </c>
+      <c r="E978" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F978" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G978" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H978" s="3" t="inlineStr"/>
+    </row>
+    <row r="979" ht="20" customHeight="1">
+      <c r="A979" s="2" t="n">
+        <v>975</v>
+      </c>
+      <c r="B979" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C979" s="2" t="n">
+        <v>1259</v>
+      </c>
+      <c r="D979" s="2" t="inlineStr">
+        <is>
+          <t>374896</t>
+        </is>
+      </c>
+      <c r="E979" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F979" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G979" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H979" s="2" t="inlineStr"/>
+    </row>
+    <row r="980" ht="20" customHeight="1">
+      <c r="A980" s="3" t="n">
+        <v>976</v>
+      </c>
+      <c r="B980" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C980" s="3" t="n">
+        <v>1260</v>
+      </c>
+      <c r="D980" s="3" t="inlineStr">
+        <is>
+          <t>374665</t>
+        </is>
+      </c>
+      <c r="E980" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F980" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G980" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H980" s="3" t="inlineStr"/>
+    </row>
+    <row r="981" ht="20" customHeight="1">
+      <c r="A981" s="2" t="n">
+        <v>977</v>
+      </c>
+      <c r="B981" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C981" s="2" t="n">
         <v>1261</v>
       </c>
-      <c r="D975" s="2" t="inlineStr">
+      <c r="D981" s="2" t="inlineStr">
         <is>
           <t>374666</t>
         </is>
       </c>
-      <c r="E975" s="2" t="inlineStr">
+      <c r="E981" s="2" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="F975" s="2" t="n">
+      <c r="F981" s="2" t="n">
         <v>36</v>
       </c>
-      <c r="G975" s="2" t="inlineStr">
-        <is>
-          <t>SELESAI</t>
-        </is>
-      </c>
-      <c r="H975" s="2" t="inlineStr"/>
+      <c r="G981" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H981" s="2" t="inlineStr"/>
+    </row>
+    <row r="982" ht="20" customHeight="1">
+      <c r="A982" s="3" t="n">
+        <v>978</v>
+      </c>
+      <c r="B982" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C982" s="3" t="n">
+        <v>1262</v>
+      </c>
+      <c r="D982" s="3" t="inlineStr">
+        <is>
+          <t>374667</t>
+        </is>
+      </c>
+      <c r="E982" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F982" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G982" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H982" s="3" t="inlineStr"/>
+    </row>
+    <row r="983" ht="20" customHeight="1">
+      <c r="A983" s="2" t="n">
+        <v>979</v>
+      </c>
+      <c r="B983" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C983" s="2" t="n">
+        <v>1263</v>
+      </c>
+      <c r="D983" s="2" t="inlineStr">
+        <is>
+          <t>374668</t>
+        </is>
+      </c>
+      <c r="E983" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F983" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="G983" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H983" s="2" t="inlineStr"/>
+    </row>
+    <row r="984" ht="20" customHeight="1">
+      <c r="A984" s="3" t="n">
+        <v>980</v>
+      </c>
+      <c r="B984" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C984" s="3" t="n">
+        <v>1266</v>
+      </c>
+      <c r="D984" s="3" t="inlineStr">
+        <is>
+          <t>374669</t>
+        </is>
+      </c>
+      <c r="E984" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F984" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G984" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H984" s="3" t="inlineStr"/>
+    </row>
+    <row r="985" ht="20" customHeight="1">
+      <c r="A985" s="2" t="n">
+        <v>981</v>
+      </c>
+      <c r="B985" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C985" s="2" t="n">
+        <v>1267</v>
+      </c>
+      <c r="D985" s="2" t="inlineStr">
+        <is>
+          <t>374898</t>
+        </is>
+      </c>
+      <c r="E985" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F985" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G985" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H985" s="2" t="inlineStr"/>
+    </row>
+    <row r="986" ht="20" customHeight="1">
+      <c r="A986" s="3" t="n">
+        <v>982</v>
+      </c>
+      <c r="B986" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C986" s="3" t="n">
+        <v>1268</v>
+      </c>
+      <c r="D986" s="3" t="inlineStr">
+        <is>
+          <t>374444</t>
+        </is>
+      </c>
+      <c r="E986" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F986" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G986" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H986" s="3" t="inlineStr"/>
+    </row>
+    <row r="987" ht="20" customHeight="1">
+      <c r="A987" s="2" t="n">
+        <v>983</v>
+      </c>
+      <c r="B987" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C987" s="2" t="n">
+        <v>1269</v>
+      </c>
+      <c r="D987" s="2" t="inlineStr">
+        <is>
+          <t>374953</t>
+        </is>
+      </c>
+      <c r="E987" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F987" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G987" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H987" s="2" t="inlineStr"/>
+    </row>
+    <row r="988" ht="20" customHeight="1">
+      <c r="A988" s="3" t="n">
+        <v>984</v>
+      </c>
+      <c r="B988" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C988" s="3" t="n">
+        <v>1270</v>
+      </c>
+      <c r="D988" s="3" t="inlineStr">
+        <is>
+          <t>374951</t>
+        </is>
+      </c>
+      <c r="E988" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F988" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G988" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H988" s="3" t="inlineStr"/>
+    </row>
+    <row r="989" ht="20" customHeight="1">
+      <c r="A989" s="2" t="n">
+        <v>985</v>
+      </c>
+      <c r="B989" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C989" s="2" t="n">
+        <v>1271</v>
+      </c>
+      <c r="D989" s="2" t="inlineStr">
+        <is>
+          <t>374670</t>
+        </is>
+      </c>
+      <c r="E989" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F989" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G989" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H989" s="2" t="inlineStr"/>
+    </row>
+    <row r="990" ht="20" customHeight="1">
+      <c r="A990" s="3" t="n">
+        <v>986</v>
+      </c>
+      <c r="B990" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C990" s="3" t="n">
+        <v>1272</v>
+      </c>
+      <c r="D990" s="3" t="inlineStr">
+        <is>
+          <t>374954</t>
+        </is>
+      </c>
+      <c r="E990" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F990" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G990" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H990" s="3" t="inlineStr"/>
+    </row>
+    <row r="991" ht="20" customHeight="1">
+      <c r="A991" s="2" t="n">
+        <v>987</v>
+      </c>
+      <c r="B991" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C991" s="2" t="n">
+        <v>1273</v>
+      </c>
+      <c r="D991" s="2" t="inlineStr">
+        <is>
+          <t>374952</t>
+        </is>
+      </c>
+      <c r="E991" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F991" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G991" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H991" s="2" t="inlineStr"/>
+    </row>
+    <row r="992" ht="20" customHeight="1">
+      <c r="A992" s="3" t="n">
+        <v>988</v>
+      </c>
+      <c r="B992" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C992" s="3" t="n">
+        <v>1274</v>
+      </c>
+      <c r="D992" s="3" t="inlineStr">
+        <is>
+          <t>374336</t>
+        </is>
+      </c>
+      <c r="E992" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F992" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G992" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H992" s="3" t="inlineStr"/>
+    </row>
+    <row r="993" ht="20" customHeight="1">
+      <c r="A993" s="2" t="n">
+        <v>989</v>
+      </c>
+      <c r="B993" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C993" s="2" t="n">
+        <v>1275</v>
+      </c>
+      <c r="D993" s="2" t="inlineStr">
+        <is>
+          <t>374572</t>
+        </is>
+      </c>
+      <c r="E993" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F993" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G993" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H993" s="2" t="inlineStr"/>
+    </row>
+    <row r="994" ht="20" customHeight="1">
+      <c r="A994" s="3" t="n">
+        <v>990</v>
+      </c>
+      <c r="B994" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C994" s="3" t="n">
+        <v>1276</v>
+      </c>
+      <c r="D994" s="3" t="inlineStr">
+        <is>
+          <t>286841</t>
+        </is>
+      </c>
+      <c r="E994" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F994" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G994" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H994" s="3" t="inlineStr"/>
+    </row>
+    <row r="995" ht="20" customHeight="1">
+      <c r="A995" s="2" t="n">
+        <v>991</v>
+      </c>
+      <c r="B995" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C995" s="2" t="n">
+        <v>1277</v>
+      </c>
+      <c r="D995" s="2" t="inlineStr">
+        <is>
+          <t>374574</t>
+        </is>
+      </c>
+      <c r="E995" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F995" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G995" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H995" s="2" t="inlineStr"/>
+    </row>
+    <row r="996" ht="20" customHeight="1">
+      <c r="A996" s="3" t="n">
+        <v>992</v>
+      </c>
+      <c r="B996" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C996" s="3" t="n">
+        <v>1278</v>
+      </c>
+      <c r="D996" s="3" t="inlineStr">
+        <is>
+          <t>374573</t>
+        </is>
+      </c>
+      <c r="E996" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F996" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G996" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H996" s="3" t="inlineStr"/>
+    </row>
+    <row r="997" ht="20" customHeight="1">
+      <c r="A997" s="2" t="n">
+        <v>993</v>
+      </c>
+      <c r="B997" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C997" s="2" t="n">
+        <v>1279</v>
+      </c>
+      <c r="D997" s="2" t="inlineStr">
+        <is>
+          <t>286791</t>
+        </is>
+      </c>
+      <c r="E997" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F997" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G997" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H997" s="2" t="inlineStr"/>
+    </row>
+    <row r="998" ht="20" customHeight="1">
+      <c r="A998" s="3" t="n">
+        <v>994</v>
+      </c>
+      <c r="B998" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C998" s="3" t="n">
+        <v>1280</v>
+      </c>
+      <c r="D998" s="3" t="inlineStr">
+        <is>
+          <t>286790</t>
+        </is>
+      </c>
+      <c r="E998" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F998" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G998" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H998" s="3" t="inlineStr"/>
+    </row>
+    <row r="999" ht="20" customHeight="1">
+      <c r="A999" s="2" t="n">
+        <v>995</v>
+      </c>
+      <c r="B999" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C999" s="2" t="n">
+        <v>1281</v>
+      </c>
+      <c r="D999" s="2" t="inlineStr">
+        <is>
+          <t>374671</t>
+        </is>
+      </c>
+      <c r="E999" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F999" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G999" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H999" s="2" t="inlineStr"/>
+    </row>
+    <row r="1000" ht="20" customHeight="1">
+      <c r="A1000" s="3" t="n">
+        <v>996</v>
+      </c>
+      <c r="B1000" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="C1000" s="3" t="n">
+        <v>1282</v>
+      </c>
+      <c r="D1000" s="3" t="inlineStr">
+        <is>
+          <t>374442</t>
+        </is>
+      </c>
+      <c r="E1000" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1000" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1000" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1000" s="3" t="inlineStr"/>
+    </row>
+    <row r="1001" ht="20" customHeight="1">
+      <c r="A1001" s="2" t="n">
+        <v>997</v>
+      </c>
+      <c r="B1001" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1001" s="2" t="n">
+        <v>1283</v>
+      </c>
+      <c r="D1001" s="2" t="inlineStr">
+        <is>
+          <t>375596</t>
+        </is>
+      </c>
+      <c r="E1001" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1001" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1001" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1001" s="2" t="inlineStr"/>
+    </row>
+    <row r="1002" ht="20" customHeight="1">
+      <c r="A1002" s="3" t="n">
+        <v>998</v>
+      </c>
+      <c r="B1002" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1002" s="3" t="n">
+        <v>1284</v>
+      </c>
+      <c r="D1002" s="3" t="inlineStr">
+        <is>
+          <t>375597</t>
+        </is>
+      </c>
+      <c r="E1002" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1002" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1002" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1002" s="3" t="inlineStr"/>
+    </row>
+    <row r="1003" ht="20" customHeight="1">
+      <c r="A1003" s="2" t="n">
+        <v>999</v>
+      </c>
+      <c r="B1003" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1003" s="2" t="n">
+        <v>1285</v>
+      </c>
+      <c r="D1003" s="2" t="inlineStr">
+        <is>
+          <t>375595</t>
+        </is>
+      </c>
+      <c r="E1003" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1003" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1003" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1003" s="2" t="inlineStr"/>
+    </row>
+    <row r="1004" ht="20" customHeight="1">
+      <c r="A1004" s="3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="B1004" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1004" s="3" t="n">
+        <v>1286</v>
+      </c>
+      <c r="D1004" s="3" t="inlineStr">
+        <is>
+          <t>375808</t>
+        </is>
+      </c>
+      <c r="E1004" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1004" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1004" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1004" s="3" t="inlineStr"/>
+    </row>
+    <row r="1005" ht="20" customHeight="1">
+      <c r="A1005" s="2" t="n">
+        <v>1001</v>
+      </c>
+      <c r="B1005" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1005" s="2" t="n">
+        <v>1287</v>
+      </c>
+      <c r="D1005" s="2" t="inlineStr">
+        <is>
+          <t>375622</t>
+        </is>
+      </c>
+      <c r="E1005" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1005" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1005" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1005" s="2" t="inlineStr"/>
+    </row>
+    <row r="1006" ht="20" customHeight="1">
+      <c r="A1006" s="3" t="n">
+        <v>1002</v>
+      </c>
+      <c r="B1006" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1006" s="3" t="n">
+        <v>1288</v>
+      </c>
+      <c r="D1006" s="3" t="inlineStr">
+        <is>
+          <t>375809</t>
+        </is>
+      </c>
+      <c r="E1006" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1006" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1006" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1006" s="3" t="inlineStr"/>
+    </row>
+    <row r="1007" ht="20" customHeight="1">
+      <c r="A1007" s="2" t="n">
+        <v>1003</v>
+      </c>
+      <c r="B1007" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1007" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="D1007" s="2" t="inlineStr">
+        <is>
+          <t>375763</t>
+        </is>
+      </c>
+      <c r="E1007" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1007" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1007" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1007" s="2" t="inlineStr"/>
+    </row>
+    <row r="1008" ht="20" customHeight="1">
+      <c r="A1008" s="3" t="n">
+        <v>1004</v>
+      </c>
+      <c r="B1008" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1008" s="3" t="n">
+        <v>1290</v>
+      </c>
+      <c r="D1008" s="3" t="inlineStr">
+        <is>
+          <t>375422</t>
+        </is>
+      </c>
+      <c r="E1008" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1008" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1008" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1008" s="3" t="inlineStr"/>
+    </row>
+    <row r="1009" ht="20" customHeight="1">
+      <c r="A1009" s="2" t="n">
+        <v>1005</v>
+      </c>
+      <c r="B1009" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1009" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="D1009" s="2" t="inlineStr">
+        <is>
+          <t>375423</t>
+        </is>
+      </c>
+      <c r="E1009" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1009" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1009" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1009" s="2" t="inlineStr"/>
+    </row>
+    <row r="1010" ht="20" customHeight="1">
+      <c r="A1010" s="3" t="n">
+        <v>1006</v>
+      </c>
+      <c r="B1010" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1010" s="3" t="n">
+        <v>1292</v>
+      </c>
+      <c r="D1010" s="3" t="inlineStr">
+        <is>
+          <t>375421</t>
+        </is>
+      </c>
+      <c r="E1010" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1010" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1010" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1010" s="3" t="inlineStr"/>
+    </row>
+    <row r="1011" ht="20" customHeight="1">
+      <c r="A1011" s="2" t="n">
+        <v>1007</v>
+      </c>
+      <c r="B1011" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1011" s="2" t="n">
+        <v>1293</v>
+      </c>
+      <c r="D1011" s="2" t="inlineStr">
+        <is>
+          <t>375424</t>
+        </is>
+      </c>
+      <c r="E1011" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1011" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1011" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1011" s="2" t="inlineStr"/>
+    </row>
+    <row r="1012" ht="20" customHeight="1">
+      <c r="A1012" s="3" t="n">
+        <v>1008</v>
+      </c>
+      <c r="B1012" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1012" s="3" t="n">
+        <v>1294</v>
+      </c>
+      <c r="D1012" s="3" t="inlineStr">
+        <is>
+          <t>375811</t>
+        </is>
+      </c>
+      <c r="E1012" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1012" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1012" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1012" s="3" t="inlineStr"/>
+    </row>
+    <row r="1013" ht="20" customHeight="1">
+      <c r="A1013" s="2" t="n">
+        <v>1009</v>
+      </c>
+      <c r="B1013" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1013" s="2" t="n">
+        <v>1295</v>
+      </c>
+      <c r="D1013" s="2" t="inlineStr">
+        <is>
+          <t>375810</t>
+        </is>
+      </c>
+      <c r="E1013" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1013" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1013" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1013" s="2" t="inlineStr"/>
+    </row>
+    <row r="1014" ht="20" customHeight="1">
+      <c r="A1014" s="3" t="n">
+        <v>1010</v>
+      </c>
+      <c r="B1014" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1014" s="3" t="n">
+        <v>1296</v>
+      </c>
+      <c r="D1014" s="3" t="inlineStr"/>
+      <c r="E1014" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1014" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1014" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1014" s="3" t="inlineStr"/>
+    </row>
+    <row r="1015" ht="20" customHeight="1">
+      <c r="A1015" s="2" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B1015" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1015" s="2" t="n">
+        <v>1297</v>
+      </c>
+      <c r="D1015" s="2" t="inlineStr"/>
+      <c r="E1015" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1015" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1015" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1015" s="2" t="inlineStr"/>
+    </row>
+    <row r="1016" ht="20" customHeight="1">
+      <c r="A1016" s="3" t="n">
+        <v>1012</v>
+      </c>
+      <c r="B1016" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1016" s="3" t="n">
+        <v>1298</v>
+      </c>
+      <c r="D1016" s="3" t="inlineStr"/>
+      <c r="E1016" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1016" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1016" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1016" s="3" t="inlineStr"/>
+    </row>
+    <row r="1017" ht="20" customHeight="1">
+      <c r="A1017" s="2" t="n">
+        <v>1013</v>
+      </c>
+      <c r="B1017" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1017" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="D1017" s="2" t="inlineStr"/>
+      <c r="E1017" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1017" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1017" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1017" s="2" t="inlineStr"/>
+    </row>
+    <row r="1018" ht="20" customHeight="1">
+      <c r="A1018" s="3" t="n">
+        <v>1014</v>
+      </c>
+      <c r="B1018" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1018" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="D1018" s="3" t="inlineStr"/>
+      <c r="E1018" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1018" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1018" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1018" s="3" t="inlineStr"/>
+    </row>
+    <row r="1019" ht="20" customHeight="1">
+      <c r="A1019" s="2" t="n">
+        <v>1015</v>
+      </c>
+      <c r="B1019" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1019" s="2" t="n">
+        <v>1301</v>
+      </c>
+      <c r="D1019" s="2" t="inlineStr"/>
+      <c r="E1019" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1019" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1019" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1019" s="2" t="inlineStr"/>
+    </row>
+    <row r="1020" ht="20" customHeight="1">
+      <c r="A1020" s="3" t="n">
+        <v>1016</v>
+      </c>
+      <c r="B1020" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1020" s="3" t="n">
+        <v>1302</v>
+      </c>
+      <c r="D1020" s="3" t="inlineStr"/>
+      <c r="E1020" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1020" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1020" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1020" s="3" t="inlineStr"/>
+    </row>
+    <row r="1021" ht="20" customHeight="1">
+      <c r="A1021" s="2" t="n">
+        <v>1017</v>
+      </c>
+      <c r="B1021" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1021" s="2" t="n">
+        <v>1303</v>
+      </c>
+      <c r="D1021" s="2" t="inlineStr">
+        <is>
+          <t>375852</t>
+        </is>
+      </c>
+      <c r="E1021" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1021" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1021" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1021" s="2" t="inlineStr"/>
+    </row>
+    <row r="1022" ht="20" customHeight="1">
+      <c r="A1022" s="3" t="n">
+        <v>1018</v>
+      </c>
+      <c r="B1022" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1022" s="3" t="n">
+        <v>1304</v>
+      </c>
+      <c r="D1022" s="3" t="inlineStr">
+        <is>
+          <t>375600</t>
+        </is>
+      </c>
+      <c r="E1022" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1022" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1022" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1022" s="3" t="inlineStr"/>
+    </row>
+    <row r="1023" ht="20" customHeight="1">
+      <c r="A1023" s="2" t="n">
+        <v>1019</v>
+      </c>
+      <c r="B1023" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1023" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="D1023" s="2" t="inlineStr">
+        <is>
+          <t>375854</t>
+        </is>
+      </c>
+      <c r="E1023" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F1023" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1023" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1023" s="2" t="inlineStr"/>
+    </row>
+    <row r="1024" ht="20" customHeight="1">
+      <c r="A1024" s="3" t="n">
+        <v>1020</v>
+      </c>
+      <c r="B1024" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1024" s="3" t="n">
+        <v>1306</v>
+      </c>
+      <c r="D1024" s="3" t="inlineStr">
+        <is>
+          <t>375599</t>
+        </is>
+      </c>
+      <c r="E1024" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1024" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1024" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1024" s="3" t="inlineStr"/>
+    </row>
+    <row r="1025" ht="20" customHeight="1">
+      <c r="A1025" s="2" t="n">
+        <v>1021</v>
+      </c>
+      <c r="B1025" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1025" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="D1025" s="2" t="inlineStr">
+        <is>
+          <t>375598</t>
+        </is>
+      </c>
+      <c r="E1025" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1025" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1025" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1025" s="2" t="inlineStr"/>
+    </row>
+    <row r="1026" ht="20" customHeight="1">
+      <c r="A1026" s="3" t="n">
+        <v>1022</v>
+      </c>
+      <c r="B1026" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1026" s="3" t="n">
+        <v>1308</v>
+      </c>
+      <c r="D1026" s="3" t="inlineStr">
+        <is>
+          <t>375851</t>
+        </is>
+      </c>
+      <c r="E1026" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="F1026" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1026" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1026" s="3" t="inlineStr"/>
+    </row>
+    <row r="1027" ht="20" customHeight="1">
+      <c r="A1027" s="2" t="n">
+        <v>1023</v>
+      </c>
+      <c r="B1027" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1027" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D1027" s="2" t="inlineStr">
+        <is>
+          <t>375853</t>
+        </is>
+      </c>
+      <c r="E1027" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1027" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1027" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1027" s="2" t="inlineStr"/>
+    </row>
+    <row r="1028" ht="20" customHeight="1">
+      <c r="A1028" s="3" t="n">
+        <v>1024</v>
+      </c>
+      <c r="B1028" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1028" s="3" t="n">
+        <v>1310</v>
+      </c>
+      <c r="D1028" s="3" t="inlineStr">
+        <is>
+          <t>375637</t>
+        </is>
+      </c>
+      <c r="E1028" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1028" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1028" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1028" s="3" t="inlineStr"/>
+    </row>
+    <row r="1029" ht="20" customHeight="1">
+      <c r="A1029" s="2" t="n">
+        <v>1025</v>
+      </c>
+      <c r="B1029" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1029" s="2" t="n">
+        <v>1311</v>
+      </c>
+      <c r="D1029" s="2" t="inlineStr">
+        <is>
+          <t>375638</t>
+        </is>
+      </c>
+      <c r="E1029" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1029" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1029" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1029" s="2" t="inlineStr"/>
+    </row>
+    <row r="1030" ht="20" customHeight="1">
+      <c r="A1030" s="3" t="n">
+        <v>1026</v>
+      </c>
+      <c r="B1030" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1030" s="3" t="n">
+        <v>1314</v>
+      </c>
+      <c r="D1030" s="3" t="inlineStr">
+        <is>
+          <t>375639</t>
+        </is>
+      </c>
+      <c r="E1030" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1030" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1030" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1030" s="3" t="inlineStr"/>
+    </row>
+    <row r="1031" ht="20" customHeight="1">
+      <c r="A1031" s="2" t="n">
+        <v>1027</v>
+      </c>
+      <c r="B1031" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1031" s="2" t="n">
+        <v>1315</v>
+      </c>
+      <c r="D1031" s="2" t="inlineStr">
+        <is>
+          <t>375806</t>
+        </is>
+      </c>
+      <c r="E1031" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1031" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1031" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1031" s="2" t="inlineStr"/>
+    </row>
+    <row r="1032" ht="20" customHeight="1">
+      <c r="A1032" s="3" t="n">
+        <v>1028</v>
+      </c>
+      <c r="B1032" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1032" s="3" t="n">
+        <v>1316</v>
+      </c>
+      <c r="D1032" s="3" t="inlineStr">
+        <is>
+          <t>375812</t>
+        </is>
+      </c>
+      <c r="E1032" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1032" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1032" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1032" s="3" t="inlineStr"/>
+    </row>
+    <row r="1033" ht="20" customHeight="1">
+      <c r="A1033" s="2" t="n">
+        <v>1029</v>
+      </c>
+      <c r="B1033" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1033" s="2" t="n">
+        <v>1317</v>
+      </c>
+      <c r="D1033" s="2" t="inlineStr">
+        <is>
+          <t>375814</t>
+        </is>
+      </c>
+      <c r="E1033" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1033" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1033" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1033" s="2" t="inlineStr"/>
+    </row>
+    <row r="1034" ht="20" customHeight="1">
+      <c r="A1034" s="3" t="n">
+        <v>1030</v>
+      </c>
+      <c r="B1034" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1034" s="3" t="n">
+        <v>1318</v>
+      </c>
+      <c r="D1034" s="3" t="inlineStr">
+        <is>
+          <t>375813</t>
+        </is>
+      </c>
+      <c r="E1034" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1034" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1034" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1034" s="3" t="inlineStr"/>
+    </row>
+    <row r="1035" ht="20" customHeight="1">
+      <c r="A1035" s="2" t="n">
+        <v>1031</v>
+      </c>
+      <c r="B1035" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1035" s="2" t="n">
+        <v>1319</v>
+      </c>
+      <c r="D1035" s="2" t="inlineStr">
+        <is>
+          <t>375306</t>
+        </is>
+      </c>
+      <c r="E1035" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1035" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1035" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1035" s="2" t="inlineStr"/>
+    </row>
+    <row r="1036" ht="20" customHeight="1">
+      <c r="A1036" s="3" t="n">
+        <v>1032</v>
+      </c>
+      <c r="B1036" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1036" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D1036" s="3" t="inlineStr">
+        <is>
+          <t>375805</t>
+        </is>
+      </c>
+      <c r="E1036" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1036" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1036" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1036" s="3" t="inlineStr"/>
+    </row>
+    <row r="1037" ht="20" customHeight="1">
+      <c r="A1037" s="2" t="n">
+        <v>1033</v>
+      </c>
+      <c r="B1037" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1037" s="2" t="n">
+        <v>1321</v>
+      </c>
+      <c r="D1037" s="2" t="inlineStr">
+        <is>
+          <t>375807</t>
+        </is>
+      </c>
+      <c r="E1037" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1037" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1037" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1037" s="2" t="inlineStr"/>
+    </row>
+    <row r="1038" ht="20" customHeight="1">
+      <c r="A1038" s="3" t="n">
+        <v>1034</v>
+      </c>
+      <c r="B1038" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1038" s="3" t="n">
+        <v>1322</v>
+      </c>
+      <c r="D1038" s="3" t="inlineStr">
+        <is>
+          <t>375307</t>
+        </is>
+      </c>
+      <c r="E1038" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1038" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1038" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1038" s="3" t="inlineStr"/>
+    </row>
+    <row r="1039" ht="20" customHeight="1">
+      <c r="A1039" s="2" t="n">
+        <v>1035</v>
+      </c>
+      <c r="B1039" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1039" s="2" t="n">
+        <v>1328</v>
+      </c>
+      <c r="D1039" s="2" t="inlineStr">
+        <is>
+          <t>375120</t>
+        </is>
+      </c>
+      <c r="E1039" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1039" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1039" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1039" s="2" t="inlineStr"/>
+    </row>
+    <row r="1040" ht="20" customHeight="1">
+      <c r="A1040" s="3" t="n">
+        <v>1036</v>
+      </c>
+      <c r="B1040" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1040" s="3" t="n">
+        <v>1329</v>
+      </c>
+      <c r="D1040" s="3" t="inlineStr">
+        <is>
+          <t>375626</t>
+        </is>
+      </c>
+      <c r="E1040" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1040" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1040" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1040" s="3" t="inlineStr"/>
+    </row>
+    <row r="1041" ht="20" customHeight="1">
+      <c r="A1041" s="2" t="n">
+        <v>1037</v>
+      </c>
+      <c r="B1041" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1041" s="2" t="n">
+        <v>1330</v>
+      </c>
+      <c r="D1041" s="2" t="inlineStr">
+        <is>
+          <t>375628</t>
+        </is>
+      </c>
+      <c r="E1041" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1041" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1041" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1041" s="2" t="inlineStr"/>
+    </row>
+    <row r="1042" ht="20" customHeight="1">
+      <c r="A1042" s="3" t="n">
+        <v>1038</v>
+      </c>
+      <c r="B1042" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1042" s="3" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D1042" s="3" t="inlineStr">
+        <is>
+          <t>375625</t>
+        </is>
+      </c>
+      <c r="E1042" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1042" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1042" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1042" s="3" t="inlineStr"/>
+    </row>
+    <row r="1043" ht="20" customHeight="1">
+      <c r="A1043" s="2" t="n">
+        <v>1039</v>
+      </c>
+      <c r="B1043" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1043" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="D1043" s="2" t="inlineStr">
+        <is>
+          <t>375629</t>
+        </is>
+      </c>
+      <c r="E1043" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1043" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1043" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1043" s="2" t="inlineStr"/>
+    </row>
+    <row r="1044" ht="20" customHeight="1">
+      <c r="A1044" s="3" t="n">
+        <v>1040</v>
+      </c>
+      <c r="B1044" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1044" s="3" t="n">
+        <v>1338</v>
+      </c>
+      <c r="D1044" s="3" t="inlineStr">
+        <is>
+          <t>375630</t>
+        </is>
+      </c>
+      <c r="E1044" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1044" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1044" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1044" s="3" t="inlineStr"/>
+    </row>
+    <row r="1045" ht="20" customHeight="1">
+      <c r="A1045" s="2" t="n">
+        <v>1041</v>
+      </c>
+      <c r="B1045" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1045" s="2" t="n">
+        <v>1339</v>
+      </c>
+      <c r="D1045" s="2" t="inlineStr">
+        <is>
+          <t>375631</t>
+        </is>
+      </c>
+      <c r="E1045" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F1045" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1045" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1045" s="2" t="inlineStr"/>
+    </row>
+    <row r="1046" ht="20" customHeight="1">
+      <c r="A1046" s="3" t="n">
+        <v>1042</v>
+      </c>
+      <c r="B1046" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1046" s="3" t="n">
+        <v>1341</v>
+      </c>
+      <c r="D1046" s="3" t="inlineStr">
+        <is>
+          <t>375627</t>
+        </is>
+      </c>
+      <c r="E1046" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1046" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1046" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1046" s="3" t="inlineStr"/>
+    </row>
+    <row r="1047" ht="20" customHeight="1">
+      <c r="A1047" s="2" t="n">
+        <v>1043</v>
+      </c>
+      <c r="B1047" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1047" s="2" t="n">
+        <v>1345</v>
+      </c>
+      <c r="D1047" s="2" t="inlineStr"/>
+      <c r="E1047" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1047" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1047" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1047" s="2" t="inlineStr"/>
+    </row>
+    <row r="1048" ht="20" customHeight="1">
+      <c r="A1048" s="3" t="n">
+        <v>1044</v>
+      </c>
+      <c r="B1048" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1048" s="3" t="n">
+        <v>1346</v>
+      </c>
+      <c r="D1048" s="3" t="inlineStr">
+        <is>
+          <t>375632</t>
+        </is>
+      </c>
+      <c r="E1048" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="F1048" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1048" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1048" s="3" t="inlineStr"/>
+    </row>
+    <row r="1049" ht="20" customHeight="1">
+      <c r="A1049" s="2" t="n">
+        <v>1045</v>
+      </c>
+      <c r="B1049" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1049" s="2" t="n">
+        <v>1352</v>
+      </c>
+      <c r="D1049" s="2" t="inlineStr">
+        <is>
+          <t>375633</t>
+        </is>
+      </c>
+      <c r="E1049" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1049" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1049" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1049" s="2" t="inlineStr"/>
+    </row>
+    <row r="1050" ht="20" customHeight="1">
+      <c r="A1050" s="3" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B1050" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1050" s="3" t="n">
+        <v>1353</v>
+      </c>
+      <c r="D1050" s="3" t="inlineStr">
+        <is>
+          <t>375122</t>
+        </is>
+      </c>
+      <c r="E1050" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1050" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1050" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1050" s="3" t="inlineStr"/>
+    </row>
+    <row r="1051" ht="20" customHeight="1">
+      <c r="A1051" s="2" t="n">
+        <v>1047</v>
+      </c>
+      <c r="B1051" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1051" s="2" t="n">
+        <v>1354</v>
+      </c>
+      <c r="D1051" s="2" t="inlineStr">
+        <is>
+          <t>375634</t>
+        </is>
+      </c>
+      <c r="E1051" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1051" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1051" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1051" s="2" t="inlineStr"/>
+    </row>
+    <row r="1052" ht="20" customHeight="1">
+      <c r="A1052" s="3" t="n">
+        <v>1048</v>
+      </c>
+      <c r="B1052" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1052" s="3" t="n">
+        <v>1355</v>
+      </c>
+      <c r="D1052" s="3" t="inlineStr">
+        <is>
+          <t>375121</t>
+        </is>
+      </c>
+      <c r="E1052" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1052" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1052" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1052" s="3" t="inlineStr"/>
+    </row>
+    <row r="1053" ht="20" customHeight="1">
+      <c r="A1053" s="2" t="n">
+        <v>1049</v>
+      </c>
+      <c r="B1053" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1053" s="2" t="n">
+        <v>1356</v>
+      </c>
+      <c r="D1053" s="2" t="inlineStr">
+        <is>
+          <t>375123</t>
+        </is>
+      </c>
+      <c r="E1053" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1053" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1053" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1053" s="2" t="inlineStr"/>
+    </row>
+    <row r="1054" ht="20" customHeight="1">
+      <c r="A1054" s="3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="B1054" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1054" s="3" t="n">
+        <v>1357</v>
+      </c>
+      <c r="D1054" s="3" t="inlineStr"/>
+      <c r="E1054" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1054" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1054" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H1054" s="3" t="inlineStr"/>
+    </row>
+    <row r="1055" ht="20" customHeight="1">
+      <c r="A1055" s="2" t="n">
+        <v>1051</v>
+      </c>
+      <c r="B1055" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1055" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="D1055" s="2" t="inlineStr">
+        <is>
+          <t>375124</t>
+        </is>
+      </c>
+      <c r="E1055" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1055" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1055" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1055" s="2" t="inlineStr"/>
+    </row>
+    <row r="1056" ht="20" customHeight="1">
+      <c r="A1056" s="3" t="n">
+        <v>1052</v>
+      </c>
+      <c r="B1056" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1056" s="3" t="n">
+        <v>1359</v>
+      </c>
+      <c r="D1056" s="3" t="inlineStr">
+        <is>
+          <t>375130</t>
+        </is>
+      </c>
+      <c r="E1056" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1056" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1056" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1056" s="3" t="inlineStr"/>
+    </row>
+    <row r="1057" ht="20" customHeight="1">
+      <c r="A1057" s="2" t="n">
+        <v>1053</v>
+      </c>
+      <c r="B1057" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1057" s="2" t="n">
+        <v>1360</v>
+      </c>
+      <c r="D1057" s="2" t="inlineStr">
+        <is>
+          <t>375125</t>
+        </is>
+      </c>
+      <c r="E1057" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1057" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1057" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1057" s="2" t="inlineStr"/>
+    </row>
+    <row r="1058" ht="20" customHeight="1">
+      <c r="A1058" s="3" t="n">
+        <v>1054</v>
+      </c>
+      <c r="B1058" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1058" s="3" t="n">
+        <v>1361</v>
+      </c>
+      <c r="D1058" s="3" t="inlineStr">
+        <is>
+          <t>375126</t>
+        </is>
+      </c>
+      <c r="E1058" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1058" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1058" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1058" s="3" t="inlineStr"/>
+    </row>
+    <row r="1059" ht="20" customHeight="1">
+      <c r="A1059" s="2" t="n">
+        <v>1055</v>
+      </c>
+      <c r="B1059" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1059" s="2" t="n">
+        <v>1362</v>
+      </c>
+      <c r="D1059" s="2" t="inlineStr">
+        <is>
+          <t>375129</t>
+        </is>
+      </c>
+      <c r="E1059" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1059" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1059" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1059" s="2" t="inlineStr"/>
+    </row>
+    <row r="1060" ht="20" customHeight="1">
+      <c r="A1060" s="3" t="n">
+        <v>1056</v>
+      </c>
+      <c r="B1060" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1060" s="3" t="n">
+        <v>1363</v>
+      </c>
+      <c r="D1060" s="3" t="inlineStr">
+        <is>
+          <t>375127</t>
+        </is>
+      </c>
+      <c r="E1060" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1060" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1060" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1060" s="3" t="inlineStr"/>
+    </row>
+    <row r="1061" ht="20" customHeight="1">
+      <c r="A1061" s="2" t="n">
+        <v>1057</v>
+      </c>
+      <c r="B1061" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1061" s="2" t="n">
+        <v>1364</v>
+      </c>
+      <c r="D1061" s="2" t="inlineStr">
+        <is>
+          <t>375636</t>
+        </is>
+      </c>
+      <c r="E1061" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1061" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1061" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1061" s="2" t="inlineStr"/>
+    </row>
+    <row r="1062" ht="20" customHeight="1">
+      <c r="A1062" s="3" t="n">
+        <v>1058</v>
+      </c>
+      <c r="B1062" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1062" s="3" t="n">
+        <v>1365</v>
+      </c>
+      <c r="D1062" s="3" t="inlineStr">
+        <is>
+          <t>375128</t>
+        </is>
+      </c>
+      <c r="E1062" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1062" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1062" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1062" s="3" t="inlineStr"/>
+    </row>
+    <row r="1063" ht="20" customHeight="1">
+      <c r="A1063" s="2" t="n">
+        <v>1059</v>
+      </c>
+      <c r="B1063" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1063" s="2" t="n">
+        <v>1366</v>
+      </c>
+      <c r="D1063" s="2" t="inlineStr">
+        <is>
+          <t>375635</t>
+        </is>
+      </c>
+      <c r="E1063" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1063" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1063" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1063" s="2" t="inlineStr"/>
+    </row>
+    <row r="1064" ht="20" customHeight="1">
+      <c r="A1064" s="3" t="n">
+        <v>1060</v>
+      </c>
+      <c r="B1064" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1064" s="3" t="n">
+        <v>1370</v>
+      </c>
+      <c r="D1064" s="3" t="inlineStr">
+        <is>
+          <t>375132</t>
+        </is>
+      </c>
+      <c r="E1064" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1064" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1064" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1064" s="3" t="inlineStr"/>
+    </row>
+    <row r="1065" ht="20" customHeight="1">
+      <c r="A1065" s="2" t="n">
+        <v>1061</v>
+      </c>
+      <c r="B1065" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1065" s="2" t="n">
+        <v>1371</v>
+      </c>
+      <c r="D1065" s="2" t="inlineStr">
+        <is>
+          <t>375131</t>
+        </is>
+      </c>
+      <c r="E1065" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1065" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1065" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1065" s="2" t="inlineStr"/>
+    </row>
+    <row r="1066" ht="20" customHeight="1">
+      <c r="A1066" s="3" t="n">
+        <v>1062</v>
+      </c>
+      <c r="B1066" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1066" s="3" t="n">
+        <v>1372</v>
+      </c>
+      <c r="D1066" s="3" t="inlineStr">
+        <is>
+          <t>375133</t>
+        </is>
+      </c>
+      <c r="E1066" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1066" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1066" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1066" s="3" t="inlineStr"/>
+    </row>
+    <row r="1067" ht="20" customHeight="1">
+      <c r="A1067" s="2" t="n">
+        <v>1063</v>
+      </c>
+      <c r="B1067" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1067" s="2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="D1067" s="2" t="inlineStr">
+        <is>
+          <t>375623</t>
+        </is>
+      </c>
+      <c r="E1067" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1067" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1067" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1067" s="2" t="inlineStr"/>
+    </row>
+    <row r="1068" ht="20" customHeight="1">
+      <c r="A1068" s="3" t="n">
+        <v>1064</v>
+      </c>
+      <c r="B1068" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="C1068" s="3" t="n">
+        <v>1374</v>
+      </c>
+      <c r="D1068" s="3" t="inlineStr">
+        <is>
+          <t>375624</t>
+        </is>
+      </c>
+      <c r="E1068" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1068" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1068" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1068" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -49740,7 +52681,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -49797,27 +52738,729 @@
         <v>1</v>
       </c>
       <c r="B5" s="2" t="n">
+        <v>1092</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>286842</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1152</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>374575</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1168</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>374895</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1171</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>374443</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1258</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>374897</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1259</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>374896</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1260</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>374665</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>1261</v>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>374666</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
+      <c r="E12" s="3" t="n">
         <v>36</v>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>SELESAI</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1262</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>374667</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1263</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>374668</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1266</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>374669</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1267</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>374898</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1268</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>374444</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1269</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>374953</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1270</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>374951</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1271</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>374670</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1272</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>374954</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1273</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>374952</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1274</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>374336</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1275</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>374572</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1276</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>286841</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1277</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>374574</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1278</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>374573</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1279</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>286791</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1280</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>286790</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1281</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>374671</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1282</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>374442</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -51512,6 +55155,1869 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1283</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>375596</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1284</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>375597</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1285</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>375595</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1286</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>375808</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1287</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>375622</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1288</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>375809</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1289</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>375763</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1290</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>375422</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1291</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>375423</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1292</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>375421</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1293</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>375424</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1294</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>375811</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1295</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>375810</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1296</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr"/>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1297</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1298</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1299</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1300</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1301</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr"/>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1302</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr"/>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1303</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>375852</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1304</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>375600</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1305</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>375854</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1306</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>375599</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1307</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>375598</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1308</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>375851</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1309</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>375853</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1310</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>375637</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1311</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>375638</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1314</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>375639</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1315</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>375806</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1316</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>375812</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1317</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>375814</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1318</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>375813</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1319</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>375306</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1320</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>375805</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1321</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>375807</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1322</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>375307</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1328</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>375120</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1329</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>375626</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1330</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>375628</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1331</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>375625</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1333</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>375629</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1338</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>375630</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1339</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>375631</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1341</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>375627</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1345</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1346</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>375632</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1352</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>375633</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1353</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>375122</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1354</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>375634</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1355</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>375121</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1356</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>375123</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1357</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr"/>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>375124</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1359</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>375130</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1360</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>375125</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1361</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>375126</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1362</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>375129</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1363</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>375127</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1364</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>375636</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1365</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>375128</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1366</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>375635</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1370</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>375132</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>1371</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>375131</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1372</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>375133</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>375623</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1374</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>375624</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
+++ b/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
@@ -42,6 +42,7 @@
     <sheet name="24 September" sheetId="33" state="visible" r:id="rId33"/>
     <sheet name="25 September" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="26 September" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="27 September" sheetId="36" state="visible" r:id="rId36"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1375"/>
+  <dimension ref="A1:H1463"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -41854,24 +41855,24 @@
       </c>
       <c r="B1306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C1306" s="3" t="n">
-        <v>1657</v>
+        <v>1656</v>
       </c>
       <c r="D1306" s="3" t="inlineStr">
         <is>
-          <t>378831</t>
+          <t>380215</t>
         </is>
       </c>
       <c r="E1306" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1306" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1306" s="3" t="inlineStr">
         <is>
@@ -41886,24 +41887,24 @@
       </c>
       <c r="B1307" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="C1307" s="2" t="n">
-        <v>1658</v>
+        <v>1657</v>
       </c>
       <c r="D1307" s="2" t="inlineStr">
         <is>
-          <t>379712</t>
+          <t>378831</t>
         </is>
       </c>
       <c r="E1307" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1307" s="2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1307" s="2" t="inlineStr">
         <is>
@@ -41922,11 +41923,11 @@
         </is>
       </c>
       <c r="C1308" s="3" t="n">
-        <v>1659</v>
+        <v>1658</v>
       </c>
       <c r="D1308" s="3" t="inlineStr">
         <is>
-          <t>379714</t>
+          <t>379712</t>
         </is>
       </c>
       <c r="E1308" s="3" t="inlineStr">
@@ -41954,16 +41955,16 @@
         </is>
       </c>
       <c r="C1309" s="2" t="n">
-        <v>1660</v>
+        <v>1659</v>
       </c>
       <c r="D1309" s="2" t="inlineStr">
         <is>
-          <t>379469</t>
+          <t>379714</t>
         </is>
       </c>
       <c r="E1309" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1309" s="2" t="n">
@@ -41986,20 +41987,20 @@
         </is>
       </c>
       <c r="C1310" s="3" t="n">
-        <v>1661</v>
+        <v>1660</v>
       </c>
       <c r="D1310" s="3" t="inlineStr">
         <is>
-          <t>379467</t>
+          <t>379469</t>
         </is>
       </c>
       <c r="E1310" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1310" s="3" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G1310" s="3" t="inlineStr">
         <is>
@@ -42018,11 +42019,11 @@
         </is>
       </c>
       <c r="C1311" s="2" t="n">
-        <v>1662</v>
+        <v>1661</v>
       </c>
       <c r="D1311" s="2" t="inlineStr">
         <is>
-          <t>379468</t>
+          <t>379467</t>
         </is>
       </c>
       <c r="E1311" s="2" t="inlineStr">
@@ -42050,20 +42051,20 @@
         </is>
       </c>
       <c r="C1312" s="3" t="n">
-        <v>1663</v>
+        <v>1662</v>
       </c>
       <c r="D1312" s="3" t="inlineStr">
         <is>
-          <t>379518</t>
+          <t>379468</t>
         </is>
       </c>
       <c r="E1312" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1312" s="3" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G1312" s="3" t="inlineStr">
         <is>
@@ -42082,11 +42083,11 @@
         </is>
       </c>
       <c r="C1313" s="2" t="n">
-        <v>1664</v>
+        <v>1663</v>
       </c>
       <c r="D1313" s="2" t="inlineStr">
         <is>
-          <t>379519</t>
+          <t>379518</t>
         </is>
       </c>
       <c r="E1313" s="2" t="inlineStr">
@@ -42095,7 +42096,7 @@
         </is>
       </c>
       <c r="F1313" s="2" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G1313" s="2" t="inlineStr">
         <is>
@@ -42114,11 +42115,11 @@
         </is>
       </c>
       <c r="C1314" s="3" t="n">
-        <v>1665</v>
+        <v>1664</v>
       </c>
       <c r="D1314" s="3" t="inlineStr">
         <is>
-          <t>379516</t>
+          <t>379519</t>
         </is>
       </c>
       <c r="E1314" s="3" t="inlineStr">
@@ -42127,7 +42128,7 @@
         </is>
       </c>
       <c r="F1314" s="3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1314" s="3" t="inlineStr">
         <is>
@@ -42146,11 +42147,11 @@
         </is>
       </c>
       <c r="C1315" s="2" t="n">
-        <v>1666</v>
+        <v>1665</v>
       </c>
       <c r="D1315" s="2" t="inlineStr">
         <is>
-          <t>379517</t>
+          <t>379516</t>
         </is>
       </c>
       <c r="E1315" s="2" t="inlineStr">
@@ -42159,7 +42160,7 @@
         </is>
       </c>
       <c r="F1315" s="2" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="G1315" s="2" t="inlineStr">
         <is>
@@ -42178,11 +42179,11 @@
         </is>
       </c>
       <c r="C1316" s="3" t="n">
-        <v>1667</v>
+        <v>1666</v>
       </c>
       <c r="D1316" s="3" t="inlineStr">
         <is>
-          <t>379514</t>
+          <t>379517</t>
         </is>
       </c>
       <c r="E1316" s="3" t="inlineStr">
@@ -42191,7 +42192,7 @@
         </is>
       </c>
       <c r="F1316" s="3" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="G1316" s="3" t="inlineStr">
         <is>
@@ -42210,11 +42211,11 @@
         </is>
       </c>
       <c r="C1317" s="2" t="n">
-        <v>1668</v>
+        <v>1667</v>
       </c>
       <c r="D1317" s="2" t="inlineStr">
         <is>
-          <t>379515</t>
+          <t>379514</t>
         </is>
       </c>
       <c r="E1317" s="2" t="inlineStr">
@@ -42223,7 +42224,7 @@
         </is>
       </c>
       <c r="F1317" s="2" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="G1317" s="2" t="inlineStr">
         <is>
@@ -42242,20 +42243,20 @@
         </is>
       </c>
       <c r="C1318" s="3" t="n">
-        <v>1669</v>
+        <v>1668</v>
       </c>
       <c r="D1318" s="3" t="inlineStr">
         <is>
-          <t>379087</t>
+          <t>379515</t>
         </is>
       </c>
       <c r="E1318" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F1318" s="3" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="G1318" s="3" t="inlineStr">
         <is>
@@ -42274,11 +42275,11 @@
         </is>
       </c>
       <c r="C1319" s="2" t="n">
-        <v>1670</v>
+        <v>1669</v>
       </c>
       <c r="D1319" s="2" t="inlineStr">
         <is>
-          <t>379088</t>
+          <t>379087</t>
         </is>
       </c>
       <c r="E1319" s="2" t="inlineStr">
@@ -42287,7 +42288,7 @@
         </is>
       </c>
       <c r="F1319" s="2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1319" s="2" t="inlineStr">
         <is>
@@ -42306,20 +42307,20 @@
         </is>
       </c>
       <c r="C1320" s="3" t="n">
-        <v>1671</v>
+        <v>1670</v>
       </c>
       <c r="D1320" s="3" t="inlineStr">
         <is>
-          <t>378590</t>
+          <t>379088</t>
         </is>
       </c>
       <c r="E1320" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1320" s="3" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="G1320" s="3" t="inlineStr">
         <is>
@@ -42338,20 +42339,20 @@
         </is>
       </c>
       <c r="C1321" s="2" t="n">
-        <v>1672</v>
+        <v>1671</v>
       </c>
       <c r="D1321" s="2" t="inlineStr">
         <is>
-          <t>379460</t>
+          <t>378590</t>
         </is>
       </c>
       <c r="E1321" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1321" s="2" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G1321" s="2" t="inlineStr">
         <is>
@@ -42370,20 +42371,20 @@
         </is>
       </c>
       <c r="C1322" s="3" t="n">
-        <v>1673</v>
+        <v>1672</v>
       </c>
       <c r="D1322" s="3" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>379460</t>
         </is>
       </c>
       <c r="E1322" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1322" s="3" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1322" s="3" t="inlineStr">
         <is>
@@ -42402,20 +42403,20 @@
         </is>
       </c>
       <c r="C1323" s="2" t="n">
-        <v>1675</v>
+        <v>1673</v>
       </c>
       <c r="D1323" s="2" t="inlineStr">
         <is>
-          <t>377178</t>
+          <t>35142</t>
         </is>
       </c>
       <c r="E1323" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F1323" s="2" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G1323" s="2" t="inlineStr">
         <is>
@@ -42434,20 +42435,20 @@
         </is>
       </c>
       <c r="C1324" s="3" t="n">
-        <v>1676</v>
+        <v>1675</v>
       </c>
       <c r="D1324" s="3" t="inlineStr">
         <is>
-          <t>379459</t>
+          <t>377178</t>
         </is>
       </c>
       <c r="E1324" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1324" s="3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1324" s="3" t="inlineStr">
         <is>
@@ -42466,20 +42467,20 @@
         </is>
       </c>
       <c r="C1325" s="2" t="n">
-        <v>1677</v>
+        <v>1676</v>
       </c>
       <c r="D1325" s="2" t="inlineStr">
         <is>
-          <t>35270</t>
+          <t>379459</t>
         </is>
       </c>
       <c r="E1325" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1325" s="2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G1325" s="2" t="inlineStr">
         <is>
@@ -42498,20 +42499,20 @@
         </is>
       </c>
       <c r="C1326" s="3" t="n">
-        <v>1680</v>
+        <v>1677</v>
       </c>
       <c r="D1326" s="3" t="inlineStr">
         <is>
-          <t>379199</t>
+          <t>35270</t>
         </is>
       </c>
       <c r="E1326" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F1326" s="3" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="G1326" s="3" t="inlineStr">
         <is>
@@ -42530,11 +42531,11 @@
         </is>
       </c>
       <c r="C1327" s="2" t="n">
-        <v>1681</v>
+        <v>1680</v>
       </c>
       <c r="D1327" s="2" t="inlineStr">
         <is>
-          <t>379200</t>
+          <t>379199</t>
         </is>
       </c>
       <c r="E1327" s="2" t="inlineStr">
@@ -42543,7 +42544,7 @@
         </is>
       </c>
       <c r="F1327" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G1327" s="2" t="inlineStr">
         <is>
@@ -42562,20 +42563,20 @@
         </is>
       </c>
       <c r="C1328" s="3" t="n">
-        <v>1682</v>
+        <v>1681</v>
       </c>
       <c r="D1328" s="3" t="inlineStr">
         <is>
-          <t>379701</t>
+          <t>379200</t>
         </is>
       </c>
       <c r="E1328" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1328" s="3" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G1328" s="3" t="inlineStr">
         <is>
@@ -42594,20 +42595,20 @@
         </is>
       </c>
       <c r="C1329" s="2" t="n">
-        <v>1683</v>
+        <v>1682</v>
       </c>
       <c r="D1329" s="2" t="inlineStr">
         <is>
-          <t>378583</t>
+          <t>379701</t>
         </is>
       </c>
       <c r="E1329" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1329" s="2" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G1329" s="2" t="inlineStr">
         <is>
@@ -42626,20 +42627,20 @@
         </is>
       </c>
       <c r="C1330" s="3" t="n">
-        <v>1684</v>
+        <v>1683</v>
       </c>
       <c r="D1330" s="3" t="inlineStr">
         <is>
-          <t>379702</t>
+          <t>378583</t>
         </is>
       </c>
       <c r="E1330" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1330" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1330" s="3" t="inlineStr">
         <is>
@@ -42658,11 +42659,11 @@
         </is>
       </c>
       <c r="C1331" s="2" t="n">
-        <v>1685</v>
+        <v>1684</v>
       </c>
       <c r="D1331" s="2" t="inlineStr">
         <is>
-          <t>379703</t>
+          <t>379702</t>
         </is>
       </c>
       <c r="E1331" s="2" t="inlineStr">
@@ -42671,7 +42672,7 @@
         </is>
       </c>
       <c r="F1331" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1331" s="2" t="inlineStr">
         <is>
@@ -42690,20 +42691,20 @@
         </is>
       </c>
       <c r="C1332" s="3" t="n">
-        <v>1686</v>
+        <v>1685</v>
       </c>
       <c r="D1332" s="3" t="inlineStr">
         <is>
-          <t>378582</t>
+          <t>379703</t>
         </is>
       </c>
       <c r="E1332" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1332" s="3" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G1332" s="3" t="inlineStr">
         <is>
@@ -42722,20 +42723,20 @@
         </is>
       </c>
       <c r="C1333" s="2" t="n">
-        <v>1687</v>
+        <v>1686</v>
       </c>
       <c r="D1333" s="2" t="inlineStr">
         <is>
-          <t>379704</t>
+          <t>378582</t>
         </is>
       </c>
       <c r="E1333" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1333" s="2" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1333" s="2" t="inlineStr">
         <is>
@@ -42754,11 +42755,11 @@
         </is>
       </c>
       <c r="C1334" s="3" t="n">
-        <v>1688</v>
+        <v>1687</v>
       </c>
       <c r="D1334" s="3" t="inlineStr">
         <is>
-          <t>379706</t>
+          <t>379704</t>
         </is>
       </c>
       <c r="E1334" s="3" t="inlineStr">
@@ -42786,11 +42787,11 @@
         </is>
       </c>
       <c r="C1335" s="2" t="n">
-        <v>1689</v>
+        <v>1688</v>
       </c>
       <c r="D1335" s="2" t="inlineStr">
         <is>
-          <t>379705</t>
+          <t>379706</t>
         </is>
       </c>
       <c r="E1335" s="2" t="inlineStr">
@@ -42799,7 +42800,7 @@
         </is>
       </c>
       <c r="F1335" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1335" s="2" t="inlineStr">
         <is>
@@ -42818,11 +42819,11 @@
         </is>
       </c>
       <c r="C1336" s="3" t="n">
-        <v>1693</v>
+        <v>1689</v>
       </c>
       <c r="D1336" s="3" t="inlineStr">
         <is>
-          <t>379709</t>
+          <t>379705</t>
         </is>
       </c>
       <c r="E1336" s="3" t="inlineStr">
@@ -42831,7 +42832,7 @@
         </is>
       </c>
       <c r="F1336" s="3" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1336" s="3" t="inlineStr">
         <is>
@@ -42850,11 +42851,11 @@
         </is>
       </c>
       <c r="C1337" s="2" t="n">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="D1337" s="2" t="inlineStr">
         <is>
-          <t>379710</t>
+          <t>379709</t>
         </is>
       </c>
       <c r="E1337" s="2" t="inlineStr">
@@ -42863,7 +42864,7 @@
         </is>
       </c>
       <c r="F1337" s="2" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1337" s="2" t="inlineStr">
         <is>
@@ -42882,20 +42883,20 @@
         </is>
       </c>
       <c r="C1338" s="3" t="n">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="D1338" s="3" t="inlineStr">
         <is>
-          <t>378588</t>
+          <t>379710</t>
         </is>
       </c>
       <c r="E1338" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1338" s="3" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1338" s="3" t="inlineStr">
         <is>
@@ -42914,20 +42915,20 @@
         </is>
       </c>
       <c r="C1339" s="2" t="n">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="D1339" s="2" t="inlineStr">
         <is>
-          <t>379089</t>
+          <t>378588</t>
         </is>
       </c>
       <c r="E1339" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1339" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G1339" s="2" t="inlineStr">
         <is>
@@ -42946,11 +42947,11 @@
         </is>
       </c>
       <c r="C1340" s="3" t="n">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="D1340" s="3" t="inlineStr">
         <is>
-          <t>379466</t>
+          <t>379089</t>
         </is>
       </c>
       <c r="E1340" s="3" t="inlineStr">
@@ -42978,11 +42979,11 @@
         </is>
       </c>
       <c r="C1341" s="2" t="n">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="D1341" s="2" t="inlineStr">
         <is>
-          <t>379090</t>
+          <t>379466</t>
         </is>
       </c>
       <c r="E1341" s="2" t="inlineStr">
@@ -42991,7 +42992,7 @@
         </is>
       </c>
       <c r="F1341" s="2" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G1341" s="2" t="inlineStr">
         <is>
@@ -43010,20 +43011,20 @@
         </is>
       </c>
       <c r="C1342" s="3" t="n">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="D1342" s="3" t="inlineStr">
         <is>
-          <t>378589</t>
+          <t>379090</t>
         </is>
       </c>
       <c r="E1342" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1342" s="3" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G1342" s="3" t="inlineStr">
         <is>
@@ -43042,11 +43043,11 @@
         </is>
       </c>
       <c r="C1343" s="2" t="n">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="D1343" s="2" t="inlineStr">
         <is>
-          <t>377190</t>
+          <t>378589</t>
         </is>
       </c>
       <c r="E1343" s="2" t="inlineStr">
@@ -43055,7 +43056,7 @@
         </is>
       </c>
       <c r="F1343" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G1343" s="2" t="inlineStr">
         <is>
@@ -43074,11 +43075,11 @@
         </is>
       </c>
       <c r="C1344" s="3" t="n">
-        <v>1701</v>
+        <v>1700</v>
       </c>
       <c r="D1344" s="3" t="inlineStr">
         <is>
-          <t>377188</t>
+          <t>377190</t>
         </is>
       </c>
       <c r="E1344" s="3" t="inlineStr">
@@ -43087,7 +43088,7 @@
         </is>
       </c>
       <c r="F1344" s="3" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1344" s="3" t="inlineStr">
         <is>
@@ -43106,11 +43107,11 @@
         </is>
       </c>
       <c r="C1345" s="2" t="n">
-        <v>1702</v>
+        <v>1701</v>
       </c>
       <c r="D1345" s="2" t="inlineStr">
         <is>
-          <t>377189</t>
+          <t>377188</t>
         </is>
       </c>
       <c r="E1345" s="2" t="inlineStr">
@@ -43119,7 +43120,7 @@
         </is>
       </c>
       <c r="F1345" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1345" s="2" t="inlineStr">
         <is>
@@ -43138,11 +43139,11 @@
         </is>
       </c>
       <c r="C1346" s="3" t="n">
-        <v>1703</v>
+        <v>1702</v>
       </c>
       <c r="D1346" s="3" t="inlineStr">
         <is>
-          <t>377186</t>
+          <t>377189</t>
         </is>
       </c>
       <c r="E1346" s="3" t="inlineStr">
@@ -43151,7 +43152,7 @@
         </is>
       </c>
       <c r="F1346" s="3" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1346" s="3" t="inlineStr">
         <is>
@@ -43170,11 +43171,11 @@
         </is>
       </c>
       <c r="C1347" s="2" t="n">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="D1347" s="2" t="inlineStr">
         <is>
-          <t>377187</t>
+          <t>377186</t>
         </is>
       </c>
       <c r="E1347" s="2" t="inlineStr">
@@ -43202,20 +43203,20 @@
         </is>
       </c>
       <c r="C1348" s="3" t="n">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="D1348" s="3" t="inlineStr">
         <is>
-          <t>377191</t>
+          <t>377187</t>
         </is>
       </c>
       <c r="E1348" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1348" s="3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1348" s="3" t="inlineStr">
         <is>
@@ -43234,20 +43235,20 @@
         </is>
       </c>
       <c r="C1349" s="2" t="n">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="D1349" s="2" t="inlineStr">
         <is>
-          <t>379715</t>
+          <t>377191</t>
         </is>
       </c>
       <c r="E1349" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1349" s="2" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G1349" s="2" t="inlineStr">
         <is>
@@ -43266,20 +43267,20 @@
         </is>
       </c>
       <c r="C1350" s="3" t="n">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="D1350" s="3" t="inlineStr">
         <is>
-          <t>379470</t>
+          <t>379715</t>
         </is>
       </c>
       <c r="E1350" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1350" s="3" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G1350" s="3" t="inlineStr">
         <is>
@@ -43298,20 +43299,20 @@
         </is>
       </c>
       <c r="C1351" s="2" t="n">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="D1351" s="2" t="inlineStr">
         <is>
-          <t>379716</t>
+          <t>379470</t>
         </is>
       </c>
       <c r="E1351" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1351" s="2" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G1351" s="2" t="inlineStr">
         <is>
@@ -43330,16 +43331,16 @@
         </is>
       </c>
       <c r="C1352" s="3" t="n">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="D1352" s="3" t="inlineStr">
         <is>
-          <t>377184</t>
+          <t>379716</t>
         </is>
       </c>
       <c r="E1352" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1352" s="3" t="n">
@@ -43362,20 +43363,20 @@
         </is>
       </c>
       <c r="C1353" s="2" t="n">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="D1353" s="2" t="inlineStr">
         <is>
-          <t>378591</t>
+          <t>377184</t>
         </is>
       </c>
       <c r="E1353" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1353" s="2" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G1353" s="2" t="inlineStr">
         <is>
@@ -43394,20 +43395,20 @@
         </is>
       </c>
       <c r="C1354" s="3" t="n">
-        <v>1712</v>
+        <v>1710</v>
       </c>
       <c r="D1354" s="3" t="inlineStr">
         <is>
-          <t>377194</t>
+          <t>378591</t>
         </is>
       </c>
       <c r="E1354" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1354" s="3" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G1354" s="3" t="inlineStr">
         <is>
@@ -43426,11 +43427,11 @@
         </is>
       </c>
       <c r="C1355" s="2" t="n">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D1355" s="2" t="inlineStr">
         <is>
-          <t>377192</t>
+          <t>377194</t>
         </is>
       </c>
       <c r="E1355" s="2" t="inlineStr">
@@ -43439,7 +43440,7 @@
         </is>
       </c>
       <c r="F1355" s="2" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G1355" s="2" t="inlineStr">
         <is>
@@ -43458,11 +43459,11 @@
         </is>
       </c>
       <c r="C1356" s="3" t="n">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D1356" s="3" t="inlineStr">
         <is>
-          <t>377195</t>
+          <t>377192</t>
         </is>
       </c>
       <c r="E1356" s="3" t="inlineStr">
@@ -43471,7 +43472,7 @@
         </is>
       </c>
       <c r="F1356" s="3" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G1356" s="3" t="inlineStr">
         <is>
@@ -43490,16 +43491,16 @@
         </is>
       </c>
       <c r="C1357" s="2" t="n">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D1357" s="2" t="inlineStr">
         <is>
-          <t>378592</t>
+          <t>377195</t>
         </is>
       </c>
       <c r="E1357" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1357" s="2" t="n">
@@ -43522,20 +43523,20 @@
         </is>
       </c>
       <c r="C1358" s="3" t="n">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="D1358" s="3" t="inlineStr">
         <is>
-          <t>377180</t>
+          <t>378592</t>
         </is>
       </c>
       <c r="E1358" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1358" s="3" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G1358" s="3" t="inlineStr">
         <is>
@@ -43554,11 +43555,11 @@
         </is>
       </c>
       <c r="C1359" s="2" t="n">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D1359" s="2" t="inlineStr">
         <is>
-          <t>377179</t>
+          <t>377180</t>
         </is>
       </c>
       <c r="E1359" s="2" t="inlineStr">
@@ -43586,20 +43587,20 @@
         </is>
       </c>
       <c r="C1360" s="3" t="n">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="D1360" s="3" t="inlineStr">
         <is>
-          <t>379707</t>
+          <t>377179</t>
         </is>
       </c>
       <c r="E1360" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1360" s="3" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G1360" s="3" t="inlineStr">
         <is>
@@ -43618,20 +43619,20 @@
         </is>
       </c>
       <c r="C1361" s="2" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="D1361" s="2" t="inlineStr">
         <is>
-          <t>377183</t>
+          <t>379707</t>
         </is>
       </c>
       <c r="E1361" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1361" s="2" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G1361" s="2" t="inlineStr">
         <is>
@@ -43650,16 +43651,16 @@
         </is>
       </c>
       <c r="C1362" s="3" t="n">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D1362" s="3" t="inlineStr">
         <is>
-          <t>377185</t>
+          <t>377183</t>
         </is>
       </c>
       <c r="E1362" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1362" s="3" t="n">
@@ -43682,20 +43683,20 @@
         </is>
       </c>
       <c r="C1363" s="2" t="n">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D1363" s="2" t="inlineStr">
         <is>
-          <t>377193</t>
+          <t>377185</t>
         </is>
       </c>
       <c r="E1363" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1363" s="2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1363" s="2" t="inlineStr">
         <is>
@@ -43714,20 +43715,20 @@
         </is>
       </c>
       <c r="C1364" s="3" t="n">
-        <v>1724</v>
+        <v>1722</v>
       </c>
       <c r="D1364" s="3" t="inlineStr">
         <is>
-          <t>378585</t>
+          <t>377193</t>
         </is>
       </c>
       <c r="E1364" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1364" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G1364" s="3" t="inlineStr">
         <is>
@@ -43742,24 +43743,24 @@
       </c>
       <c r="B1365" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C1365" s="2" t="n">
-        <v>1725</v>
+        <v>1723</v>
       </c>
       <c r="D1365" s="2" t="inlineStr">
         <is>
-          <t>378584</t>
+          <t>282376</t>
         </is>
       </c>
       <c r="E1365" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1365" s="2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G1365" s="2" t="inlineStr">
         <is>
@@ -43778,20 +43779,20 @@
         </is>
       </c>
       <c r="C1366" s="3" t="n">
-        <v>1726</v>
+        <v>1724</v>
       </c>
       <c r="D1366" s="3" t="inlineStr">
         <is>
-          <t>378593</t>
+          <t>378585</t>
         </is>
       </c>
       <c r="E1366" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1366" s="3" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G1366" s="3" t="inlineStr">
         <is>
@@ -43810,20 +43811,20 @@
         </is>
       </c>
       <c r="C1367" s="2" t="n">
-        <v>1727</v>
+        <v>1725</v>
       </c>
       <c r="D1367" s="2" t="inlineStr">
         <is>
-          <t>379465</t>
+          <t>378584</t>
         </is>
       </c>
       <c r="E1367" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1367" s="2" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G1367" s="2" t="inlineStr">
         <is>
@@ -43842,20 +43843,20 @@
         </is>
       </c>
       <c r="C1368" s="3" t="n">
-        <v>1728</v>
+        <v>1726</v>
       </c>
       <c r="D1368" s="3" t="inlineStr">
         <is>
-          <t>379708</t>
+          <t>378593</t>
         </is>
       </c>
       <c r="E1368" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1368" s="3" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G1368" s="3" t="inlineStr">
         <is>
@@ -43874,20 +43875,20 @@
         </is>
       </c>
       <c r="C1369" s="2" t="n">
-        <v>1729</v>
+        <v>1727</v>
       </c>
       <c r="D1369" s="2" t="inlineStr">
         <is>
-          <t>379461</t>
+          <t>379465</t>
         </is>
       </c>
       <c r="E1369" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1369" s="2" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G1369" s="2" t="inlineStr">
         <is>
@@ -43906,20 +43907,20 @@
         </is>
       </c>
       <c r="C1370" s="3" t="n">
-        <v>1730</v>
+        <v>1728</v>
       </c>
       <c r="D1370" s="3" t="inlineStr">
         <is>
-          <t>377850</t>
+          <t>379708</t>
         </is>
       </c>
       <c r="E1370" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1370" s="3" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G1370" s="3" t="inlineStr">
         <is>
@@ -43938,11 +43939,11 @@
         </is>
       </c>
       <c r="C1371" s="2" t="n">
-        <v>1731</v>
+        <v>1729</v>
       </c>
       <c r="D1371" s="2" t="inlineStr">
         <is>
-          <t>379462</t>
+          <t>379461</t>
         </is>
       </c>
       <c r="E1371" s="2" t="inlineStr">
@@ -43951,7 +43952,7 @@
         </is>
       </c>
       <c r="F1371" s="2" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G1371" s="2" t="inlineStr">
         <is>
@@ -43970,11 +43971,11 @@
         </is>
       </c>
       <c r="C1372" s="3" t="n">
-        <v>1732</v>
+        <v>1730</v>
       </c>
       <c r="D1372" s="3" t="inlineStr">
         <is>
-          <t>379401</t>
+          <t>377850</t>
         </is>
       </c>
       <c r="E1372" s="3" t="inlineStr">
@@ -43983,7 +43984,7 @@
         </is>
       </c>
       <c r="F1372" s="3" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="G1372" s="3" t="inlineStr">
         <is>
@@ -44002,20 +44003,20 @@
         </is>
       </c>
       <c r="C1373" s="2" t="n">
-        <v>1736</v>
+        <v>1731</v>
       </c>
       <c r="D1373" s="2" t="inlineStr">
         <is>
-          <t>378587</t>
+          <t>379462</t>
         </is>
       </c>
       <c r="E1373" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1373" s="2" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="G1373" s="2" t="inlineStr">
         <is>
@@ -44034,20 +44035,20 @@
         </is>
       </c>
       <c r="C1374" s="3" t="n">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="D1374" s="3" t="inlineStr">
         <is>
-          <t>379463</t>
+          <t>379401</t>
         </is>
       </c>
       <c r="E1374" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1374" s="3" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="G1374" s="3" t="inlineStr">
         <is>
@@ -44062,20 +44063,20 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C1375" s="2" t="n">
-        <v>1738</v>
+        <v>1734</v>
       </c>
       <c r="D1375" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>380076</t>
         </is>
       </c>
       <c r="E1375" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1375" s="2" t="n">
@@ -44087,6 +44088,2822 @@
         </is>
       </c>
       <c r="H1375" s="2" t="inlineStr"/>
+    </row>
+    <row r="1376" ht="20" customHeight="1">
+      <c r="A1376" s="3" t="n">
+        <v>1372</v>
+      </c>
+      <c r="B1376" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1376" s="3" t="n">
+        <v>1735</v>
+      </c>
+      <c r="D1376" s="3" t="inlineStr">
+        <is>
+          <t>380075</t>
+        </is>
+      </c>
+      <c r="E1376" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1376" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1376" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1376" s="3" t="inlineStr"/>
+    </row>
+    <row r="1377" ht="20" customHeight="1">
+      <c r="A1377" s="2" t="n">
+        <v>1373</v>
+      </c>
+      <c r="B1377" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C1377" s="2" t="n">
+        <v>1736</v>
+      </c>
+      <c r="D1377" s="2" t="inlineStr">
+        <is>
+          <t>378587</t>
+        </is>
+      </c>
+      <c r="E1377" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1377" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1377" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1377" s="2" t="inlineStr"/>
+    </row>
+    <row r="1378" ht="20" customHeight="1">
+      <c r="A1378" s="3" t="n">
+        <v>1374</v>
+      </c>
+      <c r="B1378" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C1378" s="3" t="n">
+        <v>1737</v>
+      </c>
+      <c r="D1378" s="3" t="inlineStr">
+        <is>
+          <t>379463</t>
+        </is>
+      </c>
+      <c r="E1378" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1378" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1378" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1378" s="3" t="inlineStr"/>
+    </row>
+    <row r="1379" ht="20" customHeight="1">
+      <c r="A1379" s="2" t="n">
+        <v>1375</v>
+      </c>
+      <c r="B1379" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26</t>
+        </is>
+      </c>
+      <c r="C1379" s="2" t="n">
+        <v>1738</v>
+      </c>
+      <c r="D1379" s="2" t="inlineStr">
+        <is>
+          <t>35143</t>
+        </is>
+      </c>
+      <c r="E1379" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F1379" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1379" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1379" s="2" t="inlineStr"/>
+    </row>
+    <row r="1380" ht="20" customHeight="1">
+      <c r="A1380" s="3" t="n">
+        <v>1376</v>
+      </c>
+      <c r="B1380" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1380" s="3" t="n">
+        <v>1740</v>
+      </c>
+      <c r="D1380" s="3" t="inlineStr">
+        <is>
+          <t>380214</t>
+        </is>
+      </c>
+      <c r="E1380" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1380" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1380" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1380" s="3" t="inlineStr"/>
+    </row>
+    <row r="1381" ht="20" customHeight="1">
+      <c r="A1381" s="2" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B1381" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1381" s="2" t="n">
+        <v>1742</v>
+      </c>
+      <c r="D1381" s="2" t="inlineStr">
+        <is>
+          <t>380305</t>
+        </is>
+      </c>
+      <c r="E1381" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1381" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1381" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1381" s="2" t="inlineStr"/>
+    </row>
+    <row r="1382" ht="20" customHeight="1">
+      <c r="A1382" s="3" t="n">
+        <v>1378</v>
+      </c>
+      <c r="B1382" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1382" s="3" t="n">
+        <v>1743</v>
+      </c>
+      <c r="D1382" s="3" t="inlineStr">
+        <is>
+          <t>380310</t>
+        </is>
+      </c>
+      <c r="E1382" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1382" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1382" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1382" s="3" t="inlineStr"/>
+    </row>
+    <row r="1383" ht="20" customHeight="1">
+      <c r="A1383" s="2" t="n">
+        <v>1379</v>
+      </c>
+      <c r="B1383" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1383" s="2" t="n">
+        <v>1744</v>
+      </c>
+      <c r="D1383" s="2" t="inlineStr">
+        <is>
+          <t>380308</t>
+        </is>
+      </c>
+      <c r="E1383" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1383" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1383" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1383" s="2" t="inlineStr"/>
+    </row>
+    <row r="1384" ht="20" customHeight="1">
+      <c r="A1384" s="3" t="n">
+        <v>1380</v>
+      </c>
+      <c r="B1384" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1384" s="3" t="n">
+        <v>1745</v>
+      </c>
+      <c r="D1384" s="3" t="inlineStr">
+        <is>
+          <t>380307</t>
+        </is>
+      </c>
+      <c r="E1384" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1384" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1384" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1384" s="3" t="inlineStr"/>
+    </row>
+    <row r="1385" ht="20" customHeight="1">
+      <c r="A1385" s="2" t="n">
+        <v>1381</v>
+      </c>
+      <c r="B1385" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1385" s="2" t="n">
+        <v>1746</v>
+      </c>
+      <c r="D1385" s="2" t="inlineStr">
+        <is>
+          <t>380311</t>
+        </is>
+      </c>
+      <c r="E1385" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1385" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1385" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1385" s="2" t="inlineStr"/>
+    </row>
+    <row r="1386" ht="20" customHeight="1">
+      <c r="A1386" s="3" t="n">
+        <v>1382</v>
+      </c>
+      <c r="B1386" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1386" s="3" t="n">
+        <v>1747</v>
+      </c>
+      <c r="D1386" s="3" t="inlineStr">
+        <is>
+          <t>380309</t>
+        </is>
+      </c>
+      <c r="E1386" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1386" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1386" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1386" s="3" t="inlineStr"/>
+    </row>
+    <row r="1387" ht="20" customHeight="1">
+      <c r="A1387" s="2" t="n">
+        <v>1383</v>
+      </c>
+      <c r="B1387" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1387" s="2" t="n">
+        <v>1748</v>
+      </c>
+      <c r="D1387" s="2" t="inlineStr">
+        <is>
+          <t>380199</t>
+        </is>
+      </c>
+      <c r="E1387" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1387" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1387" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1387" s="2" t="inlineStr"/>
+    </row>
+    <row r="1388" ht="20" customHeight="1">
+      <c r="A1388" s="3" t="n">
+        <v>1384</v>
+      </c>
+      <c r="B1388" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1388" s="3" t="n">
+        <v>1749</v>
+      </c>
+      <c r="D1388" s="3" t="inlineStr">
+        <is>
+          <t>380217</t>
+        </is>
+      </c>
+      <c r="E1388" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1388" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1388" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1388" s="3" t="inlineStr"/>
+    </row>
+    <row r="1389" ht="20" customHeight="1">
+      <c r="A1389" s="2" t="n">
+        <v>1385</v>
+      </c>
+      <c r="B1389" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1389" s="2" t="n">
+        <v>1750</v>
+      </c>
+      <c r="D1389" s="2" t="inlineStr">
+        <is>
+          <t>380301</t>
+        </is>
+      </c>
+      <c r="E1389" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1389" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1389" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1389" s="2" t="inlineStr"/>
+    </row>
+    <row r="1390" ht="20" customHeight="1">
+      <c r="A1390" s="3" t="n">
+        <v>1386</v>
+      </c>
+      <c r="B1390" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1390" s="3" t="n">
+        <v>1751</v>
+      </c>
+      <c r="D1390" s="3" t="inlineStr">
+        <is>
+          <t>380200</t>
+        </is>
+      </c>
+      <c r="E1390" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1390" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1390" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1390" s="3" t="inlineStr"/>
+    </row>
+    <row r="1391" ht="20" customHeight="1">
+      <c r="A1391" s="2" t="n">
+        <v>1387</v>
+      </c>
+      <c r="B1391" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1391" s="2" t="n">
+        <v>1752</v>
+      </c>
+      <c r="D1391" s="2" t="inlineStr">
+        <is>
+          <t>380303</t>
+        </is>
+      </c>
+      <c r="E1391" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1391" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1391" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1391" s="2" t="inlineStr"/>
+    </row>
+    <row r="1392" ht="20" customHeight="1">
+      <c r="A1392" s="3" t="n">
+        <v>1388</v>
+      </c>
+      <c r="B1392" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1392" s="3" t="n">
+        <v>1753</v>
+      </c>
+      <c r="D1392" s="3" t="inlineStr">
+        <is>
+          <t>380302</t>
+        </is>
+      </c>
+      <c r="E1392" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1392" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1392" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1392" s="3" t="inlineStr"/>
+    </row>
+    <row r="1393" ht="20" customHeight="1">
+      <c r="A1393" s="2" t="n">
+        <v>1389</v>
+      </c>
+      <c r="B1393" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1393" s="2" t="n">
+        <v>1756</v>
+      </c>
+      <c r="D1393" s="2" t="inlineStr">
+        <is>
+          <t>379993</t>
+        </is>
+      </c>
+      <c r="E1393" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1393" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1393" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1393" s="2" t="inlineStr"/>
+    </row>
+    <row r="1394" ht="20" customHeight="1">
+      <c r="A1394" s="3" t="n">
+        <v>1390</v>
+      </c>
+      <c r="B1394" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1394" s="3" t="n">
+        <v>1757</v>
+      </c>
+      <c r="D1394" s="3" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="E1394" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1394" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1394" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1394" s="3" t="inlineStr"/>
+    </row>
+    <row r="1395" ht="20" customHeight="1">
+      <c r="A1395" s="2" t="n">
+        <v>1391</v>
+      </c>
+      <c r="B1395" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1395" s="2" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D1395" s="2" t="inlineStr">
+        <is>
+          <t>380401</t>
+        </is>
+      </c>
+      <c r="E1395" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1395" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1395" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1395" s="2" t="inlineStr"/>
+    </row>
+    <row r="1396" ht="20" customHeight="1">
+      <c r="A1396" s="3" t="n">
+        <v>1392</v>
+      </c>
+      <c r="B1396" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1396" s="3" t="n">
+        <v>1759</v>
+      </c>
+      <c r="D1396" s="3" t="inlineStr">
+        <is>
+          <t>380402</t>
+        </is>
+      </c>
+      <c r="E1396" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1396" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1396" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1396" s="3" t="inlineStr"/>
+    </row>
+    <row r="1397" ht="20" customHeight="1">
+      <c r="A1397" s="2" t="n">
+        <v>1393</v>
+      </c>
+      <c r="B1397" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1397" s="2" t="n">
+        <v>1760</v>
+      </c>
+      <c r="D1397" s="2" t="inlineStr">
+        <is>
+          <t>380221</t>
+        </is>
+      </c>
+      <c r="E1397" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1397" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1397" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1397" s="2" t="inlineStr"/>
+    </row>
+    <row r="1398" ht="20" customHeight="1">
+      <c r="A1398" s="3" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B1398" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1398" s="3" t="n">
+        <v>1761</v>
+      </c>
+      <c r="D1398" s="3" t="inlineStr">
+        <is>
+          <t>380222</t>
+        </is>
+      </c>
+      <c r="E1398" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1398" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1398" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1398" s="3" t="inlineStr"/>
+    </row>
+    <row r="1399" ht="20" customHeight="1">
+      <c r="A1399" s="2" t="n">
+        <v>1395</v>
+      </c>
+      <c r="B1399" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1399" s="2" t="n">
+        <v>1762</v>
+      </c>
+      <c r="D1399" s="2" t="inlineStr">
+        <is>
+          <t>380404</t>
+        </is>
+      </c>
+      <c r="E1399" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1399" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1399" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1399" s="2" t="inlineStr"/>
+    </row>
+    <row r="1400" ht="20" customHeight="1">
+      <c r="A1400" s="3" t="n">
+        <v>1396</v>
+      </c>
+      <c r="B1400" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1400" s="3" t="n">
+        <v>1763</v>
+      </c>
+      <c r="D1400" s="3" t="inlineStr">
+        <is>
+          <t>282377</t>
+        </is>
+      </c>
+      <c r="E1400" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F1400" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1400" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1400" s="3" t="inlineStr"/>
+    </row>
+    <row r="1401" ht="20" customHeight="1">
+      <c r="A1401" s="2" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B1401" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1401" s="2" t="n">
+        <v>1764</v>
+      </c>
+      <c r="D1401" s="2" t="inlineStr">
+        <is>
+          <t>282378</t>
+        </is>
+      </c>
+      <c r="E1401" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F1401" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1401" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1401" s="2" t="inlineStr"/>
+    </row>
+    <row r="1402" ht="20" customHeight="1">
+      <c r="A1402" s="3" t="n">
+        <v>1398</v>
+      </c>
+      <c r="B1402" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1402" s="3" t="n">
+        <v>1765</v>
+      </c>
+      <c r="D1402" s="3" t="inlineStr">
+        <is>
+          <t>380405</t>
+        </is>
+      </c>
+      <c r="E1402" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1402" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1402" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1402" s="3" t="inlineStr"/>
+    </row>
+    <row r="1403" ht="20" customHeight="1">
+      <c r="A1403" s="2" t="n">
+        <v>1399</v>
+      </c>
+      <c r="B1403" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1403" s="2" t="n">
+        <v>1766</v>
+      </c>
+      <c r="D1403" s="2" t="inlineStr">
+        <is>
+          <t>380403</t>
+        </is>
+      </c>
+      <c r="E1403" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1403" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1403" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1403" s="2" t="inlineStr"/>
+    </row>
+    <row r="1404" ht="20" customHeight="1">
+      <c r="A1404" s="3" t="n">
+        <v>1400</v>
+      </c>
+      <c r="B1404" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1404" s="3" t="n">
+        <v>1767</v>
+      </c>
+      <c r="D1404" s="3" t="inlineStr">
+        <is>
+          <t>379421</t>
+        </is>
+      </c>
+      <c r="E1404" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="F1404" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1404" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1404" s="3" t="inlineStr"/>
+    </row>
+    <row r="1405" ht="20" customHeight="1">
+      <c r="A1405" s="2" t="n">
+        <v>1401</v>
+      </c>
+      <c r="B1405" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1405" s="2" t="n">
+        <v>1769</v>
+      </c>
+      <c r="D1405" s="2" t="inlineStr">
+        <is>
+          <t>380410</t>
+        </is>
+      </c>
+      <c r="E1405" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1405" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1405" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1405" s="2" t="inlineStr"/>
+    </row>
+    <row r="1406" ht="20" customHeight="1">
+      <c r="A1406" s="3" t="n">
+        <v>1402</v>
+      </c>
+      <c r="B1406" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1406" s="3" t="n">
+        <v>1770</v>
+      </c>
+      <c r="D1406" s="3" t="inlineStr">
+        <is>
+          <t>380406</t>
+        </is>
+      </c>
+      <c r="E1406" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1406" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1406" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1406" s="3" t="inlineStr"/>
+    </row>
+    <row r="1407" ht="20" customHeight="1">
+      <c r="A1407" s="2" t="n">
+        <v>1403</v>
+      </c>
+      <c r="B1407" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1407" s="2" t="n">
+        <v>1771</v>
+      </c>
+      <c r="D1407" s="2" t="inlineStr">
+        <is>
+          <t>379420</t>
+        </is>
+      </c>
+      <c r="E1407" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1407" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1407" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1407" s="2" t="inlineStr"/>
+    </row>
+    <row r="1408" ht="20" customHeight="1">
+      <c r="A1408" s="3" t="n">
+        <v>1404</v>
+      </c>
+      <c r="B1408" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1408" s="3" t="n">
+        <v>1772</v>
+      </c>
+      <c r="D1408" s="3" t="inlineStr">
+        <is>
+          <t>379422</t>
+        </is>
+      </c>
+      <c r="E1408" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1408" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1408" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1408" s="3" t="inlineStr"/>
+    </row>
+    <row r="1409" ht="20" customHeight="1">
+      <c r="A1409" s="2" t="n">
+        <v>1405</v>
+      </c>
+      <c r="B1409" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1409" s="2" t="n">
+        <v>1773</v>
+      </c>
+      <c r="D1409" s="2" t="inlineStr">
+        <is>
+          <t>380411</t>
+        </is>
+      </c>
+      <c r="E1409" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1409" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1409" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1409" s="2" t="inlineStr"/>
+    </row>
+    <row r="1410" ht="20" customHeight="1">
+      <c r="A1410" s="3" t="n">
+        <v>1406</v>
+      </c>
+      <c r="B1410" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1410" s="3" t="n">
+        <v>1774</v>
+      </c>
+      <c r="D1410" s="3" t="inlineStr">
+        <is>
+          <t>380409</t>
+        </is>
+      </c>
+      <c r="E1410" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1410" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1410" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1410" s="3" t="inlineStr"/>
+    </row>
+    <row r="1411" ht="20" customHeight="1">
+      <c r="A1411" s="2" t="n">
+        <v>1407</v>
+      </c>
+      <c r="B1411" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1411" s="2" t="n">
+        <v>1775</v>
+      </c>
+      <c r="D1411" s="2" t="inlineStr">
+        <is>
+          <t>380407</t>
+        </is>
+      </c>
+      <c r="E1411" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1411" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1411" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1411" s="2" t="inlineStr"/>
+    </row>
+    <row r="1412" ht="20" customHeight="1">
+      <c r="A1412" s="3" t="n">
+        <v>1408</v>
+      </c>
+      <c r="B1412" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1412" s="3" t="n">
+        <v>1776</v>
+      </c>
+      <c r="D1412" s="3" t="inlineStr">
+        <is>
+          <t>380408</t>
+        </is>
+      </c>
+      <c r="E1412" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1412" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1412" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1412" s="3" t="inlineStr"/>
+    </row>
+    <row r="1413" ht="20" customHeight="1">
+      <c r="A1413" s="2" t="n">
+        <v>1409</v>
+      </c>
+      <c r="B1413" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1413" s="2" t="n">
+        <v>1777</v>
+      </c>
+      <c r="D1413" s="2" t="inlineStr">
+        <is>
+          <t>380077</t>
+        </is>
+      </c>
+      <c r="E1413" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1413" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1413" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1413" s="2" t="inlineStr"/>
+    </row>
+    <row r="1414" ht="20" customHeight="1">
+      <c r="A1414" s="3" t="n">
+        <v>1410</v>
+      </c>
+      <c r="B1414" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1414" s="3" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D1414" s="3" t="inlineStr">
+        <is>
+          <t>380306</t>
+        </is>
+      </c>
+      <c r="E1414" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1414" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1414" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1414" s="3" t="inlineStr"/>
+    </row>
+    <row r="1415" ht="20" customHeight="1">
+      <c r="A1415" s="2" t="n">
+        <v>1411</v>
+      </c>
+      <c r="B1415" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1415" s="2" t="n">
+        <v>1779</v>
+      </c>
+      <c r="D1415" s="2" t="inlineStr">
+        <is>
+          <t>380078</t>
+        </is>
+      </c>
+      <c r="E1415" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1415" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1415" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1415" s="2" t="inlineStr"/>
+    </row>
+    <row r="1416" ht="20" customHeight="1">
+      <c r="A1416" s="3" t="n">
+        <v>1412</v>
+      </c>
+      <c r="B1416" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1416" s="3" t="n">
+        <v>1780</v>
+      </c>
+      <c r="D1416" s="3" t="inlineStr">
+        <is>
+          <t>380224</t>
+        </is>
+      </c>
+      <c r="E1416" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1416" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1416" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1416" s="3" t="inlineStr"/>
+    </row>
+    <row r="1417" ht="20" customHeight="1">
+      <c r="A1417" s="2" t="n">
+        <v>1413</v>
+      </c>
+      <c r="B1417" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1417" s="2" t="n">
+        <v>1781</v>
+      </c>
+      <c r="D1417" s="2" t="inlineStr">
+        <is>
+          <t>380223</t>
+        </is>
+      </c>
+      <c r="E1417" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1417" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1417" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1417" s="2" t="inlineStr"/>
+    </row>
+    <row r="1418" ht="20" customHeight="1">
+      <c r="A1418" s="3" t="n">
+        <v>1414</v>
+      </c>
+      <c r="B1418" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1418" s="3" t="n">
+        <v>1782</v>
+      </c>
+      <c r="D1418" s="3" t="inlineStr">
+        <is>
+          <t>380312</t>
+        </is>
+      </c>
+      <c r="E1418" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1418" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1418" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1418" s="3" t="inlineStr"/>
+    </row>
+    <row r="1419" ht="20" customHeight="1">
+      <c r="A1419" s="2" t="n">
+        <v>1415</v>
+      </c>
+      <c r="B1419" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1419" s="2" t="n">
+        <v>1783</v>
+      </c>
+      <c r="D1419" s="2" t="inlineStr">
+        <is>
+          <t>380226</t>
+        </is>
+      </c>
+      <c r="E1419" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1419" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1419" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1419" s="2" t="inlineStr"/>
+    </row>
+    <row r="1420" ht="20" customHeight="1">
+      <c r="A1420" s="3" t="n">
+        <v>1416</v>
+      </c>
+      <c r="B1420" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1420" s="3" t="n">
+        <v>1784</v>
+      </c>
+      <c r="D1420" s="3" t="inlineStr">
+        <is>
+          <t>380225</t>
+        </is>
+      </c>
+      <c r="E1420" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1420" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1420" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1420" s="3" t="inlineStr"/>
+    </row>
+    <row r="1421" ht="20" customHeight="1">
+      <c r="A1421" s="2" t="n">
+        <v>1417</v>
+      </c>
+      <c r="B1421" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1421" s="2" t="n">
+        <v>1785</v>
+      </c>
+      <c r="D1421" s="2" t="inlineStr">
+        <is>
+          <t>380228</t>
+        </is>
+      </c>
+      <c r="E1421" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1421" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="G1421" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1421" s="2" t="inlineStr"/>
+    </row>
+    <row r="1422" ht="20" customHeight="1">
+      <c r="A1422" s="3" t="n">
+        <v>1418</v>
+      </c>
+      <c r="B1422" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1422" s="3" t="n">
+        <v>1786</v>
+      </c>
+      <c r="D1422" s="3" t="inlineStr">
+        <is>
+          <t>380412</t>
+        </is>
+      </c>
+      <c r="E1422" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1422" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1422" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1422" s="3" t="inlineStr"/>
+    </row>
+    <row r="1423" ht="20" customHeight="1">
+      <c r="A1423" s="2" t="n">
+        <v>1419</v>
+      </c>
+      <c r="B1423" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1423" s="2" t="n">
+        <v>1787</v>
+      </c>
+      <c r="D1423" s="2" t="inlineStr">
+        <is>
+          <t>380227</t>
+        </is>
+      </c>
+      <c r="E1423" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1423" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1423" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1423" s="2" t="inlineStr"/>
+    </row>
+    <row r="1424" ht="20" customHeight="1">
+      <c r="A1424" s="3" t="n">
+        <v>1420</v>
+      </c>
+      <c r="B1424" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1424" s="3" t="n">
+        <v>1788</v>
+      </c>
+      <c r="D1424" s="3" t="inlineStr">
+        <is>
+          <t>380079</t>
+        </is>
+      </c>
+      <c r="E1424" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1424" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1424" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1424" s="3" t="inlineStr"/>
+    </row>
+    <row r="1425" ht="20" customHeight="1">
+      <c r="A1425" s="2" t="n">
+        <v>1421</v>
+      </c>
+      <c r="B1425" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1425" s="2" t="n">
+        <v>1789</v>
+      </c>
+      <c r="D1425" s="2" t="inlineStr">
+        <is>
+          <t>380231</t>
+        </is>
+      </c>
+      <c r="E1425" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1425" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1425" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1425" s="2" t="inlineStr"/>
+    </row>
+    <row r="1426" ht="20" customHeight="1">
+      <c r="A1426" s="3" t="n">
+        <v>1422</v>
+      </c>
+      <c r="B1426" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1426" s="3" t="n">
+        <v>1790</v>
+      </c>
+      <c r="D1426" s="3" t="inlineStr">
+        <is>
+          <t>380235</t>
+        </is>
+      </c>
+      <c r="E1426" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1426" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1426" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1426" s="3" t="inlineStr"/>
+    </row>
+    <row r="1427" ht="20" customHeight="1">
+      <c r="A1427" s="2" t="n">
+        <v>1423</v>
+      </c>
+      <c r="B1427" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1427" s="2" t="n">
+        <v>1791</v>
+      </c>
+      <c r="D1427" s="2" t="inlineStr">
+        <is>
+          <t>380229</t>
+        </is>
+      </c>
+      <c r="E1427" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1427" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1427" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1427" s="2" t="inlineStr"/>
+    </row>
+    <row r="1428" ht="20" customHeight="1">
+      <c r="A1428" s="3" t="n">
+        <v>1424</v>
+      </c>
+      <c r="B1428" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1428" s="3" t="n">
+        <v>1792</v>
+      </c>
+      <c r="D1428" s="3" t="inlineStr">
+        <is>
+          <t>380232</t>
+        </is>
+      </c>
+      <c r="E1428" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1428" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1428" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1428" s="3" t="inlineStr"/>
+    </row>
+    <row r="1429" ht="20" customHeight="1">
+      <c r="A1429" s="2" t="n">
+        <v>1425</v>
+      </c>
+      <c r="B1429" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1429" s="2" t="n">
+        <v>1793</v>
+      </c>
+      <c r="D1429" s="2" t="inlineStr">
+        <is>
+          <t>380314</t>
+        </is>
+      </c>
+      <c r="E1429" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1429" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1429" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1429" s="2" t="inlineStr"/>
+    </row>
+    <row r="1430" ht="20" customHeight="1">
+      <c r="A1430" s="3" t="n">
+        <v>1426</v>
+      </c>
+      <c r="B1430" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1430" s="3" t="n">
+        <v>1794</v>
+      </c>
+      <c r="D1430" s="3" t="inlineStr">
+        <is>
+          <t>380313</t>
+        </is>
+      </c>
+      <c r="E1430" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1430" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1430" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1430" s="3" t="inlineStr"/>
+    </row>
+    <row r="1431" ht="20" customHeight="1">
+      <c r="A1431" s="2" t="n">
+        <v>1427</v>
+      </c>
+      <c r="B1431" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1431" s="2" t="n">
+        <v>1796</v>
+      </c>
+      <c r="D1431" s="2" t="inlineStr">
+        <is>
+          <t>380230</t>
+        </is>
+      </c>
+      <c r="E1431" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1431" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1431" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1431" s="2" t="inlineStr"/>
+    </row>
+    <row r="1432" ht="20" customHeight="1">
+      <c r="A1432" s="3" t="n">
+        <v>1428</v>
+      </c>
+      <c r="B1432" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1432" s="3" t="n">
+        <v>1797</v>
+      </c>
+      <c r="D1432" s="3" t="inlineStr">
+        <is>
+          <t>380080</t>
+        </is>
+      </c>
+      <c r="E1432" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1432" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1432" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1432" s="3" t="inlineStr"/>
+    </row>
+    <row r="1433" ht="20" customHeight="1">
+      <c r="A1433" s="2" t="n">
+        <v>1429</v>
+      </c>
+      <c r="B1433" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1433" s="2" t="n">
+        <v>1798</v>
+      </c>
+      <c r="D1433" s="2" t="inlineStr">
+        <is>
+          <t>380234</t>
+        </is>
+      </c>
+      <c r="E1433" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1433" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1433" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1433" s="2" t="inlineStr"/>
+    </row>
+    <row r="1434" ht="20" customHeight="1">
+      <c r="A1434" s="3" t="n">
+        <v>1430</v>
+      </c>
+      <c r="B1434" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1434" s="3" t="n">
+        <v>1799</v>
+      </c>
+      <c r="D1434" s="3" t="inlineStr">
+        <is>
+          <t>380233</t>
+        </is>
+      </c>
+      <c r="E1434" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1434" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1434" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1434" s="3" t="inlineStr"/>
+    </row>
+    <row r="1435" ht="20" customHeight="1">
+      <c r="A1435" s="2" t="n">
+        <v>1431</v>
+      </c>
+      <c r="B1435" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1435" s="2" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D1435" s="2" t="inlineStr">
+        <is>
+          <t>379413</t>
+        </is>
+      </c>
+      <c r="E1435" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1435" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1435" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1435" s="2" t="inlineStr"/>
+    </row>
+    <row r="1436" ht="20" customHeight="1">
+      <c r="A1436" s="3" t="n">
+        <v>1432</v>
+      </c>
+      <c r="B1436" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1436" s="3" t="n">
+        <v>1803</v>
+      </c>
+      <c r="D1436" s="3" t="inlineStr">
+        <is>
+          <t>379412</t>
+        </is>
+      </c>
+      <c r="E1436" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1436" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1436" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1436" s="3" t="inlineStr"/>
+    </row>
+    <row r="1437" ht="20" customHeight="1">
+      <c r="A1437" s="2" t="n">
+        <v>1433</v>
+      </c>
+      <c r="B1437" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1437" s="2" t="n">
+        <v>1804</v>
+      </c>
+      <c r="D1437" s="2" t="inlineStr">
+        <is>
+          <t>379415</t>
+        </is>
+      </c>
+      <c r="E1437" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1437" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1437" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1437" s="2" t="inlineStr"/>
+    </row>
+    <row r="1438" ht="20" customHeight="1">
+      <c r="A1438" s="3" t="n">
+        <v>1434</v>
+      </c>
+      <c r="B1438" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1438" s="3" t="n">
+        <v>1805</v>
+      </c>
+      <c r="D1438" s="3" t="inlineStr">
+        <is>
+          <t>379414</t>
+        </is>
+      </c>
+      <c r="E1438" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="F1438" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1438" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1438" s="3" t="inlineStr"/>
+    </row>
+    <row r="1439" ht="20" customHeight="1">
+      <c r="A1439" s="2" t="n">
+        <v>1435</v>
+      </c>
+      <c r="B1439" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1439" s="2" t="n">
+        <v>1806</v>
+      </c>
+      <c r="D1439" s="2" t="inlineStr">
+        <is>
+          <t>379416</t>
+        </is>
+      </c>
+      <c r="E1439" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1439" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1439" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1439" s="2" t="inlineStr"/>
+    </row>
+    <row r="1440" ht="20" customHeight="1">
+      <c r="A1440" s="3" t="n">
+        <v>1436</v>
+      </c>
+      <c r="B1440" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1440" s="3" t="n">
+        <v>1811</v>
+      </c>
+      <c r="D1440" s="3" t="inlineStr">
+        <is>
+          <t>379991</t>
+        </is>
+      </c>
+      <c r="E1440" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1440" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1440" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1440" s="3" t="inlineStr"/>
+    </row>
+    <row r="1441" ht="20" customHeight="1">
+      <c r="A1441" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="B1441" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1441" s="2" t="n">
+        <v>1812</v>
+      </c>
+      <c r="D1441" s="2" t="inlineStr">
+        <is>
+          <t>379989</t>
+        </is>
+      </c>
+      <c r="E1441" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1441" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1441" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1441" s="2" t="inlineStr"/>
+    </row>
+    <row r="1442" ht="20" customHeight="1">
+      <c r="A1442" s="3" t="n">
+        <v>1438</v>
+      </c>
+      <c r="B1442" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1442" s="3" t="n">
+        <v>1813</v>
+      </c>
+      <c r="D1442" s="3" t="inlineStr">
+        <is>
+          <t>379988</t>
+        </is>
+      </c>
+      <c r="E1442" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1442" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1442" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1442" s="3" t="inlineStr"/>
+    </row>
+    <row r="1443" ht="20" customHeight="1">
+      <c r="A1443" s="2" t="n">
+        <v>1439</v>
+      </c>
+      <c r="B1443" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1443" s="2" t="n">
+        <v>1814</v>
+      </c>
+      <c r="D1443" s="2" t="inlineStr">
+        <is>
+          <t>379990</t>
+        </is>
+      </c>
+      <c r="E1443" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1443" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1443" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1443" s="2" t="inlineStr"/>
+    </row>
+    <row r="1444" ht="20" customHeight="1">
+      <c r="A1444" s="3" t="n">
+        <v>1440</v>
+      </c>
+      <c r="B1444" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1444" s="3" t="n">
+        <v>1815</v>
+      </c>
+      <c r="D1444" s="3" t="inlineStr">
+        <is>
+          <t>379992</t>
+        </is>
+      </c>
+      <c r="E1444" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1444" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1444" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1444" s="3" t="inlineStr"/>
+    </row>
+    <row r="1445" ht="20" customHeight="1">
+      <c r="A1445" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="B1445" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1445" s="2" t="n">
+        <v>1816</v>
+      </c>
+      <c r="D1445" s="2" t="inlineStr">
+        <is>
+          <t>380216</t>
+        </is>
+      </c>
+      <c r="E1445" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1445" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1445" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1445" s="2" t="inlineStr"/>
+    </row>
+    <row r="1446" ht="20" customHeight="1">
+      <c r="A1446" s="3" t="n">
+        <v>1442</v>
+      </c>
+      <c r="B1446" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1446" s="3" t="n">
+        <v>1822</v>
+      </c>
+      <c r="D1446" s="3" t="inlineStr">
+        <is>
+          <t>379994</t>
+        </is>
+      </c>
+      <c r="E1446" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1446" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1446" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1446" s="3" t="inlineStr"/>
+    </row>
+    <row r="1447" ht="20" customHeight="1">
+      <c r="A1447" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="B1447" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1447" s="2" t="n">
+        <v>1823</v>
+      </c>
+      <c r="D1447" s="2" t="inlineStr">
+        <is>
+          <t>379995</t>
+        </is>
+      </c>
+      <c r="E1447" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1447" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1447" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1447" s="2" t="inlineStr"/>
+    </row>
+    <row r="1448" ht="20" customHeight="1">
+      <c r="A1448" s="3" t="n">
+        <v>1444</v>
+      </c>
+      <c r="B1448" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1448" s="3" t="n">
+        <v>1824</v>
+      </c>
+      <c r="D1448" s="3" t="inlineStr">
+        <is>
+          <t>379986</t>
+        </is>
+      </c>
+      <c r="E1448" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1448" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1448" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1448" s="3" t="inlineStr"/>
+    </row>
+    <row r="1449" ht="20" customHeight="1">
+      <c r="A1449" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="B1449" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1449" s="2" t="n">
+        <v>1825</v>
+      </c>
+      <c r="D1449" s="2" t="inlineStr">
+        <is>
+          <t>379996</t>
+        </is>
+      </c>
+      <c r="E1449" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1449" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1449" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1449" s="2" t="inlineStr"/>
+    </row>
+    <row r="1450" ht="20" customHeight="1">
+      <c r="A1450" s="3" t="n">
+        <v>1446</v>
+      </c>
+      <c r="B1450" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1450" s="3" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D1450" s="3" t="inlineStr">
+        <is>
+          <t>380304</t>
+        </is>
+      </c>
+      <c r="E1450" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1450" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1450" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1450" s="3" t="inlineStr"/>
+    </row>
+    <row r="1451" ht="20" customHeight="1">
+      <c r="A1451" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="B1451" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1451" s="2" t="n">
+        <v>1827</v>
+      </c>
+      <c r="D1451" s="2" t="inlineStr">
+        <is>
+          <t>379419</t>
+        </is>
+      </c>
+      <c r="E1451" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1451" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1451" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1451" s="2" t="inlineStr"/>
+    </row>
+    <row r="1452" ht="20" customHeight="1">
+      <c r="A1452" s="3" t="n">
+        <v>1448</v>
+      </c>
+      <c r="B1452" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1452" s="3" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D1452" s="3" t="inlineStr">
+        <is>
+          <t>379418</t>
+        </is>
+      </c>
+      <c r="E1452" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1452" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1452" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1452" s="3" t="inlineStr"/>
+    </row>
+    <row r="1453" ht="20" customHeight="1">
+      <c r="A1453" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="B1453" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1453" s="2" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D1453" s="2" t="inlineStr">
+        <is>
+          <t>379417</t>
+        </is>
+      </c>
+      <c r="E1453" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1453" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1453" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1453" s="2" t="inlineStr"/>
+    </row>
+    <row r="1454" ht="20" customHeight="1">
+      <c r="A1454" s="3" t="n">
+        <v>1450</v>
+      </c>
+      <c r="B1454" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1454" s="3" t="n">
+        <v>1831</v>
+      </c>
+      <c r="D1454" s="3" t="inlineStr">
+        <is>
+          <t>380220</t>
+        </is>
+      </c>
+      <c r="E1454" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1454" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1454" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1454" s="3" t="inlineStr"/>
+    </row>
+    <row r="1455" ht="20" customHeight="1">
+      <c r="A1455" s="2" t="n">
+        <v>1451</v>
+      </c>
+      <c r="B1455" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1455" s="2" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D1455" s="2" t="inlineStr">
+        <is>
+          <t>379997</t>
+        </is>
+      </c>
+      <c r="E1455" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1455" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1455" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1455" s="2" t="inlineStr"/>
+    </row>
+    <row r="1456" ht="20" customHeight="1">
+      <c r="A1456" s="3" t="n">
+        <v>1452</v>
+      </c>
+      <c r="B1456" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1456" s="3" t="n">
+        <v>1833</v>
+      </c>
+      <c r="D1456" s="3" t="inlineStr">
+        <is>
+          <t>380218</t>
+        </is>
+      </c>
+      <c r="E1456" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1456" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1456" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1456" s="3" t="inlineStr"/>
+    </row>
+    <row r="1457" ht="20" customHeight="1">
+      <c r="A1457" s="2" t="n">
+        <v>1453</v>
+      </c>
+      <c r="B1457" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1457" s="2" t="n">
+        <v>1834</v>
+      </c>
+      <c r="D1457" s="2" t="inlineStr">
+        <is>
+          <t>379999</t>
+        </is>
+      </c>
+      <c r="E1457" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1457" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1457" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1457" s="2" t="inlineStr"/>
+    </row>
+    <row r="1458" ht="20" customHeight="1">
+      <c r="A1458" s="3" t="n">
+        <v>1454</v>
+      </c>
+      <c r="B1458" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1458" s="3" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D1458" s="3" t="inlineStr">
+        <is>
+          <t>380219</t>
+        </is>
+      </c>
+      <c r="E1458" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1458" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1458" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1458" s="3" t="inlineStr"/>
+    </row>
+    <row r="1459" ht="20" customHeight="1">
+      <c r="A1459" s="2" t="n">
+        <v>1455</v>
+      </c>
+      <c r="B1459" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1459" s="2" t="n">
+        <v>1836</v>
+      </c>
+      <c r="D1459" s="2" t="inlineStr">
+        <is>
+          <t>379998</t>
+        </is>
+      </c>
+      <c r="E1459" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1459" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1459" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1459" s="2" t="inlineStr"/>
+    </row>
+    <row r="1460" ht="20" customHeight="1">
+      <c r="A1460" s="3" t="n">
+        <v>1456</v>
+      </c>
+      <c r="B1460" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1460" s="3" t="n">
+        <v>1837</v>
+      </c>
+      <c r="D1460" s="3" t="inlineStr">
+        <is>
+          <t>379985</t>
+        </is>
+      </c>
+      <c r="E1460" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1460" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1460" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1460" s="3" t="inlineStr"/>
+    </row>
+    <row r="1461" ht="20" customHeight="1">
+      <c r="A1461" s="2" t="n">
+        <v>1457</v>
+      </c>
+      <c r="B1461" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1461" s="2" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D1461" s="2" t="inlineStr">
+        <is>
+          <t>379987</t>
+        </is>
+      </c>
+      <c r="E1461" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1461" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1461" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1461" s="2" t="inlineStr"/>
+    </row>
+    <row r="1462" ht="20" customHeight="1">
+      <c r="A1462" s="3" t="n">
+        <v>1458</v>
+      </c>
+      <c r="B1462" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1462" s="3" t="n">
+        <v>1839</v>
+      </c>
+      <c r="D1462" s="3" t="inlineStr">
+        <is>
+          <t>379410</t>
+        </is>
+      </c>
+      <c r="E1462" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1462" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1462" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1462" s="3" t="inlineStr"/>
+    </row>
+    <row r="1463" ht="20" customHeight="1">
+      <c r="A1463" s="2" t="n">
+        <v>1459</v>
+      </c>
+      <c r="B1463" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1463" s="2" t="n">
+        <v>1841</v>
+      </c>
+      <c r="D1463" s="2" t="inlineStr">
+        <is>
+          <t>379411</t>
+        </is>
+      </c>
+      <c r="E1463" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1463" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1463" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1463" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -75509,6 +78326,2445 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G92"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1656</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>380215</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1723</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>282376</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1734</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>380076</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1735</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>380075</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1740</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>380214</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1742</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>380305</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1743</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>380310</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1744</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>380308</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1745</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>380307</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1746</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>380311</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1747</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>380309</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1748</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>380199</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1749</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>380217</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1750</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>380301</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1751</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>380200</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1752</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>380303</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>380302</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1756</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>379993</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1757</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>380000</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1758</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>380401</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1759</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>380402</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1760</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>380221</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1761</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>380222</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1762</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>380404</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1763</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>282377</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1764</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>282378</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1765</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>380405</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1766</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>380403</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1767</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>379421</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1769</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>380410</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1770</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>380406</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1771</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>379420</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1772</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>379422</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1773</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>380411</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1774</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>380409</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1775</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>380407</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1776</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>380408</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1777</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>380077</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1778</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>380306</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1779</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>380078</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1780</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>380224</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1781</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>380223</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>380312</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1783</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>380226</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1784</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>380225</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1785</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>380228</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>41</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1786</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>380412</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1787</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>380227</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>380079</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1789</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>380231</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1790</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>380235</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1791</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>380229</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1792</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>380232</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1793</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>380314</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1794</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>380313</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1796</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>380230</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1797</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>380080</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1798</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>380234</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1799</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>380233</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>379413</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1803</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>379412</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1804</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>379415</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1805</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>379414</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1806</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>379416</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+    </row>
+    <row r="69" ht="20" customHeight="1">
+      <c r="A69" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>1811</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>379991</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr"/>
+    </row>
+    <row r="70" ht="20" customHeight="1">
+      <c r="A70" s="3" t="n">
+        <v>66</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>379989</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr"/>
+    </row>
+    <row r="71" ht="20" customHeight="1">
+      <c r="A71" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>1813</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>379988</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr"/>
+    </row>
+    <row r="72" ht="20" customHeight="1">
+      <c r="A72" s="3" t="n">
+        <v>68</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v>1814</v>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>379990</t>
+        </is>
+      </c>
+      <c r="D72" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F72" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr"/>
+    </row>
+    <row r="73" ht="20" customHeight="1">
+      <c r="A73" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>1815</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>379992</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr"/>
+    </row>
+    <row r="74" ht="20" customHeight="1">
+      <c r="A74" s="3" t="n">
+        <v>70</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v>1816</v>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>380216</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F74" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G74" s="3" t="inlineStr"/>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="A75" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>1822</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>379994</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+    </row>
+    <row r="76" ht="20" customHeight="1">
+      <c r="A76" s="3" t="n">
+        <v>72</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v>1823</v>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>379995</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F76" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G76" s="3" t="inlineStr"/>
+    </row>
+    <row r="77" ht="20" customHeight="1">
+      <c r="A77" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>1824</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>379986</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr"/>
+    </row>
+    <row r="78" ht="20" customHeight="1">
+      <c r="A78" s="3" t="n">
+        <v>74</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v>1825</v>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>379996</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F78" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G78" s="3" t="inlineStr"/>
+    </row>
+    <row r="79" ht="20" customHeight="1">
+      <c r="A79" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>1826</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>380304</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr"/>
+    </row>
+    <row r="80" ht="20" customHeight="1">
+      <c r="A80" s="3" t="n">
+        <v>76</v>
+      </c>
+      <c r="B80" s="3" t="n">
+        <v>1827</v>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>379419</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F80" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G80" s="3" t="inlineStr"/>
+    </row>
+    <row r="81" ht="20" customHeight="1">
+      <c r="A81" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>379418</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr"/>
+    </row>
+    <row r="82" ht="20" customHeight="1">
+      <c r="A82" s="3" t="n">
+        <v>78</v>
+      </c>
+      <c r="B82" s="3" t="n">
+        <v>1829</v>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>379417</t>
+        </is>
+      </c>
+      <c r="D82" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F82" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr"/>
+    </row>
+    <row r="83" ht="20" customHeight="1">
+      <c r="A83" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>1831</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>380220</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr"/>
+    </row>
+    <row r="84" ht="20" customHeight="1">
+      <c r="A84" s="3" t="n">
+        <v>80</v>
+      </c>
+      <c r="B84" s="3" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>379997</t>
+        </is>
+      </c>
+      <c r="D84" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F84" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr"/>
+    </row>
+    <row r="85" ht="20" customHeight="1">
+      <c r="A85" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>1833</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>380218</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr"/>
+    </row>
+    <row r="86" ht="20" customHeight="1">
+      <c r="A86" s="3" t="n">
+        <v>82</v>
+      </c>
+      <c r="B86" s="3" t="n">
+        <v>1834</v>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>379999</t>
+        </is>
+      </c>
+      <c r="D86" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F86" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr"/>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="A87" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>1835</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>380219</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr"/>
+    </row>
+    <row r="88" ht="20" customHeight="1">
+      <c r="A88" s="3" t="n">
+        <v>84</v>
+      </c>
+      <c r="B88" s="3" t="n">
+        <v>1836</v>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>379998</t>
+        </is>
+      </c>
+      <c r="D88" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F88" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr"/>
+    </row>
+    <row r="89" ht="20" customHeight="1">
+      <c r="A89" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>1837</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>379985</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr"/>
+    </row>
+    <row r="90" ht="20" customHeight="1">
+      <c r="A90" s="3" t="n">
+        <v>86</v>
+      </c>
+      <c r="B90" s="3" t="n">
+        <v>1838</v>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>379987</t>
+        </is>
+      </c>
+      <c r="D90" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F90" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr"/>
+    </row>
+    <row r="91" ht="20" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>1839</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>379410</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr"/>
+    </row>
+    <row r="92" ht="20" customHeight="1">
+      <c r="A92" s="3" t="n">
+        <v>88</v>
+      </c>
+      <c r="B92" s="3" t="n">
+        <v>1841</v>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>379411</t>
+        </is>
+      </c>
+      <c r="D92" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F92" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
+++ b/Dokumen_Rekap_NoGud_Barkot_Kg.xlsx
@@ -43,6 +43,7 @@
     <sheet name="25 September" sheetId="34" state="visible" r:id="rId34"/>
     <sheet name="26 September" sheetId="35" state="visible" r:id="rId35"/>
     <sheet name="27 September" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="28 September" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -491,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1463"/>
+  <dimension ref="A1:H1526"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -43423,24 +43424,24 @@
       </c>
       <c r="B1355" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1355" s="2" t="n">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="D1355" s="2" t="inlineStr">
         <is>
-          <t>377194</t>
+          <t>282379</t>
         </is>
       </c>
       <c r="E1355" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1355" s="2" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1355" s="2" t="inlineStr">
         <is>
@@ -43459,11 +43460,11 @@
         </is>
       </c>
       <c r="C1356" s="3" t="n">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="D1356" s="3" t="inlineStr">
         <is>
-          <t>377192</t>
+          <t>377194</t>
         </is>
       </c>
       <c r="E1356" s="3" t="inlineStr">
@@ -43472,7 +43473,7 @@
         </is>
       </c>
       <c r="F1356" s="3" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G1356" s="3" t="inlineStr">
         <is>
@@ -43491,11 +43492,11 @@
         </is>
       </c>
       <c r="C1357" s="2" t="n">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="D1357" s="2" t="inlineStr">
         <is>
-          <t>377195</t>
+          <t>377192</t>
         </is>
       </c>
       <c r="E1357" s="2" t="inlineStr">
@@ -43504,7 +43505,7 @@
         </is>
       </c>
       <c r="F1357" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G1357" s="2" t="inlineStr">
         <is>
@@ -43523,16 +43524,16 @@
         </is>
       </c>
       <c r="C1358" s="3" t="n">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="D1358" s="3" t="inlineStr">
         <is>
-          <t>378592</t>
+          <t>377195</t>
         </is>
       </c>
       <c r="E1358" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1358" s="3" t="n">
@@ -43555,20 +43556,20 @@
         </is>
       </c>
       <c r="C1359" s="2" t="n">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="D1359" s="2" t="inlineStr">
         <is>
-          <t>377180</t>
+          <t>378592</t>
         </is>
       </c>
       <c r="E1359" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1359" s="2" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G1359" s="2" t="inlineStr">
         <is>
@@ -43587,11 +43588,11 @@
         </is>
       </c>
       <c r="C1360" s="3" t="n">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="D1360" s="3" t="inlineStr">
         <is>
-          <t>377179</t>
+          <t>377180</t>
         </is>
       </c>
       <c r="E1360" s="3" t="inlineStr">
@@ -43619,20 +43620,20 @@
         </is>
       </c>
       <c r="C1361" s="2" t="n">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="D1361" s="2" t="inlineStr">
         <is>
-          <t>379707</t>
+          <t>377179</t>
         </is>
       </c>
       <c r="E1361" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1361" s="2" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="G1361" s="2" t="inlineStr">
         <is>
@@ -43651,20 +43652,20 @@
         </is>
       </c>
       <c r="C1362" s="3" t="n">
-        <v>1720</v>
+        <v>1718</v>
       </c>
       <c r="D1362" s="3" t="inlineStr">
         <is>
-          <t>377183</t>
+          <t>379707</t>
         </is>
       </c>
       <c r="E1362" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1362" s="3" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="G1362" s="3" t="inlineStr">
         <is>
@@ -43683,16 +43684,16 @@
         </is>
       </c>
       <c r="C1363" s="2" t="n">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="D1363" s="2" t="inlineStr">
         <is>
-          <t>377185</t>
+          <t>377183</t>
         </is>
       </c>
       <c r="E1363" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1363" s="2" t="n">
@@ -43715,20 +43716,20 @@
         </is>
       </c>
       <c r="C1364" s="3" t="n">
-        <v>1722</v>
+        <v>1721</v>
       </c>
       <c r="D1364" s="3" t="inlineStr">
         <is>
-          <t>377193</t>
+          <t>377185</t>
         </is>
       </c>
       <c r="E1364" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1364" s="3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1364" s="3" t="inlineStr">
         <is>
@@ -43743,15 +43744,15 @@
       </c>
       <c r="B1365" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C1365" s="2" t="n">
-        <v>1723</v>
+        <v>1722</v>
       </c>
       <c r="D1365" s="2" t="inlineStr">
         <is>
-          <t>282376</t>
+          <t>377193</t>
         </is>
       </c>
       <c r="E1365" s="2" t="inlineStr">
@@ -43760,7 +43761,7 @@
         </is>
       </c>
       <c r="F1365" s="2" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="G1365" s="2" t="inlineStr">
         <is>
@@ -43775,24 +43776,24 @@
       </c>
       <c r="B1366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C1366" s="3" t="n">
-        <v>1724</v>
+        <v>1723</v>
       </c>
       <c r="D1366" s="3" t="inlineStr">
         <is>
-          <t>378585</t>
+          <t>282376</t>
         </is>
       </c>
       <c r="E1366" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1366" s="3" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G1366" s="3" t="inlineStr">
         <is>
@@ -43811,20 +43812,20 @@
         </is>
       </c>
       <c r="C1367" s="2" t="n">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="D1367" s="2" t="inlineStr">
         <is>
-          <t>378584</t>
+          <t>378585</t>
         </is>
       </c>
       <c r="E1367" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1367" s="2" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="G1367" s="2" t="inlineStr">
         <is>
@@ -43843,20 +43844,20 @@
         </is>
       </c>
       <c r="C1368" s="3" t="n">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="D1368" s="3" t="inlineStr">
         <is>
-          <t>378593</t>
+          <t>378584</t>
         </is>
       </c>
       <c r="E1368" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1368" s="3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1368" s="3" t="inlineStr">
         <is>
@@ -43875,20 +43876,20 @@
         </is>
       </c>
       <c r="C1369" s="2" t="n">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="D1369" s="2" t="inlineStr">
         <is>
-          <t>379465</t>
+          <t>378593</t>
         </is>
       </c>
       <c r="E1369" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1369" s="2" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G1369" s="2" t="inlineStr">
         <is>
@@ -43907,11 +43908,11 @@
         </is>
       </c>
       <c r="C1370" s="3" t="n">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="D1370" s="3" t="inlineStr">
         <is>
-          <t>379708</t>
+          <t>379465</t>
         </is>
       </c>
       <c r="E1370" s="3" t="inlineStr">
@@ -43920,7 +43921,7 @@
         </is>
       </c>
       <c r="F1370" s="3" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G1370" s="3" t="inlineStr">
         <is>
@@ -43939,20 +43940,20 @@
         </is>
       </c>
       <c r="C1371" s="2" t="n">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="D1371" s="2" t="inlineStr">
         <is>
-          <t>379461</t>
+          <t>379708</t>
         </is>
       </c>
       <c r="E1371" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1371" s="2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1371" s="2" t="inlineStr">
         <is>
@@ -43971,11 +43972,11 @@
         </is>
       </c>
       <c r="C1372" s="3" t="n">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="D1372" s="3" t="inlineStr">
         <is>
-          <t>377850</t>
+          <t>379461</t>
         </is>
       </c>
       <c r="E1372" s="3" t="inlineStr">
@@ -43984,7 +43985,7 @@
         </is>
       </c>
       <c r="F1372" s="3" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="G1372" s="3" t="inlineStr">
         <is>
@@ -44003,11 +44004,11 @@
         </is>
       </c>
       <c r="C1373" s="2" t="n">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="D1373" s="2" t="inlineStr">
         <is>
-          <t>379462</t>
+          <t>377850</t>
         </is>
       </c>
       <c r="E1373" s="2" t="inlineStr">
@@ -44016,7 +44017,7 @@
         </is>
       </c>
       <c r="F1373" s="2" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G1373" s="2" t="inlineStr">
         <is>
@@ -44035,11 +44036,11 @@
         </is>
       </c>
       <c r="C1374" s="3" t="n">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="D1374" s="3" t="inlineStr">
         <is>
-          <t>379401</t>
+          <t>379462</t>
         </is>
       </c>
       <c r="E1374" s="3" t="inlineStr">
@@ -44048,7 +44049,7 @@
         </is>
       </c>
       <c r="F1374" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G1374" s="3" t="inlineStr">
         <is>
@@ -44063,20 +44064,20 @@
       </c>
       <c r="B1375" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C1375" s="2" t="n">
-        <v>1734</v>
+        <v>1732</v>
       </c>
       <c r="D1375" s="2" t="inlineStr">
         <is>
-          <t>380076</t>
+          <t>379401</t>
         </is>
       </c>
       <c r="E1375" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1375" s="2" t="n">
@@ -44099,11 +44100,11 @@
         </is>
       </c>
       <c r="C1376" s="3" t="n">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="D1376" s="3" t="inlineStr">
         <is>
-          <t>380075</t>
+          <t>380076</t>
         </is>
       </c>
       <c r="E1376" s="3" t="inlineStr">
@@ -44112,7 +44113,7 @@
         </is>
       </c>
       <c r="F1376" s="3" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="G1376" s="3" t="inlineStr">
         <is>
@@ -44127,24 +44128,24 @@
       </c>
       <c r="B1377" s="2" t="inlineStr">
         <is>
-          <t>2026-09-26</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="C1377" s="2" t="n">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="D1377" s="2" t="inlineStr">
         <is>
-          <t>378587</t>
+          <t>380075</t>
         </is>
       </c>
       <c r="E1377" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1377" s="2" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G1377" s="2" t="inlineStr">
         <is>
@@ -44163,11 +44164,11 @@
         </is>
       </c>
       <c r="C1378" s="3" t="n">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="D1378" s="3" t="inlineStr">
         <is>
-          <t>379463</t>
+          <t>378587</t>
         </is>
       </c>
       <c r="E1378" s="3" t="inlineStr">
@@ -44176,7 +44177,7 @@
         </is>
       </c>
       <c r="F1378" s="3" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G1378" s="3" t="inlineStr">
         <is>
@@ -44195,20 +44196,20 @@
         </is>
       </c>
       <c r="C1379" s="2" t="n">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="D1379" s="2" t="inlineStr">
         <is>
-          <t>35143</t>
+          <t>379463</t>
         </is>
       </c>
       <c r="E1379" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1379" s="2" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="G1379" s="2" t="inlineStr">
         <is>
@@ -44223,24 +44224,24 @@
       </c>
       <c r="B1380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-26</t>
         </is>
       </c>
       <c r="C1380" s="3" t="n">
-        <v>1740</v>
+        <v>1738</v>
       </c>
       <c r="D1380" s="3" t="inlineStr">
         <is>
-          <t>380214</t>
+          <t>35143</t>
         </is>
       </c>
       <c r="E1380" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1380" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G1380" s="3" t="inlineStr">
         <is>
@@ -44255,24 +44256,24 @@
       </c>
       <c r="B1381" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1381" s="2" t="n">
-        <v>1742</v>
+        <v>1739</v>
       </c>
       <c r="D1381" s="2" t="inlineStr">
         <is>
-          <t>380305</t>
+          <t>380901</t>
         </is>
       </c>
       <c r="E1381" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1381" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1381" s="2" t="inlineStr">
         <is>
@@ -44291,11 +44292,11 @@
         </is>
       </c>
       <c r="C1382" s="3" t="n">
-        <v>1743</v>
+        <v>1740</v>
       </c>
       <c r="D1382" s="3" t="inlineStr">
         <is>
-          <t>380310</t>
+          <t>380214</t>
         </is>
       </c>
       <c r="E1382" s="3" t="inlineStr">
@@ -44304,7 +44305,7 @@
         </is>
       </c>
       <c r="F1382" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G1382" s="3" t="inlineStr">
         <is>
@@ -44323,11 +44324,11 @@
         </is>
       </c>
       <c r="C1383" s="2" t="n">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="D1383" s="2" t="inlineStr">
         <is>
-          <t>380308</t>
+          <t>380305</t>
         </is>
       </c>
       <c r="E1383" s="2" t="inlineStr">
@@ -44336,7 +44337,7 @@
         </is>
       </c>
       <c r="F1383" s="2" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G1383" s="2" t="inlineStr">
         <is>
@@ -44355,11 +44356,11 @@
         </is>
       </c>
       <c r="C1384" s="3" t="n">
-        <v>1745</v>
+        <v>1743</v>
       </c>
       <c r="D1384" s="3" t="inlineStr">
         <is>
-          <t>380307</t>
+          <t>380310</t>
         </is>
       </c>
       <c r="E1384" s="3" t="inlineStr">
@@ -44368,7 +44369,7 @@
         </is>
       </c>
       <c r="F1384" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1384" s="3" t="inlineStr">
         <is>
@@ -44387,11 +44388,11 @@
         </is>
       </c>
       <c r="C1385" s="2" t="n">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="D1385" s="2" t="inlineStr">
         <is>
-          <t>380311</t>
+          <t>380308</t>
         </is>
       </c>
       <c r="E1385" s="2" t="inlineStr">
@@ -44400,7 +44401,7 @@
         </is>
       </c>
       <c r="F1385" s="2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1385" s="2" t="inlineStr">
         <is>
@@ -44419,11 +44420,11 @@
         </is>
       </c>
       <c r="C1386" s="3" t="n">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="D1386" s="3" t="inlineStr">
         <is>
-          <t>380309</t>
+          <t>380307</t>
         </is>
       </c>
       <c r="E1386" s="3" t="inlineStr">
@@ -44432,7 +44433,7 @@
         </is>
       </c>
       <c r="F1386" s="3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G1386" s="3" t="inlineStr">
         <is>
@@ -44451,11 +44452,11 @@
         </is>
       </c>
       <c r="C1387" s="2" t="n">
-        <v>1748</v>
+        <v>1746</v>
       </c>
       <c r="D1387" s="2" t="inlineStr">
         <is>
-          <t>380199</t>
+          <t>380311</t>
         </is>
       </c>
       <c r="E1387" s="2" t="inlineStr">
@@ -44464,7 +44465,7 @@
         </is>
       </c>
       <c r="F1387" s="2" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="G1387" s="2" t="inlineStr">
         <is>
@@ -44483,11 +44484,11 @@
         </is>
       </c>
       <c r="C1388" s="3" t="n">
-        <v>1749</v>
+        <v>1747</v>
       </c>
       <c r="D1388" s="3" t="inlineStr">
         <is>
-          <t>380217</t>
+          <t>380309</t>
         </is>
       </c>
       <c r="E1388" s="3" t="inlineStr">
@@ -44496,7 +44497,7 @@
         </is>
       </c>
       <c r="F1388" s="3" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G1388" s="3" t="inlineStr">
         <is>
@@ -44515,11 +44516,11 @@
         </is>
       </c>
       <c r="C1389" s="2" t="n">
-        <v>1750</v>
+        <v>1748</v>
       </c>
       <c r="D1389" s="2" t="inlineStr">
         <is>
-          <t>380301</t>
+          <t>380199</t>
         </is>
       </c>
       <c r="E1389" s="2" t="inlineStr">
@@ -44528,7 +44529,7 @@
         </is>
       </c>
       <c r="F1389" s="2" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G1389" s="2" t="inlineStr">
         <is>
@@ -44547,11 +44548,11 @@
         </is>
       </c>
       <c r="C1390" s="3" t="n">
-        <v>1751</v>
+        <v>1749</v>
       </c>
       <c r="D1390" s="3" t="inlineStr">
         <is>
-          <t>380200</t>
+          <t>380217</t>
         </is>
       </c>
       <c r="E1390" s="3" t="inlineStr">
@@ -44560,7 +44561,7 @@
         </is>
       </c>
       <c r="F1390" s="3" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G1390" s="3" t="inlineStr">
         <is>
@@ -44579,20 +44580,20 @@
         </is>
       </c>
       <c r="C1391" s="2" t="n">
-        <v>1752</v>
+        <v>1750</v>
       </c>
       <c r="D1391" s="2" t="inlineStr">
         <is>
-          <t>380303</t>
+          <t>380301</t>
         </is>
       </c>
       <c r="E1391" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1391" s="2" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G1391" s="2" t="inlineStr">
         <is>
@@ -44611,11 +44612,11 @@
         </is>
       </c>
       <c r="C1392" s="3" t="n">
-        <v>1753</v>
+        <v>1751</v>
       </c>
       <c r="D1392" s="3" t="inlineStr">
         <is>
-          <t>380302</t>
+          <t>380200</t>
         </is>
       </c>
       <c r="E1392" s="3" t="inlineStr">
@@ -44624,7 +44625,7 @@
         </is>
       </c>
       <c r="F1392" s="3" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="G1392" s="3" t="inlineStr">
         <is>
@@ -44643,20 +44644,20 @@
         </is>
       </c>
       <c r="C1393" s="2" t="n">
-        <v>1756</v>
+        <v>1752</v>
       </c>
       <c r="D1393" s="2" t="inlineStr">
         <is>
-          <t>379993</t>
+          <t>380303</t>
         </is>
       </c>
       <c r="E1393" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F1393" s="2" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="G1393" s="2" t="inlineStr">
         <is>
@@ -44675,20 +44676,20 @@
         </is>
       </c>
       <c r="C1394" s="3" t="n">
-        <v>1757</v>
+        <v>1753</v>
       </c>
       <c r="D1394" s="3" t="inlineStr">
         <is>
-          <t>380000</t>
+          <t>380302</t>
         </is>
       </c>
       <c r="E1394" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1394" s="3" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="G1394" s="3" t="inlineStr">
         <is>
@@ -44703,24 +44704,24 @@
       </c>
       <c r="B1395" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1395" s="2" t="n">
-        <v>1758</v>
+        <v>1754</v>
       </c>
       <c r="D1395" s="2" t="inlineStr">
         <is>
-          <t>380401</t>
+          <t>282385</t>
         </is>
       </c>
       <c r="E1395" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1395" s="2" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G1395" s="2" t="inlineStr">
         <is>
@@ -44735,24 +44736,24 @@
       </c>
       <c r="B1396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1396" s="3" t="n">
-        <v>1759</v>
+        <v>1755</v>
       </c>
       <c r="D1396" s="3" t="inlineStr">
         <is>
-          <t>380402</t>
+          <t>282380</t>
         </is>
       </c>
       <c r="E1396" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1396" s="3" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G1396" s="3" t="inlineStr">
         <is>
@@ -44771,20 +44772,20 @@
         </is>
       </c>
       <c r="C1397" s="2" t="n">
-        <v>1760</v>
+        <v>1756</v>
       </c>
       <c r="D1397" s="2" t="inlineStr">
         <is>
-          <t>380221</t>
+          <t>379993</t>
         </is>
       </c>
       <c r="E1397" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F1397" s="2" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G1397" s="2" t="inlineStr">
         <is>
@@ -44803,20 +44804,20 @@
         </is>
       </c>
       <c r="C1398" s="3" t="n">
-        <v>1761</v>
+        <v>1757</v>
       </c>
       <c r="D1398" s="3" t="inlineStr">
         <is>
-          <t>380222</t>
+          <t>380000</t>
         </is>
       </c>
       <c r="E1398" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1398" s="3" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="G1398" s="3" t="inlineStr">
         <is>
@@ -44835,20 +44836,20 @@
         </is>
       </c>
       <c r="C1399" s="2" t="n">
-        <v>1762</v>
+        <v>1758</v>
       </c>
       <c r="D1399" s="2" t="inlineStr">
         <is>
-          <t>380404</t>
+          <t>380401</t>
         </is>
       </c>
       <c r="E1399" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F1399" s="2" t="n">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="G1399" s="2" t="inlineStr">
         <is>
@@ -44867,20 +44868,20 @@
         </is>
       </c>
       <c r="C1400" s="3" t="n">
-        <v>1763</v>
+        <v>1759</v>
       </c>
       <c r="D1400" s="3" t="inlineStr">
         <is>
-          <t>282377</t>
+          <t>380402</t>
         </is>
       </c>
       <c r="E1400" s="3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F1400" s="3" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="G1400" s="3" t="inlineStr">
         <is>
@@ -44899,20 +44900,20 @@
         </is>
       </c>
       <c r="C1401" s="2" t="n">
-        <v>1764</v>
+        <v>1760</v>
       </c>
       <c r="D1401" s="2" t="inlineStr">
         <is>
-          <t>282378</t>
+          <t>380221</t>
         </is>
       </c>
       <c r="E1401" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1401" s="2" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="G1401" s="2" t="inlineStr">
         <is>
@@ -44931,20 +44932,20 @@
         </is>
       </c>
       <c r="C1402" s="3" t="n">
-        <v>1765</v>
+        <v>1761</v>
       </c>
       <c r="D1402" s="3" t="inlineStr">
         <is>
-          <t>380405</t>
+          <t>380222</t>
         </is>
       </c>
       <c r="E1402" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F1402" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1402" s="3" t="inlineStr">
         <is>
@@ -44963,20 +44964,20 @@
         </is>
       </c>
       <c r="C1403" s="2" t="n">
-        <v>1766</v>
+        <v>1762</v>
       </c>
       <c r="D1403" s="2" t="inlineStr">
         <is>
-          <t>380403</t>
+          <t>380404</t>
         </is>
       </c>
       <c r="E1403" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1403" s="2" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="G1403" s="2" t="inlineStr">
         <is>
@@ -44995,11 +44996,11 @@
         </is>
       </c>
       <c r="C1404" s="3" t="n">
-        <v>1767</v>
+        <v>1763</v>
       </c>
       <c r="D1404" s="3" t="inlineStr">
         <is>
-          <t>379421</t>
+          <t>282377</t>
         </is>
       </c>
       <c r="E1404" s="3" t="inlineStr">
@@ -45008,7 +45009,7 @@
         </is>
       </c>
       <c r="F1404" s="3" t="n">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="G1404" s="3" t="inlineStr">
         <is>
@@ -45027,20 +45028,20 @@
         </is>
       </c>
       <c r="C1405" s="2" t="n">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="D1405" s="2" t="inlineStr">
         <is>
-          <t>380410</t>
+          <t>282378</t>
         </is>
       </c>
       <c r="E1405" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F1405" s="2" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="G1405" s="2" t="inlineStr">
         <is>
@@ -45059,11 +45060,11 @@
         </is>
       </c>
       <c r="C1406" s="3" t="n">
-        <v>1770</v>
+        <v>1765</v>
       </c>
       <c r="D1406" s="3" t="inlineStr">
         <is>
-          <t>380406</t>
+          <t>380405</t>
         </is>
       </c>
       <c r="E1406" s="3" t="inlineStr">
@@ -45072,7 +45073,7 @@
         </is>
       </c>
       <c r="F1406" s="3" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G1406" s="3" t="inlineStr">
         <is>
@@ -45091,16 +45092,16 @@
         </is>
       </c>
       <c r="C1407" s="2" t="n">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="D1407" s="2" t="inlineStr">
         <is>
-          <t>379420</t>
+          <t>380403</t>
         </is>
       </c>
       <c r="E1407" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1407" s="2" t="n">
@@ -45123,20 +45124,20 @@
         </is>
       </c>
       <c r="C1408" s="3" t="n">
-        <v>1772</v>
+        <v>1767</v>
       </c>
       <c r="D1408" s="3" t="inlineStr">
         <is>
-          <t>379422</t>
+          <t>379421</t>
         </is>
       </c>
       <c r="E1408" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>55</t>
         </is>
       </c>
       <c r="F1408" s="3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G1408" s="3" t="inlineStr">
         <is>
@@ -45155,20 +45156,20 @@
         </is>
       </c>
       <c r="C1409" s="2" t="n">
-        <v>1773</v>
+        <v>1769</v>
       </c>
       <c r="D1409" s="2" t="inlineStr">
         <is>
-          <t>380411</t>
+          <t>380410</t>
         </is>
       </c>
       <c r="E1409" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1409" s="2" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G1409" s="2" t="inlineStr">
         <is>
@@ -45187,20 +45188,20 @@
         </is>
       </c>
       <c r="C1410" s="3" t="n">
-        <v>1774</v>
+        <v>1770</v>
       </c>
       <c r="D1410" s="3" t="inlineStr">
         <is>
-          <t>380409</t>
+          <t>380406</t>
         </is>
       </c>
       <c r="E1410" s="3" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1410" s="3" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G1410" s="3" t="inlineStr">
         <is>
@@ -45219,20 +45220,20 @@
         </is>
       </c>
       <c r="C1411" s="2" t="n">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="D1411" s="2" t="inlineStr">
         <is>
-          <t>380407</t>
+          <t>379420</t>
         </is>
       </c>
       <c r="E1411" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1411" s="2" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="G1411" s="2" t="inlineStr">
         <is>
@@ -45251,20 +45252,20 @@
         </is>
       </c>
       <c r="C1412" s="3" t="n">
-        <v>1776</v>
+        <v>1772</v>
       </c>
       <c r="D1412" s="3" t="inlineStr">
         <is>
-          <t>380408</t>
+          <t>379422</t>
         </is>
       </c>
       <c r="E1412" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>60</t>
         </is>
       </c>
       <c r="F1412" s="3" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="G1412" s="3" t="inlineStr">
         <is>
@@ -45283,20 +45284,20 @@
         </is>
       </c>
       <c r="C1413" s="2" t="n">
-        <v>1777</v>
+        <v>1773</v>
       </c>
       <c r="D1413" s="2" t="inlineStr">
         <is>
-          <t>380077</t>
+          <t>380411</t>
         </is>
       </c>
       <c r="E1413" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F1413" s="2" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="G1413" s="2" t="inlineStr">
         <is>
@@ -45315,20 +45316,20 @@
         </is>
       </c>
       <c r="C1414" s="3" t="n">
-        <v>1778</v>
+        <v>1774</v>
       </c>
       <c r="D1414" s="3" t="inlineStr">
         <is>
-          <t>380306</t>
+          <t>380409</t>
         </is>
       </c>
       <c r="E1414" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>63</t>
         </is>
       </c>
       <c r="F1414" s="3" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G1414" s="3" t="inlineStr">
         <is>
@@ -45347,20 +45348,20 @@
         </is>
       </c>
       <c r="C1415" s="2" t="n">
-        <v>1779</v>
+        <v>1775</v>
       </c>
       <c r="D1415" s="2" t="inlineStr">
         <is>
-          <t>380078</t>
+          <t>380407</t>
         </is>
       </c>
       <c r="E1415" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1415" s="2" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G1415" s="2" t="inlineStr">
         <is>
@@ -45379,20 +45380,20 @@
         </is>
       </c>
       <c r="C1416" s="3" t="n">
-        <v>1780</v>
+        <v>1776</v>
       </c>
       <c r="D1416" s="3" t="inlineStr">
         <is>
-          <t>380224</t>
+          <t>380408</t>
         </is>
       </c>
       <c r="E1416" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1416" s="3" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G1416" s="3" t="inlineStr">
         <is>
@@ -45411,20 +45412,20 @@
         </is>
       </c>
       <c r="C1417" s="2" t="n">
-        <v>1781</v>
+        <v>1777</v>
       </c>
       <c r="D1417" s="2" t="inlineStr">
         <is>
-          <t>380223</t>
+          <t>380077</t>
         </is>
       </c>
       <c r="E1417" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1417" s="2" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="G1417" s="2" t="inlineStr">
         <is>
@@ -45443,20 +45444,20 @@
         </is>
       </c>
       <c r="C1418" s="3" t="n">
-        <v>1782</v>
+        <v>1778</v>
       </c>
       <c r="D1418" s="3" t="inlineStr">
         <is>
-          <t>380312</t>
+          <t>380306</t>
         </is>
       </c>
       <c r="E1418" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1418" s="3" t="n">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="G1418" s="3" t="inlineStr">
         <is>
@@ -45475,11 +45476,11 @@
         </is>
       </c>
       <c r="C1419" s="2" t="n">
-        <v>1783</v>
+        <v>1779</v>
       </c>
       <c r="D1419" s="2" t="inlineStr">
         <is>
-          <t>380226</t>
+          <t>380078</t>
         </is>
       </c>
       <c r="E1419" s="2" t="inlineStr">
@@ -45488,7 +45489,7 @@
         </is>
       </c>
       <c r="F1419" s="2" t="n">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G1419" s="2" t="inlineStr">
         <is>
@@ -45507,11 +45508,11 @@
         </is>
       </c>
       <c r="C1420" s="3" t="n">
-        <v>1784</v>
+        <v>1780</v>
       </c>
       <c r="D1420" s="3" t="inlineStr">
         <is>
-          <t>380225</t>
+          <t>380224</t>
         </is>
       </c>
       <c r="E1420" s="3" t="inlineStr">
@@ -45520,7 +45521,7 @@
         </is>
       </c>
       <c r="F1420" s="3" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="G1420" s="3" t="inlineStr">
         <is>
@@ -45539,20 +45540,20 @@
         </is>
       </c>
       <c r="C1421" s="2" t="n">
-        <v>1785</v>
+        <v>1781</v>
       </c>
       <c r="D1421" s="2" t="inlineStr">
         <is>
-          <t>380228</t>
+          <t>380223</t>
         </is>
       </c>
       <c r="E1421" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1421" s="2" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G1421" s="2" t="inlineStr">
         <is>
@@ -45571,20 +45572,20 @@
         </is>
       </c>
       <c r="C1422" s="3" t="n">
-        <v>1786</v>
+        <v>1782</v>
       </c>
       <c r="D1422" s="3" t="inlineStr">
         <is>
-          <t>380412</t>
+          <t>380312</t>
         </is>
       </c>
       <c r="E1422" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1422" s="3" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G1422" s="3" t="inlineStr">
         <is>
@@ -45603,20 +45604,20 @@
         </is>
       </c>
       <c r="C1423" s="2" t="n">
-        <v>1787</v>
+        <v>1783</v>
       </c>
       <c r="D1423" s="2" t="inlineStr">
         <is>
-          <t>380227</t>
+          <t>380226</t>
         </is>
       </c>
       <c r="E1423" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>67</t>
         </is>
       </c>
       <c r="F1423" s="2" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G1423" s="2" t="inlineStr">
         <is>
@@ -45635,11 +45636,11 @@
         </is>
       </c>
       <c r="C1424" s="3" t="n">
-        <v>1788</v>
+        <v>1784</v>
       </c>
       <c r="D1424" s="3" t="inlineStr">
         <is>
-          <t>380079</t>
+          <t>380225</t>
         </is>
       </c>
       <c r="E1424" s="3" t="inlineStr">
@@ -45648,7 +45649,7 @@
         </is>
       </c>
       <c r="F1424" s="3" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G1424" s="3" t="inlineStr">
         <is>
@@ -45667,11 +45668,11 @@
         </is>
       </c>
       <c r="C1425" s="2" t="n">
-        <v>1789</v>
+        <v>1785</v>
       </c>
       <c r="D1425" s="2" t="inlineStr">
         <is>
-          <t>380231</t>
+          <t>380228</t>
         </is>
       </c>
       <c r="E1425" s="2" t="inlineStr">
@@ -45680,7 +45681,7 @@
         </is>
       </c>
       <c r="F1425" s="2" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="G1425" s="2" t="inlineStr">
         <is>
@@ -45699,11 +45700,11 @@
         </is>
       </c>
       <c r="C1426" s="3" t="n">
-        <v>1790</v>
+        <v>1786</v>
       </c>
       <c r="D1426" s="3" t="inlineStr">
         <is>
-          <t>380235</t>
+          <t>380412</t>
         </is>
       </c>
       <c r="E1426" s="3" t="inlineStr">
@@ -45712,7 +45713,7 @@
         </is>
       </c>
       <c r="F1426" s="3" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G1426" s="3" t="inlineStr">
         <is>
@@ -45731,20 +45732,20 @@
         </is>
       </c>
       <c r="C1427" s="2" t="n">
-        <v>1791</v>
+        <v>1787</v>
       </c>
       <c r="D1427" s="2" t="inlineStr">
         <is>
-          <t>380229</t>
+          <t>380227</t>
         </is>
       </c>
       <c r="E1427" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1427" s="2" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G1427" s="2" t="inlineStr">
         <is>
@@ -45763,11 +45764,11 @@
         </is>
       </c>
       <c r="C1428" s="3" t="n">
-        <v>1792</v>
+        <v>1788</v>
       </c>
       <c r="D1428" s="3" t="inlineStr">
         <is>
-          <t>380232</t>
+          <t>380079</t>
         </is>
       </c>
       <c r="E1428" s="3" t="inlineStr">
@@ -45776,7 +45777,7 @@
         </is>
       </c>
       <c r="F1428" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G1428" s="3" t="inlineStr">
         <is>
@@ -45795,20 +45796,20 @@
         </is>
       </c>
       <c r="C1429" s="2" t="n">
-        <v>1793</v>
+        <v>1789</v>
       </c>
       <c r="D1429" s="2" t="inlineStr">
         <is>
-          <t>380314</t>
+          <t>380231</t>
         </is>
       </c>
       <c r="E1429" s="2" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1429" s="2" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="G1429" s="2" t="inlineStr">
         <is>
@@ -45827,16 +45828,16 @@
         </is>
       </c>
       <c r="C1430" s="3" t="n">
-        <v>1794</v>
+        <v>1790</v>
       </c>
       <c r="D1430" s="3" t="inlineStr">
         <is>
-          <t>380313</t>
+          <t>380235</t>
         </is>
       </c>
       <c r="E1430" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1430" s="3" t="n">
@@ -45859,11 +45860,11 @@
         </is>
       </c>
       <c r="C1431" s="2" t="n">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="D1431" s="2" t="inlineStr">
         <is>
-          <t>380230</t>
+          <t>380229</t>
         </is>
       </c>
       <c r="E1431" s="2" t="inlineStr">
@@ -45872,7 +45873,7 @@
         </is>
       </c>
       <c r="F1431" s="2" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="G1431" s="2" t="inlineStr">
         <is>
@@ -45891,11 +45892,11 @@
         </is>
       </c>
       <c r="C1432" s="3" t="n">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="D1432" s="3" t="inlineStr">
         <is>
-          <t>380080</t>
+          <t>380232</t>
         </is>
       </c>
       <c r="E1432" s="3" t="inlineStr">
@@ -45904,7 +45905,7 @@
         </is>
       </c>
       <c r="F1432" s="3" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G1432" s="3" t="inlineStr">
         <is>
@@ -45923,20 +45924,20 @@
         </is>
       </c>
       <c r="C1433" s="2" t="n">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="D1433" s="2" t="inlineStr">
         <is>
-          <t>380234</t>
+          <t>380314</t>
         </is>
       </c>
       <c r="E1433" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1433" s="2" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G1433" s="2" t="inlineStr">
         <is>
@@ -45955,20 +45956,20 @@
         </is>
       </c>
       <c r="C1434" s="3" t="n">
-        <v>1799</v>
+        <v>1794</v>
       </c>
       <c r="D1434" s="3" t="inlineStr">
         <is>
-          <t>380233</t>
+          <t>380313</t>
         </is>
       </c>
       <c r="E1434" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1434" s="3" t="n">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="G1434" s="3" t="inlineStr">
         <is>
@@ -45987,20 +45988,20 @@
         </is>
       </c>
       <c r="C1435" s="2" t="n">
-        <v>1802</v>
+        <v>1796</v>
       </c>
       <c r="D1435" s="2" t="inlineStr">
         <is>
-          <t>379413</t>
+          <t>380230</t>
         </is>
       </c>
       <c r="E1435" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1435" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G1435" s="2" t="inlineStr">
         <is>
@@ -46019,20 +46020,20 @@
         </is>
       </c>
       <c r="C1436" s="3" t="n">
-        <v>1803</v>
+        <v>1797</v>
       </c>
       <c r="D1436" s="3" t="inlineStr">
         <is>
-          <t>379412</t>
+          <t>380080</t>
         </is>
       </c>
       <c r="E1436" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1436" s="3" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="G1436" s="3" t="inlineStr">
         <is>
@@ -46051,20 +46052,20 @@
         </is>
       </c>
       <c r="C1437" s="2" t="n">
-        <v>1804</v>
+        <v>1798</v>
       </c>
       <c r="D1437" s="2" t="inlineStr">
         <is>
-          <t>379415</t>
+          <t>380234</t>
         </is>
       </c>
       <c r="E1437" s="2" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1437" s="2" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G1437" s="2" t="inlineStr">
         <is>
@@ -46083,20 +46084,20 @@
         </is>
       </c>
       <c r="C1438" s="3" t="n">
-        <v>1805</v>
+        <v>1799</v>
       </c>
       <c r="D1438" s="3" t="inlineStr">
         <is>
-          <t>379414</t>
+          <t>380233</t>
         </is>
       </c>
       <c r="E1438" s="3" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1438" s="3" t="n">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="G1438" s="3" t="inlineStr">
         <is>
@@ -46111,24 +46112,24 @@
       </c>
       <c r="B1439" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1439" s="2" t="n">
-        <v>1806</v>
+        <v>1800</v>
       </c>
       <c r="D1439" s="2" t="inlineStr">
         <is>
-          <t>379416</t>
+          <t>282382</t>
         </is>
       </c>
       <c r="E1439" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1439" s="2" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="G1439" s="2" t="inlineStr">
         <is>
@@ -46143,24 +46144,24 @@
       </c>
       <c r="B1440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1440" s="3" t="n">
-        <v>1811</v>
+        <v>1801</v>
       </c>
       <c r="D1440" s="3" t="inlineStr">
         <is>
-          <t>379991</t>
+          <t>282383</t>
         </is>
       </c>
       <c r="E1440" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1440" s="3" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="G1440" s="3" t="inlineStr">
         <is>
@@ -46179,20 +46180,20 @@
         </is>
       </c>
       <c r="C1441" s="2" t="n">
-        <v>1812</v>
+        <v>1802</v>
       </c>
       <c r="D1441" s="2" t="inlineStr">
         <is>
-          <t>379989</t>
+          <t>379413</t>
         </is>
       </c>
       <c r="E1441" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1441" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G1441" s="2" t="inlineStr">
         <is>
@@ -46211,20 +46212,20 @@
         </is>
       </c>
       <c r="C1442" s="3" t="n">
-        <v>1813</v>
+        <v>1803</v>
       </c>
       <c r="D1442" s="3" t="inlineStr">
         <is>
-          <t>379988</t>
+          <t>379412</t>
         </is>
       </c>
       <c r="E1442" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1442" s="3" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G1442" s="3" t="inlineStr">
         <is>
@@ -46243,20 +46244,20 @@
         </is>
       </c>
       <c r="C1443" s="2" t="n">
-        <v>1814</v>
+        <v>1804</v>
       </c>
       <c r="D1443" s="2" t="inlineStr">
         <is>
-          <t>379990</t>
+          <t>379415</t>
         </is>
       </c>
       <c r="E1443" s="2" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1443" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G1443" s="2" t="inlineStr">
         <is>
@@ -46275,20 +46276,20 @@
         </is>
       </c>
       <c r="C1444" s="3" t="n">
-        <v>1815</v>
+        <v>1805</v>
       </c>
       <c r="D1444" s="3" t="inlineStr">
         <is>
-          <t>379992</t>
+          <t>379414</t>
         </is>
       </c>
       <c r="E1444" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>64</t>
         </is>
       </c>
       <c r="F1444" s="3" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G1444" s="3" t="inlineStr">
         <is>
@@ -46307,16 +46308,16 @@
         </is>
       </c>
       <c r="C1445" s="2" t="n">
-        <v>1816</v>
+        <v>1806</v>
       </c>
       <c r="D1445" s="2" t="inlineStr">
         <is>
-          <t>380216</t>
+          <t>379416</t>
         </is>
       </c>
       <c r="E1445" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1445" s="2" t="n">
@@ -46335,24 +46336,24 @@
       </c>
       <c r="B1446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1446" s="3" t="n">
-        <v>1822</v>
+        <v>1807</v>
       </c>
       <c r="D1446" s="3" t="inlineStr">
         <is>
-          <t>379994</t>
+          <t>379450</t>
         </is>
       </c>
       <c r="E1446" s="3" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>62</t>
         </is>
       </c>
       <c r="F1446" s="3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G1446" s="3" t="inlineStr">
         <is>
@@ -46367,24 +46368,24 @@
       </c>
       <c r="B1447" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1447" s="2" t="n">
-        <v>1823</v>
+        <v>1808</v>
       </c>
       <c r="D1447" s="2" t="inlineStr">
         <is>
-          <t>379995</t>
+          <t>282381</t>
         </is>
       </c>
       <c r="E1447" s="2" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1447" s="2" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="G1447" s="2" t="inlineStr">
         <is>
@@ -46399,24 +46400,24 @@
       </c>
       <c r="B1448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1448" s="3" t="n">
-        <v>1824</v>
+        <v>1810</v>
       </c>
       <c r="D1448" s="3" t="inlineStr">
         <is>
-          <t>379986</t>
+          <t>282384</t>
         </is>
       </c>
       <c r="E1448" s="3" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>58</t>
         </is>
       </c>
       <c r="F1448" s="3" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G1448" s="3" t="inlineStr">
         <is>
@@ -46435,20 +46436,20 @@
         </is>
       </c>
       <c r="C1449" s="2" t="n">
-        <v>1825</v>
+        <v>1811</v>
       </c>
       <c r="D1449" s="2" t="inlineStr">
         <is>
-          <t>379996</t>
+          <t>379991</t>
         </is>
       </c>
       <c r="E1449" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1449" s="2" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G1449" s="2" t="inlineStr">
         <is>
@@ -46467,20 +46468,20 @@
         </is>
       </c>
       <c r="C1450" s="3" t="n">
-        <v>1826</v>
+        <v>1812</v>
       </c>
       <c r="D1450" s="3" t="inlineStr">
         <is>
-          <t>380304</t>
+          <t>379989</t>
         </is>
       </c>
       <c r="E1450" s="3" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1450" s="3" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="G1450" s="3" t="inlineStr">
         <is>
@@ -46499,20 +46500,20 @@
         </is>
       </c>
       <c r="C1451" s="2" t="n">
-        <v>1827</v>
+        <v>1813</v>
       </c>
       <c r="D1451" s="2" t="inlineStr">
         <is>
-          <t>379419</t>
+          <t>379988</t>
         </is>
       </c>
       <c r="E1451" s="2" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1451" s="2" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="G1451" s="2" t="inlineStr">
         <is>
@@ -46531,20 +46532,20 @@
         </is>
       </c>
       <c r="C1452" s="3" t="n">
-        <v>1828</v>
+        <v>1814</v>
       </c>
       <c r="D1452" s="3" t="inlineStr">
         <is>
-          <t>379418</t>
+          <t>379990</t>
         </is>
       </c>
       <c r="E1452" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1452" s="3" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G1452" s="3" t="inlineStr">
         <is>
@@ -46563,20 +46564,20 @@
         </is>
       </c>
       <c r="C1453" s="2" t="n">
-        <v>1829</v>
+        <v>1815</v>
       </c>
       <c r="D1453" s="2" t="inlineStr">
         <is>
-          <t>379417</t>
+          <t>379992</t>
         </is>
       </c>
       <c r="E1453" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1453" s="2" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G1453" s="2" t="inlineStr">
         <is>
@@ -46595,20 +46596,20 @@
         </is>
       </c>
       <c r="C1454" s="3" t="n">
-        <v>1831</v>
+        <v>1816</v>
       </c>
       <c r="D1454" s="3" t="inlineStr">
         <is>
-          <t>380220</t>
+          <t>380216</t>
         </is>
       </c>
       <c r="E1454" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>68</t>
         </is>
       </c>
       <c r="F1454" s="3" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G1454" s="3" t="inlineStr">
         <is>
@@ -46623,24 +46624,24 @@
       </c>
       <c r="B1455" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1455" s="2" t="n">
-        <v>1832</v>
+        <v>1817</v>
       </c>
       <c r="D1455" s="2" t="inlineStr">
         <is>
-          <t>379997</t>
+          <t>380807</t>
         </is>
       </c>
       <c r="E1455" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1455" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G1455" s="2" t="inlineStr">
         <is>
@@ -46655,15 +46656,15 @@
       </c>
       <c r="B1456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1456" s="3" t="n">
-        <v>1833</v>
+        <v>1818</v>
       </c>
       <c r="D1456" s="3" t="inlineStr">
         <is>
-          <t>380218</t>
+          <t>380669</t>
         </is>
       </c>
       <c r="E1456" s="3" t="inlineStr">
@@ -46672,7 +46673,7 @@
         </is>
       </c>
       <c r="F1456" s="3" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="G1456" s="3" t="inlineStr">
         <is>
@@ -46687,24 +46688,24 @@
       </c>
       <c r="B1457" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1457" s="2" t="n">
-        <v>1834</v>
+        <v>1819</v>
       </c>
       <c r="D1457" s="2" t="inlineStr">
         <is>
-          <t>379999</t>
+          <t>380806</t>
         </is>
       </c>
       <c r="E1457" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1457" s="2" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="G1457" s="2" t="inlineStr">
         <is>
@@ -46719,24 +46720,24 @@
       </c>
       <c r="B1458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1458" s="3" t="n">
-        <v>1835</v>
+        <v>1820</v>
       </c>
       <c r="D1458" s="3" t="inlineStr">
         <is>
-          <t>380219</t>
+          <t>380808</t>
         </is>
       </c>
       <c r="E1458" s="3" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1458" s="3" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="G1458" s="3" t="inlineStr">
         <is>
@@ -46751,24 +46752,24 @@
       </c>
       <c r="B1459" s="2" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="C1459" s="2" t="n">
-        <v>1836</v>
+        <v>1821</v>
       </c>
       <c r="D1459" s="2" t="inlineStr">
         <is>
-          <t>379998</t>
+          <t>380809</t>
         </is>
       </c>
       <c r="E1459" s="2" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>70</t>
         </is>
       </c>
       <c r="F1459" s="2" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="G1459" s="2" t="inlineStr">
         <is>
@@ -46787,20 +46788,20 @@
         </is>
       </c>
       <c r="C1460" s="3" t="n">
-        <v>1837</v>
+        <v>1822</v>
       </c>
       <c r="D1460" s="3" t="inlineStr">
         <is>
-          <t>379985</t>
+          <t>379994</t>
         </is>
       </c>
       <c r="E1460" s="3" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>66</t>
         </is>
       </c>
       <c r="F1460" s="3" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="G1460" s="3" t="inlineStr">
         <is>
@@ -46819,20 +46820,20 @@
         </is>
       </c>
       <c r="C1461" s="2" t="n">
-        <v>1838</v>
+        <v>1823</v>
       </c>
       <c r="D1461" s="2" t="inlineStr">
         <is>
-          <t>379987</t>
+          <t>379995</t>
         </is>
       </c>
       <c r="E1461" s="2" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1461" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G1461" s="2" t="inlineStr">
         <is>
@@ -46851,20 +46852,20 @@
         </is>
       </c>
       <c r="C1462" s="3" t="n">
-        <v>1839</v>
+        <v>1824</v>
       </c>
       <c r="D1462" s="3" t="inlineStr">
         <is>
-          <t>379410</t>
+          <t>379986</t>
         </is>
       </c>
       <c r="E1462" s="3" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>65</t>
         </is>
       </c>
       <c r="F1462" s="3" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G1462" s="3" t="inlineStr">
         <is>
@@ -46883,27 +46884,2043 @@
         </is>
       </c>
       <c r="C1463" s="2" t="n">
+        <v>1825</v>
+      </c>
+      <c r="D1463" s="2" t="inlineStr">
+        <is>
+          <t>379996</t>
+        </is>
+      </c>
+      <c r="E1463" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1463" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1463" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1463" s="2" t="inlineStr"/>
+    </row>
+    <row r="1464" ht="20" customHeight="1">
+      <c r="A1464" s="3" t="n">
+        <v>1460</v>
+      </c>
+      <c r="B1464" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1464" s="3" t="n">
+        <v>1826</v>
+      </c>
+      <c r="D1464" s="3" t="inlineStr">
+        <is>
+          <t>380304</t>
+        </is>
+      </c>
+      <c r="E1464" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1464" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1464" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1464" s="3" t="inlineStr"/>
+    </row>
+    <row r="1465" ht="20" customHeight="1">
+      <c r="A1465" s="2" t="n">
+        <v>1461</v>
+      </c>
+      <c r="B1465" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1465" s="2" t="n">
+        <v>1827</v>
+      </c>
+      <c r="D1465" s="2" t="inlineStr">
+        <is>
+          <t>379419</t>
+        </is>
+      </c>
+      <c r="E1465" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1465" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1465" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1465" s="2" t="inlineStr"/>
+    </row>
+    <row r="1466" ht="20" customHeight="1">
+      <c r="A1466" s="3" t="n">
+        <v>1462</v>
+      </c>
+      <c r="B1466" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1466" s="3" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D1466" s="3" t="inlineStr">
+        <is>
+          <t>379418</t>
+        </is>
+      </c>
+      <c r="E1466" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1466" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1466" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1466" s="3" t="inlineStr"/>
+    </row>
+    <row r="1467" ht="20" customHeight="1">
+      <c r="A1467" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="B1467" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1467" s="2" t="n">
+        <v>1829</v>
+      </c>
+      <c r="D1467" s="2" t="inlineStr">
+        <is>
+          <t>380851</t>
+        </is>
+      </c>
+      <c r="E1467" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1467" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1467" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1467" s="2" t="inlineStr"/>
+    </row>
+    <row r="1468" ht="20" customHeight="1">
+      <c r="A1468" s="3" t="n">
+        <v>1464</v>
+      </c>
+      <c r="B1468" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1468" s="3" t="n">
+        <v>1831</v>
+      </c>
+      <c r="D1468" s="3" t="inlineStr">
+        <is>
+          <t>380220</t>
+        </is>
+      </c>
+      <c r="E1468" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1468" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1468" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1468" s="3" t="inlineStr"/>
+    </row>
+    <row r="1469" ht="20" customHeight="1">
+      <c r="A1469" s="2" t="n">
+        <v>1465</v>
+      </c>
+      <c r="B1469" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1469" s="2" t="n">
+        <v>1832</v>
+      </c>
+      <c r="D1469" s="2" t="inlineStr">
+        <is>
+          <t>379997</t>
+        </is>
+      </c>
+      <c r="E1469" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1469" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1469" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1469" s="2" t="inlineStr"/>
+    </row>
+    <row r="1470" ht="20" customHeight="1">
+      <c r="A1470" s="3" t="n">
+        <v>1466</v>
+      </c>
+      <c r="B1470" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1470" s="3" t="n">
+        <v>1833</v>
+      </c>
+      <c r="D1470" s="3" t="inlineStr">
+        <is>
+          <t>380218</t>
+        </is>
+      </c>
+      <c r="E1470" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1470" s="3" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1470" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1470" s="3" t="inlineStr"/>
+    </row>
+    <row r="1471" ht="20" customHeight="1">
+      <c r="A1471" s="2" t="n">
+        <v>1467</v>
+      </c>
+      <c r="B1471" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1471" s="2" t="n">
+        <v>1834</v>
+      </c>
+      <c r="D1471" s="2" t="inlineStr">
+        <is>
+          <t>379999</t>
+        </is>
+      </c>
+      <c r="E1471" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1471" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1471" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1471" s="2" t="inlineStr"/>
+    </row>
+    <row r="1472" ht="20" customHeight="1">
+      <c r="A1472" s="3" t="n">
+        <v>1468</v>
+      </c>
+      <c r="B1472" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1472" s="3" t="n">
+        <v>1835</v>
+      </c>
+      <c r="D1472" s="3" t="inlineStr">
+        <is>
+          <t>380219</t>
+        </is>
+      </c>
+      <c r="E1472" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1472" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1472" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1472" s="3" t="inlineStr"/>
+    </row>
+    <row r="1473" ht="20" customHeight="1">
+      <c r="A1473" s="2" t="n">
+        <v>1469</v>
+      </c>
+      <c r="B1473" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1473" s="2" t="n">
+        <v>1836</v>
+      </c>
+      <c r="D1473" s="2" t="inlineStr">
+        <is>
+          <t>379998</t>
+        </is>
+      </c>
+      <c r="E1473" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1473" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1473" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1473" s="2" t="inlineStr"/>
+    </row>
+    <row r="1474" ht="20" customHeight="1">
+      <c r="A1474" s="3" t="n">
+        <v>1470</v>
+      </c>
+      <c r="B1474" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1474" s="3" t="n">
+        <v>1837</v>
+      </c>
+      <c r="D1474" s="3" t="inlineStr">
+        <is>
+          <t>379985</t>
+        </is>
+      </c>
+      <c r="E1474" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1474" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1474" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1474" s="3" t="inlineStr"/>
+    </row>
+    <row r="1475" ht="20" customHeight="1">
+      <c r="A1475" s="2" t="n">
+        <v>1471</v>
+      </c>
+      <c r="B1475" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1475" s="2" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D1475" s="2" t="inlineStr">
+        <is>
+          <t>379987</t>
+        </is>
+      </c>
+      <c r="E1475" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1475" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1475" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1475" s="2" t="inlineStr"/>
+    </row>
+    <row r="1476" ht="20" customHeight="1">
+      <c r="A1476" s="3" t="n">
+        <v>1472</v>
+      </c>
+      <c r="B1476" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1476" s="3" t="n">
+        <v>1839</v>
+      </c>
+      <c r="D1476" s="3" t="inlineStr">
+        <is>
+          <t>379410</t>
+        </is>
+      </c>
+      <c r="E1476" s="3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="F1476" s="3" t="n">
+        <v>37</v>
+      </c>
+      <c r="G1476" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1476" s="3" t="inlineStr"/>
+    </row>
+    <row r="1477" ht="20" customHeight="1">
+      <c r="A1477" s="2" t="n">
+        <v>1473</v>
+      </c>
+      <c r="B1477" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1477" s="2" t="n">
+        <v>1840</v>
+      </c>
+      <c r="D1477" s="2" t="inlineStr">
+        <is>
+          <t>379448</t>
+        </is>
+      </c>
+      <c r="E1477" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F1477" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="G1477" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1477" s="2" t="inlineStr"/>
+    </row>
+    <row r="1478" ht="20" customHeight="1">
+      <c r="A1478" s="3" t="n">
+        <v>1474</v>
+      </c>
+      <c r="B1478" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="C1478" s="3" t="n">
         <v>1841</v>
       </c>
-      <c r="D1463" s="2" t="inlineStr">
+      <c r="D1478" s="3" t="inlineStr">
         <is>
           <t>379411</t>
         </is>
       </c>
-      <c r="E1463" s="2" t="inlineStr">
+      <c r="E1478" s="3" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="F1463" s="2" t="n">
+      <c r="F1478" s="3" t="n">
         <v>42</v>
       </c>
-      <c r="G1463" s="2" t="inlineStr">
-        <is>
-          <t>SELESAI</t>
-        </is>
-      </c>
-      <c r="H1463" s="2" t="inlineStr"/>
+      <c r="G1478" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1478" s="3" t="inlineStr"/>
+    </row>
+    <row r="1479" ht="20" customHeight="1">
+      <c r="A1479" s="2" t="n">
+        <v>1475</v>
+      </c>
+      <c r="B1479" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1479" s="2" t="n">
+        <v>1843</v>
+      </c>
+      <c r="D1479" s="2" t="inlineStr">
+        <is>
+          <t>380810</t>
+        </is>
+      </c>
+      <c r="E1479" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1479" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1479" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1479" s="2" t="inlineStr"/>
+    </row>
+    <row r="1480" ht="20" customHeight="1">
+      <c r="A1480" s="3" t="n">
+        <v>1476</v>
+      </c>
+      <c r="B1480" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1480" s="3" t="n">
+        <v>1845</v>
+      </c>
+      <c r="D1480" s="3" t="inlineStr">
+        <is>
+          <t>380762</t>
+        </is>
+      </c>
+      <c r="E1480" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1480" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="G1480" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1480" s="3" t="inlineStr"/>
+    </row>
+    <row r="1481" ht="20" customHeight="1">
+      <c r="A1481" s="2" t="n">
+        <v>1477</v>
+      </c>
+      <c r="B1481" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1481" s="2" t="n">
+        <v>1846</v>
+      </c>
+      <c r="D1481" s="2" t="inlineStr">
+        <is>
+          <t>380764</t>
+        </is>
+      </c>
+      <c r="E1481" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1481" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1481" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1481" s="2" t="inlineStr"/>
+    </row>
+    <row r="1482" ht="20" customHeight="1">
+      <c r="A1482" s="3" t="n">
+        <v>1478</v>
+      </c>
+      <c r="B1482" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1482" s="3" t="n">
+        <v>1847</v>
+      </c>
+      <c r="D1482" s="3" t="inlineStr">
+        <is>
+          <t>380763</t>
+        </is>
+      </c>
+      <c r="E1482" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1482" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1482" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1482" s="3" t="inlineStr"/>
+    </row>
+    <row r="1483" ht="20" customHeight="1">
+      <c r="A1483" s="2" t="n">
+        <v>1479</v>
+      </c>
+      <c r="B1483" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1483" s="2" t="n">
+        <v>1848</v>
+      </c>
+      <c r="D1483" s="2" t="inlineStr">
+        <is>
+          <t>380761</t>
+        </is>
+      </c>
+      <c r="E1483" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1483" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1483" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1483" s="2" t="inlineStr"/>
+    </row>
+    <row r="1484" ht="20" customHeight="1">
+      <c r="A1484" s="3" t="n">
+        <v>1480</v>
+      </c>
+      <c r="B1484" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1484" s="3" t="n">
+        <v>1849</v>
+      </c>
+      <c r="D1484" s="3" t="inlineStr">
+        <is>
+          <t>380765</t>
+        </is>
+      </c>
+      <c r="E1484" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1484" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1484" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1484" s="3" t="inlineStr"/>
+    </row>
+    <row r="1485" ht="20" customHeight="1">
+      <c r="A1485" s="2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="B1485" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1485" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="D1485" s="2" t="inlineStr">
+        <is>
+          <t>380766</t>
+        </is>
+      </c>
+      <c r="E1485" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1485" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1485" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1485" s="2" t="inlineStr"/>
+    </row>
+    <row r="1486" ht="20" customHeight="1">
+      <c r="A1486" s="3" t="n">
+        <v>1482</v>
+      </c>
+      <c r="B1486" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1486" s="3" t="n">
+        <v>1851</v>
+      </c>
+      <c r="D1486" s="3" t="inlineStr">
+        <is>
+          <t>380768</t>
+        </is>
+      </c>
+      <c r="E1486" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="F1486" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="G1486" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1486" s="3" t="inlineStr"/>
+    </row>
+    <row r="1487" ht="20" customHeight="1">
+      <c r="A1487" s="2" t="n">
+        <v>1483</v>
+      </c>
+      <c r="B1487" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1487" s="2" t="n">
+        <v>1852</v>
+      </c>
+      <c r="D1487" s="2" t="inlineStr">
+        <is>
+          <t>380649</t>
+        </is>
+      </c>
+      <c r="E1487" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1487" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1487" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1487" s="2" t="inlineStr"/>
+    </row>
+    <row r="1488" ht="20" customHeight="1">
+      <c r="A1488" s="3" t="n">
+        <v>1484</v>
+      </c>
+      <c r="B1488" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1488" s="3" t="n">
+        <v>1853</v>
+      </c>
+      <c r="D1488" s="3" t="inlineStr">
+        <is>
+          <t>380767</t>
+        </is>
+      </c>
+      <c r="E1488" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1488" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1488" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1488" s="3" t="inlineStr"/>
+    </row>
+    <row r="1489" ht="20" customHeight="1">
+      <c r="A1489" s="2" t="n">
+        <v>1485</v>
+      </c>
+      <c r="B1489" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1489" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="D1489" s="2" t="inlineStr">
+        <is>
+          <t>380650</t>
+        </is>
+      </c>
+      <c r="E1489" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1489" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1489" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1489" s="2" t="inlineStr"/>
+    </row>
+    <row r="1490" ht="20" customHeight="1">
+      <c r="A1490" s="3" t="n">
+        <v>1486</v>
+      </c>
+      <c r="B1490" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1490" s="3" t="n">
+        <v>1855</v>
+      </c>
+      <c r="D1490" s="3" t="inlineStr">
+        <is>
+          <t>380651</t>
+        </is>
+      </c>
+      <c r="E1490" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1490" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1490" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1490" s="3" t="inlineStr"/>
+    </row>
+    <row r="1491" ht="20" customHeight="1">
+      <c r="A1491" s="2" t="n">
+        <v>1487</v>
+      </c>
+      <c r="B1491" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1491" s="2" t="n">
+        <v>1857</v>
+      </c>
+      <c r="D1491" s="2" t="inlineStr">
+        <is>
+          <t>380802</t>
+        </is>
+      </c>
+      <c r="E1491" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1491" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1491" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1491" s="2" t="inlineStr"/>
+    </row>
+    <row r="1492" ht="20" customHeight="1">
+      <c r="A1492" s="3" t="n">
+        <v>1488</v>
+      </c>
+      <c r="B1492" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1492" s="3" t="n">
+        <v>1858</v>
+      </c>
+      <c r="D1492" s="3" t="inlineStr">
+        <is>
+          <t>380652</t>
+        </is>
+      </c>
+      <c r="E1492" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1492" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1492" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1492" s="3" t="inlineStr"/>
+    </row>
+    <row r="1493" ht="20" customHeight="1">
+      <c r="A1493" s="2" t="n">
+        <v>1489</v>
+      </c>
+      <c r="B1493" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1493" s="2" t="n">
+        <v>1859</v>
+      </c>
+      <c r="D1493" s="2" t="inlineStr">
+        <is>
+          <t>380803</t>
+        </is>
+      </c>
+      <c r="E1493" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1493" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1493" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1493" s="2" t="inlineStr"/>
+    </row>
+    <row r="1494" ht="20" customHeight="1">
+      <c r="A1494" s="3" t="n">
+        <v>1490</v>
+      </c>
+      <c r="B1494" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1494" s="3" t="n">
+        <v>1860</v>
+      </c>
+      <c r="D1494" s="3" t="inlineStr">
+        <is>
+          <t>380655</t>
+        </is>
+      </c>
+      <c r="E1494" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1494" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1494" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1494" s="3" t="inlineStr"/>
+    </row>
+    <row r="1495" ht="20" customHeight="1">
+      <c r="A1495" s="2" t="n">
+        <v>1491</v>
+      </c>
+      <c r="B1495" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1495" s="2" t="n">
+        <v>1861</v>
+      </c>
+      <c r="D1495" s="2" t="inlineStr">
+        <is>
+          <t>380467</t>
+        </is>
+      </c>
+      <c r="E1495" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1495" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="G1495" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1495" s="2" t="inlineStr"/>
+    </row>
+    <row r="1496" ht="20" customHeight="1">
+      <c r="A1496" s="3" t="n">
+        <v>1492</v>
+      </c>
+      <c r="B1496" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1496" s="3" t="n">
+        <v>1862</v>
+      </c>
+      <c r="D1496" s="3" t="inlineStr">
+        <is>
+          <t>380466</t>
+        </is>
+      </c>
+      <c r="E1496" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1496" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1496" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1496" s="3" t="inlineStr"/>
+    </row>
+    <row r="1497" ht="20" customHeight="1">
+      <c r="A1497" s="2" t="n">
+        <v>1493</v>
+      </c>
+      <c r="B1497" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1497" s="2" t="n">
+        <v>1863</v>
+      </c>
+      <c r="D1497" s="2" t="inlineStr">
+        <is>
+          <t>380654</t>
+        </is>
+      </c>
+      <c r="E1497" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1497" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1497" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1497" s="2" t="inlineStr"/>
+    </row>
+    <row r="1498" ht="20" customHeight="1">
+      <c r="A1498" s="3" t="n">
+        <v>1494</v>
+      </c>
+      <c r="B1498" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1498" s="3" t="n">
+        <v>1864</v>
+      </c>
+      <c r="D1498" s="3" t="inlineStr">
+        <is>
+          <t>380769</t>
+        </is>
+      </c>
+      <c r="E1498" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1498" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1498" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1498" s="3" t="inlineStr"/>
+    </row>
+    <row r="1499" ht="20" customHeight="1">
+      <c r="A1499" s="2" t="n">
+        <v>1495</v>
+      </c>
+      <c r="B1499" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1499" s="2" t="n">
+        <v>1865</v>
+      </c>
+      <c r="D1499" s="2" t="inlineStr">
+        <is>
+          <t>380653</t>
+        </is>
+      </c>
+      <c r="E1499" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1499" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="G1499" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1499" s="2" t="inlineStr"/>
+    </row>
+    <row r="1500" ht="20" customHeight="1">
+      <c r="A1500" s="3" t="n">
+        <v>1496</v>
+      </c>
+      <c r="B1500" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1500" s="3" t="n">
+        <v>1866</v>
+      </c>
+      <c r="D1500" s="3" t="inlineStr">
+        <is>
+          <t>380770</t>
+        </is>
+      </c>
+      <c r="E1500" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="F1500" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1500" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1500" s="3" t="inlineStr"/>
+    </row>
+    <row r="1501" ht="20" customHeight="1">
+      <c r="A1501" s="2" t="n">
+        <v>1497</v>
+      </c>
+      <c r="B1501" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1501" s="2" t="n">
+        <v>1867</v>
+      </c>
+      <c r="D1501" s="2" t="inlineStr">
+        <is>
+          <t>380656</t>
+        </is>
+      </c>
+      <c r="E1501" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1501" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="G1501" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1501" s="2" t="inlineStr"/>
+    </row>
+    <row r="1502" ht="20" customHeight="1">
+      <c r="A1502" s="3" t="n">
+        <v>1498</v>
+      </c>
+      <c r="B1502" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1502" s="3" t="n">
+        <v>1868</v>
+      </c>
+      <c r="D1502" s="3" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="E1502" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1502" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1502" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1502" s="3" t="inlineStr"/>
+    </row>
+    <row r="1503" ht="20" customHeight="1">
+      <c r="A1503" s="2" t="n">
+        <v>1499</v>
+      </c>
+      <c r="B1503" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1503" s="2" t="n">
+        <v>1869</v>
+      </c>
+      <c r="D1503" s="2" t="inlineStr">
+        <is>
+          <t>380657</t>
+        </is>
+      </c>
+      <c r="E1503" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1503" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="G1503" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1503" s="2" t="inlineStr"/>
+    </row>
+    <row r="1504" ht="20" customHeight="1">
+      <c r="A1504" s="3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="B1504" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1504" s="3" t="n">
+        <v>1870</v>
+      </c>
+      <c r="D1504" s="3" t="inlineStr">
+        <is>
+          <t>380648</t>
+        </is>
+      </c>
+      <c r="E1504" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1504" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1504" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1504" s="3" t="inlineStr"/>
+    </row>
+    <row r="1505" ht="20" customHeight="1">
+      <c r="A1505" s="2" t="n">
+        <v>1501</v>
+      </c>
+      <c r="B1505" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1505" s="2" t="n">
+        <v>1871</v>
+      </c>
+      <c r="D1505" s="2" t="inlineStr">
+        <is>
+          <t>380469</t>
+        </is>
+      </c>
+      <c r="E1505" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1505" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1505" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1505" s="2" t="inlineStr"/>
+    </row>
+    <row r="1506" ht="20" customHeight="1">
+      <c r="A1506" s="3" t="n">
+        <v>1502</v>
+      </c>
+      <c r="B1506" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1506" s="3" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D1506" s="3" t="inlineStr">
+        <is>
+          <t>380470</t>
+        </is>
+      </c>
+      <c r="E1506" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1506" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1506" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1506" s="3" t="inlineStr"/>
+    </row>
+    <row r="1507" ht="20" customHeight="1">
+      <c r="A1507" s="2" t="n">
+        <v>1503</v>
+      </c>
+      <c r="B1507" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1507" s="2" t="n">
+        <v>1873</v>
+      </c>
+      <c r="D1507" s="2" t="inlineStr">
+        <is>
+          <t>380662</t>
+        </is>
+      </c>
+      <c r="E1507" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1507" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1507" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1507" s="2" t="inlineStr"/>
+    </row>
+    <row r="1508" ht="20" customHeight="1">
+      <c r="A1508" s="3" t="n">
+        <v>1504</v>
+      </c>
+      <c r="B1508" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1508" s="3" t="n">
+        <v>1874</v>
+      </c>
+      <c r="D1508" s="3" t="inlineStr">
+        <is>
+          <t>380663</t>
+        </is>
+      </c>
+      <c r="E1508" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1508" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1508" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1508" s="3" t="inlineStr"/>
+    </row>
+    <row r="1509" ht="20" customHeight="1">
+      <c r="A1509" s="2" t="n">
+        <v>1505</v>
+      </c>
+      <c r="B1509" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1509" s="2" t="n">
+        <v>1875</v>
+      </c>
+      <c r="D1509" s="2" t="inlineStr">
+        <is>
+          <t>380660</t>
+        </is>
+      </c>
+      <c r="E1509" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1509" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1509" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1509" s="2" t="inlineStr"/>
+    </row>
+    <row r="1510" ht="20" customHeight="1">
+      <c r="A1510" s="3" t="n">
+        <v>1506</v>
+      </c>
+      <c r="B1510" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1510" s="3" t="n">
+        <v>1876</v>
+      </c>
+      <c r="D1510" s="3" t="inlineStr">
+        <is>
+          <t>380659</t>
+        </is>
+      </c>
+      <c r="E1510" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1510" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="G1510" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1510" s="3" t="inlineStr"/>
+    </row>
+    <row r="1511" ht="20" customHeight="1">
+      <c r="A1511" s="2" t="n">
+        <v>1507</v>
+      </c>
+      <c r="B1511" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1511" s="2" t="n">
+        <v>1877</v>
+      </c>
+      <c r="D1511" s="2" t="inlineStr">
+        <is>
+          <t>380661</t>
+        </is>
+      </c>
+      <c r="E1511" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1511" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="G1511" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1511" s="2" t="inlineStr"/>
+    </row>
+    <row r="1512" ht="20" customHeight="1">
+      <c r="A1512" s="3" t="n">
+        <v>1508</v>
+      </c>
+      <c r="B1512" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1512" s="3" t="n">
+        <v>1878</v>
+      </c>
+      <c r="D1512" s="3" t="inlineStr">
+        <is>
+          <t>380804</t>
+        </is>
+      </c>
+      <c r="E1512" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="F1512" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1512" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1512" s="3" t="inlineStr"/>
+    </row>
+    <row r="1513" ht="20" customHeight="1">
+      <c r="A1513" s="2" t="n">
+        <v>1509</v>
+      </c>
+      <c r="B1513" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1513" s="2" t="n">
+        <v>1879</v>
+      </c>
+      <c r="D1513" s="2" t="inlineStr">
+        <is>
+          <t>380664</t>
+        </is>
+      </c>
+      <c r="E1513" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1513" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1513" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1513" s="2" t="inlineStr"/>
+    </row>
+    <row r="1514" ht="20" customHeight="1">
+      <c r="A1514" s="3" t="n">
+        <v>1510</v>
+      </c>
+      <c r="B1514" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1514" s="3" t="n">
+        <v>1880</v>
+      </c>
+      <c r="D1514" s="3" t="inlineStr">
+        <is>
+          <t>380471</t>
+        </is>
+      </c>
+      <c r="E1514" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1514" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1514" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1514" s="3" t="inlineStr"/>
+    </row>
+    <row r="1515" ht="20" customHeight="1">
+      <c r="A1515" s="2" t="n">
+        <v>1511</v>
+      </c>
+      <c r="B1515" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1515" s="2" t="n">
+        <v>1881</v>
+      </c>
+      <c r="D1515" s="2" t="inlineStr">
+        <is>
+          <t>380667</t>
+        </is>
+      </c>
+      <c r="E1515" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1515" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1515" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1515" s="2" t="inlineStr"/>
+    </row>
+    <row r="1516" ht="20" customHeight="1">
+      <c r="A1516" s="3" t="n">
+        <v>1512</v>
+      </c>
+      <c r="B1516" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1516" s="3" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D1516" s="3" t="inlineStr">
+        <is>
+          <t>380665</t>
+        </is>
+      </c>
+      <c r="E1516" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1516" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="G1516" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1516" s="3" t="inlineStr"/>
+    </row>
+    <row r="1517" ht="20" customHeight="1">
+      <c r="A1517" s="2" t="n">
+        <v>1513</v>
+      </c>
+      <c r="B1517" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1517" s="2" t="n">
+        <v>1883</v>
+      </c>
+      <c r="D1517" s="2" t="inlineStr">
+        <is>
+          <t>380666</t>
+        </is>
+      </c>
+      <c r="E1517" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1517" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1517" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1517" s="2" t="inlineStr"/>
+    </row>
+    <row r="1518" ht="20" customHeight="1">
+      <c r="A1518" s="3" t="n">
+        <v>1514</v>
+      </c>
+      <c r="B1518" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1518" s="3" t="n">
+        <v>1884</v>
+      </c>
+      <c r="D1518" s="3" t="inlineStr">
+        <is>
+          <t>380472</t>
+        </is>
+      </c>
+      <c r="E1518" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1518" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="G1518" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1518" s="3" t="inlineStr"/>
+    </row>
+    <row r="1519" ht="20" customHeight="1">
+      <c r="A1519" s="2" t="n">
+        <v>1515</v>
+      </c>
+      <c r="B1519" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1519" s="2" t="n">
+        <v>1885</v>
+      </c>
+      <c r="D1519" s="2" t="inlineStr">
+        <is>
+          <t>380805</t>
+        </is>
+      </c>
+      <c r="E1519" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1519" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G1519" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1519" s="2" t="inlineStr"/>
+    </row>
+    <row r="1520" ht="20" customHeight="1">
+      <c r="A1520" s="3" t="n">
+        <v>1516</v>
+      </c>
+      <c r="B1520" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1520" s="3" t="n">
+        <v>1886</v>
+      </c>
+      <c r="D1520" s="3" t="inlineStr">
+        <is>
+          <t>379449</t>
+        </is>
+      </c>
+      <c r="E1520" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F1520" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="G1520" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1520" s="3" t="inlineStr"/>
+    </row>
+    <row r="1521" ht="20" customHeight="1">
+      <c r="A1521" s="2" t="n">
+        <v>1517</v>
+      </c>
+      <c r="B1521" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1521" s="2" t="n">
+        <v>1887</v>
+      </c>
+      <c r="D1521" s="2" t="inlineStr">
+        <is>
+          <t>379447</t>
+        </is>
+      </c>
+      <c r="E1521" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="F1521" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="G1521" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1521" s="2" t="inlineStr"/>
+    </row>
+    <row r="1522" ht="20" customHeight="1">
+      <c r="A1522" s="3" t="n">
+        <v>1518</v>
+      </c>
+      <c r="B1522" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1522" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="D1522" s="3" t="inlineStr">
+        <is>
+          <t>380476</t>
+        </is>
+      </c>
+      <c r="E1522" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="F1522" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="G1522" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1522" s="3" t="inlineStr"/>
+    </row>
+    <row r="1523" ht="20" customHeight="1">
+      <c r="A1523" s="2" t="n">
+        <v>1519</v>
+      </c>
+      <c r="B1523" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1523" s="2" t="n">
+        <v>1891</v>
+      </c>
+      <c r="D1523" s="2" t="inlineStr">
+        <is>
+          <t>380474</t>
+        </is>
+      </c>
+      <c r="E1523" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F1523" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G1523" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1523" s="2" t="inlineStr"/>
+    </row>
+    <row r="1524" ht="20" customHeight="1">
+      <c r="A1524" s="3" t="n">
+        <v>1520</v>
+      </c>
+      <c r="B1524" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1524" s="3" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D1524" s="3" t="inlineStr">
+        <is>
+          <t>380668</t>
+        </is>
+      </c>
+      <c r="E1524" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="F1524" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="G1524" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1524" s="3" t="inlineStr"/>
+    </row>
+    <row r="1525" ht="20" customHeight="1">
+      <c r="A1525" s="2" t="n">
+        <v>1521</v>
+      </c>
+      <c r="B1525" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1525" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="D1525" s="2" t="inlineStr">
+        <is>
+          <t>380473</t>
+        </is>
+      </c>
+      <c r="E1525" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="F1525" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="G1525" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1525" s="2" t="inlineStr"/>
+    </row>
+    <row r="1526" ht="20" customHeight="1">
+      <c r="A1526" s="3" t="n">
+        <v>1522</v>
+      </c>
+      <c r="B1526" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="C1526" s="3" t="n">
+        <v>1894</v>
+      </c>
+      <c r="D1526" s="3" t="inlineStr">
+        <is>
+          <t>380475</t>
+        </is>
+      </c>
+      <c r="E1526" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F1526" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="G1526" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="H1526" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -80765,6 +82782,1797 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G68"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>No Gudang</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="inlineStr">
+        <is>
+          <t>Nomor Barcode</t>
+        </is>
+      </c>
+      <c r="D4" s="1" t="inlineStr">
+        <is>
+          <t>Grade</t>
+        </is>
+      </c>
+      <c r="E4" s="1" t="inlineStr">
+        <is>
+          <t>Berat (Kg)</t>
+        </is>
+      </c>
+      <c r="F4" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G4" s="1" t="inlineStr">
+        <is>
+          <t>Keterangan</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>1711</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>282379</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6" ht="20" customHeight="1">
+      <c r="A6" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1739</v>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>380901</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>1754</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>282385</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1755</v>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>282380</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>1800</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>282382</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1801</v>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>282383</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>33</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>1807</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>379450</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1808</v>
+      </c>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>282381</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>1810</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>282384</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>1817</v>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>380807</t>
+        </is>
+      </c>
+      <c r="D14" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F14" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G14" s="3" t="inlineStr"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>1818</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>380669</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>1819</v>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>380806</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>1820</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>380808</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="3" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>1821</v>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>380809</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>1829</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>380851</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="3" t="n">
+        <v>16</v>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>1840</v>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>379448</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>1843</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>380810</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1845</v>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>380762</t>
+        </is>
+      </c>
+      <c r="D22" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>1846</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>380764</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24" ht="20" customHeight="1">
+      <c r="A24" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1847</v>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>380763</t>
+        </is>
+      </c>
+      <c r="D24" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G24" s="3" t="inlineStr"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>380761</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>1849</v>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>380765</t>
+        </is>
+      </c>
+      <c r="D26" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F26" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G26" s="3" t="inlineStr"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>1850</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>380766</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="n">
+        <v>24</v>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1851</v>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>380768</t>
+        </is>
+      </c>
+      <c r="D28" s="3" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G28" s="3" t="inlineStr"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>1852</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>380649</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="3" t="n">
+        <v>26</v>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1853</v>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>380767</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G30" s="3" t="inlineStr"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>1854</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>380650</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="3" t="n">
+        <v>28</v>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1855</v>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>380651</t>
+        </is>
+      </c>
+      <c r="D32" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>1857</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>380802</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>1858</v>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>380652</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>39</v>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>1859</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>380803</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>1860</v>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>380655</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>43</v>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>1861</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>380467</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="n">
+        <v>34</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
+        <is>
+          <t>380466</t>
+        </is>
+      </c>
+      <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>32</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="inlineStr"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>1863</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>380654</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1864</v>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
+        <is>
+          <t>380769</t>
+        </is>
+      </c>
+      <c r="D40" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="F40" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G40" s="3" t="inlineStr"/>
+    </row>
+    <row r="41" ht="20" customHeight="1">
+      <c r="A41" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>1865</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>380653</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1866</v>
+      </c>
+      <c r="C42" s="3" t="inlineStr">
+        <is>
+          <t>380770</t>
+        </is>
+      </c>
+      <c r="D42" s="3" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F42" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr"/>
+    </row>
+    <row r="43" ht="20" customHeight="1">
+      <c r="A43" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>1867</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>380656</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="20" customHeight="1">
+      <c r="A44" s="3" t="n">
+        <v>40</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>1868</v>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
+        <is>
+          <t>380658</t>
+        </is>
+      </c>
+      <c r="D44" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>47</v>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr"/>
+    </row>
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>1869</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>380657</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>1870</v>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
+        <is>
+          <t>380648</t>
+        </is>
+      </c>
+      <c r="D46" s="3" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F46" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G46" s="3" t="inlineStr"/>
+    </row>
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>1871</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>380469</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48" ht="20" customHeight="1">
+      <c r="A48" s="3" t="n">
+        <v>44</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1872</v>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
+        <is>
+          <t>380470</t>
+        </is>
+      </c>
+      <c r="D48" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>38</v>
+      </c>
+      <c r="F48" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G48" s="3" t="inlineStr"/>
+    </row>
+    <row r="49" ht="20" customHeight="1">
+      <c r="A49" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>1873</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>380662</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50" ht="20" customHeight="1">
+      <c r="A50" s="3" t="n">
+        <v>46</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1874</v>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>380663</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="inlineStr"/>
+    </row>
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>1875</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>380660</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+    </row>
+    <row r="52" ht="20" customHeight="1">
+      <c r="A52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>1876</v>
+      </c>
+      <c r="C52" s="3" t="inlineStr">
+        <is>
+          <t>380659</t>
+        </is>
+      </c>
+      <c r="D52" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>48</v>
+      </c>
+      <c r="F52" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G52" s="3" t="inlineStr"/>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>1877</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>380661</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr"/>
+    </row>
+    <row r="54" ht="20" customHeight="1">
+      <c r="A54" s="3" t="n">
+        <v>50</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>1878</v>
+      </c>
+      <c r="C54" s="3" t="inlineStr">
+        <is>
+          <t>380804</t>
+        </is>
+      </c>
+      <c r="D54" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F54" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G54" s="3" t="inlineStr"/>
+    </row>
+    <row r="55" ht="20" customHeight="1">
+      <c r="A55" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>1879</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>380664</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+    </row>
+    <row r="56" ht="20" customHeight="1">
+      <c r="A56" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>1880</v>
+      </c>
+      <c r="C56" s="3" t="inlineStr">
+        <is>
+          <t>380471</t>
+        </is>
+      </c>
+      <c r="D56" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F56" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G56" s="3" t="inlineStr"/>
+    </row>
+    <row r="57" ht="20" customHeight="1">
+      <c r="A57" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>1881</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>380667</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr"/>
+    </row>
+    <row r="58" ht="20" customHeight="1">
+      <c r="A58" s="3" t="n">
+        <v>54</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>1882</v>
+      </c>
+      <c r="C58" s="3" t="inlineStr">
+        <is>
+          <t>380665</t>
+        </is>
+      </c>
+      <c r="D58" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>36</v>
+      </c>
+      <c r="F58" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G58" s="3" t="inlineStr"/>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="A59" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>1883</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>380666</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="A60" s="3" t="n">
+        <v>56</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>1884</v>
+      </c>
+      <c r="C60" s="3" t="inlineStr">
+        <is>
+          <t>380472</t>
+        </is>
+      </c>
+      <c r="D60" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>31</v>
+      </c>
+      <c r="F60" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G60" s="3" t="inlineStr"/>
+    </row>
+    <row r="61" ht="20" customHeight="1">
+      <c r="A61" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>1885</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>380805</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62" ht="20" customHeight="1">
+      <c r="A62" s="3" t="n">
+        <v>58</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>1886</v>
+      </c>
+      <c r="C62" s="3" t="inlineStr">
+        <is>
+          <t>379449</t>
+        </is>
+      </c>
+      <c r="D62" s="3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="F62" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G62" s="3" t="inlineStr"/>
+    </row>
+    <row r="63" ht="20" customHeight="1">
+      <c r="A63" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>1887</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>379447</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr"/>
+    </row>
+    <row r="64" ht="20" customHeight="1">
+      <c r="A64" s="3" t="n">
+        <v>60</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>1890</v>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>380476</t>
+        </is>
+      </c>
+      <c r="D64" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>35</v>
+      </c>
+      <c r="F64" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr"/>
+    </row>
+    <row r="65" ht="20" customHeight="1">
+      <c r="A65" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>1891</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>380474</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr"/>
+    </row>
+    <row r="66" ht="20" customHeight="1">
+      <c r="A66" s="3" t="n">
+        <v>62</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>1892</v>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>380668</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>45</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr"/>
+    </row>
+    <row r="67" ht="20" customHeight="1">
+      <c r="A67" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>1893</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>380473</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68" ht="20" customHeight="1">
+      <c r="A68" s="3" t="n">
+        <v>64</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>1894</v>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>380475</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>42</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>SELESAI</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
